--- a/activity/WEEKLY_RECAP_REP.xlsx
+++ b/activity/WEEKLY_RECAP_REP.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2319" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2583" uniqueCount="590">
   <si>
     <t>Weekly Rep Recap</t>
   </si>
@@ -1020,6 +1020,102 @@
   </si>
   <si>
     <t>New Clients — September 2026</t>
+  </si>
+  <si>
+    <t>New = customer's first invoice landed in this month · derived from invoice history through 2026-09-11</t>
+  </si>
+  <si>
+    <t>YTD New Clients</t>
+  </si>
+  <si>
+    <t>This Month</t>
+  </si>
+  <si>
+    <t>Last Month</t>
+  </si>
+  <si>
+    <t>Best Month (Apr)</t>
+  </si>
+  <si>
+    <t>Month-over-month · new clients by rep</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Karin</t>
+  </si>
+  <si>
+    <t>Megan</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>MoM Δ</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>+2</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>+6</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>+4</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>-8</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>-2</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>+1</t>
+  </si>
+  <si>
+    <t>August</t>
+  </si>
+  <si>
+    <t>+7</t>
+  </si>
+  <si>
+    <t>September (MTD)</t>
+  </si>
+  <si>
+    <t>-12</t>
+  </si>
+  <si>
+    <t>YTD Total</t>
+  </si>
+  <si>
+    <t>September new clients (2)</t>
+  </si>
+  <si>
+    <t>2026 new-client roster (75) — sorted newest first</t>
+  </si>
+  <si>
+    <t>First Invoice</t>
   </si>
   <si>
     <t>Outstanding Balances (Aging)</t>
@@ -1706,7 +1802,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0;(&quot;$&quot;#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1848,6 +1944,34 @@
       <sz val="13"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="0C4E54"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="7A7974"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="1E7F3E"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="B22222"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1930,7 +2054,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -2073,6 +2197,33 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -3190,46 +3341,46 @@
         <v>262</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>338</v>
+        <v>370</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>339</v>
+        <v>371</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>224</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>341</v>
+        <v>373</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>226</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>342</v>
+        <v>374</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>343</v>
+        <v>375</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>227</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>344</v>
+        <v>376</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>345</v>
+        <v>377</v>
       </c>
       <c r="M1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>346</v>
+        <v>378</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>347</v>
+        <v>379</v>
       </c>
       <c r="P1" s="9" t="s">
         <v>229</v>
@@ -3240,10 +3391,10 @@
         <v>203</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>349</v>
+        <v>381</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>241</v>
@@ -3290,10 +3441,10 @@
         <v>143</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>350</v>
+        <v>382</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>351</v>
+        <v>383</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>241</v>
@@ -3340,10 +3491,10 @@
         <v>100</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>352</v>
+        <v>384</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>231</v>
@@ -3393,7 +3544,7 @@
         <v>104</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>354</v>
+        <v>386</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>240</v>
@@ -3440,10 +3591,10 @@
         <v>146</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>355</v>
+        <v>387</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>356</v>
+        <v>388</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>270</v>
@@ -3490,10 +3641,10 @@
         <v>168</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>358</v>
+        <v>390</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>251</v>
@@ -3540,10 +3691,10 @@
         <v>83</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>359</v>
+        <v>391</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>360</v>
+        <v>392</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>231</v>
@@ -3593,7 +3744,7 @@
         <v>77</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>361</v>
+        <v>393</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>231</v>
@@ -3643,7 +3794,7 @@
         <v>109</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>362</v>
+        <v>394</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>231</v>
@@ -3690,10 +3841,10 @@
         <v>204</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>363</v>
+        <v>395</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>364</v>
+        <v>396</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>231</v>
@@ -3740,10 +3891,10 @@
         <v>206</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>365</v>
+        <v>397</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>366</v>
+        <v>398</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>295</v>
@@ -3790,10 +3941,10 @@
         <v>118</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>367</v>
+        <v>399</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>368</v>
+        <v>400</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>231</v>
@@ -3843,7 +3994,7 @@
         <v>112</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>369</v>
+        <v>401</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>245</v>
@@ -3890,10 +4041,10 @@
         <v>207</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>370</v>
+        <v>402</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>371</v>
+        <v>403</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>270</v>
@@ -3940,10 +4091,10 @@
         <v>169</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>373</v>
+        <v>405</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>241</v>
@@ -3993,7 +4144,7 @@
         <v>89</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>374</v>
+        <v>406</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>296</v>
@@ -4040,10 +4191,10 @@
         <v>145</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>375</v>
+        <v>407</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>231</v>
@@ -4093,7 +4244,7 @@
         <v>71</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>377</v>
+        <v>409</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>230</v>
@@ -4140,10 +4291,10 @@
         <v>161</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>378</v>
+        <v>410</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>379</v>
+        <v>411</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>241</v>
@@ -4190,10 +4341,10 @@
         <v>114</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>380</v>
+        <v>412</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>381</v>
+        <v>413</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>236</v>
@@ -4243,7 +4394,7 @@
         <v>116</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>382</v>
+        <v>414</v>
       </c>
       <c r="D22" s="10" t="s">
         <v>250</v>
@@ -4293,7 +4444,7 @@
         <v>90</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>383</v>
+        <v>415</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>296</v>
@@ -4340,10 +4491,10 @@
         <v>159</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>384</v>
+        <v>416</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>385</v>
+        <v>417</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>247</v>
@@ -4390,10 +4541,10 @@
         <v>172</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>386</v>
+        <v>418</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>387</v>
+        <v>419</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>300</v>
@@ -4440,10 +4591,10 @@
         <v>126</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>388</v>
+        <v>420</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>389</v>
+        <v>421</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>250</v>
@@ -4490,10 +4641,10 @@
         <v>92</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>390</v>
+        <v>422</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>391</v>
+        <v>423</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>236</v>
@@ -4540,10 +4691,10 @@
         <v>208</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>392</v>
+        <v>424</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>393</v>
+        <v>425</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>250</v>
@@ -4590,10 +4741,10 @@
         <v>86</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>394</v>
+        <v>426</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>395</v>
+        <v>427</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>231</v>
@@ -4640,10 +4791,10 @@
         <v>148</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>396</v>
+        <v>428</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>397</v>
+        <v>429</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>241</v>
@@ -4690,10 +4841,10 @@
         <v>103</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>399</v>
+        <v>431</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>231</v>
@@ -4743,7 +4894,7 @@
         <v>80</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>400</v>
+        <v>432</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>231</v>
@@ -4790,10 +4941,10 @@
         <v>144</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>401</v>
+        <v>433</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>296</v>
@@ -4840,10 +4991,10 @@
         <v>209</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>403</v>
+        <v>435</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>404</v>
+        <v>436</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>236</v>
@@ -4890,10 +5041,10 @@
         <v>74</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>405</v>
+        <v>437</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>406</v>
+        <v>438</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>231</v>
@@ -4940,10 +5091,10 @@
         <v>120</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>407</v>
+        <v>439</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>408</v>
+        <v>440</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>231</v>
@@ -4993,7 +5144,7 @@
         <v>173</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>409</v>
+        <v>441</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>276</v>
@@ -5040,10 +5191,10 @@
         <v>129</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>410</v>
+        <v>442</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>411</v>
+        <v>443</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>230</v>
@@ -5090,10 +5241,10 @@
         <v>174</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>413</v>
+        <v>445</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>231</v>
@@ -5140,10 +5291,10 @@
         <v>210</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>414</v>
+        <v>446</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>415</v>
+        <v>447</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>230</v>
@@ -5190,10 +5341,10 @@
         <v>131</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>416</v>
+        <v>448</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>417</v>
+        <v>449</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>231</v>
@@ -5240,10 +5391,10 @@
         <v>132</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>418</v>
+        <v>450</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>419</v>
+        <v>451</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>231</v>
@@ -5290,10 +5441,10 @@
         <v>107</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>420</v>
+        <v>452</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>421</v>
+        <v>453</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>236</v>
@@ -5340,10 +5491,10 @@
         <v>211</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>422</v>
+        <v>454</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>423</v>
+        <v>455</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>301</v>
@@ -5390,10 +5541,10 @@
         <v>213</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>424</v>
+        <v>456</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>425</v>
+        <v>457</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>230</v>
@@ -5440,10 +5591,10 @@
         <v>124</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>426</v>
+        <v>458</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>427</v>
+        <v>459</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>230</v>
@@ -5490,10 +5641,10 @@
         <v>134</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>428</v>
+        <v>460</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>429</v>
+        <v>461</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>277</v>
@@ -5540,10 +5691,10 @@
         <v>163</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>430</v>
+        <v>462</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>431</v>
+        <v>463</v>
       </c>
       <c r="D48" s="10" t="s">
         <v>252</v>
@@ -5593,7 +5744,7 @@
         <v>155</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>432</v>
+        <v>464</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>231</v>
@@ -5643,7 +5794,7 @@
         <v>158</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>433</v>
+        <v>465</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>296</v>
@@ -5690,10 +5841,10 @@
         <v>136</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>434</v>
+        <v>466</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>435</v>
+        <v>467</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>246</v>
@@ -5740,10 +5891,10 @@
         <v>215</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>436</v>
+        <v>468</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>437</v>
+        <v>469</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>278</v>
@@ -5790,10 +5941,10 @@
         <v>139</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>438</v>
+        <v>470</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>439</v>
+        <v>471</v>
       </c>
       <c r="D53" s="10" t="s">
         <v>302</v>
@@ -5843,7 +5994,7 @@
         <v>110</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>440</v>
+        <v>472</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>241</v>
@@ -5890,10 +6041,10 @@
         <v>175</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>441</v>
+        <v>473</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>442</v>
+        <v>474</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>231</v>
@@ -5940,10 +6091,10 @@
         <v>141</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>443</v>
+        <v>475</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>444</v>
+        <v>476</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>241</v>
@@ -5990,10 +6141,10 @@
         <v>178</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>445</v>
+        <v>477</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>446</v>
+        <v>478</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>230</v>
@@ -6040,10 +6191,10 @@
         <v>149</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>447</v>
+        <v>479</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>448</v>
+        <v>480</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>241</v>
@@ -6090,10 +6241,10 @@
         <v>217</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>449</v>
+        <v>481</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>450</v>
+        <v>482</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>301</v>
@@ -6140,10 +6291,10 @@
         <v>180</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>451</v>
+        <v>483</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>452</v>
+        <v>484</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>230</v>
@@ -6190,10 +6341,10 @@
         <v>94</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>453</v>
+        <v>485</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>454</v>
+        <v>486</v>
       </c>
       <c r="D61" s="10" t="s">
         <v>230</v>
@@ -6240,10 +6391,10 @@
         <v>164</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>456</v>
+        <v>488</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>248</v>
@@ -6290,10 +6441,10 @@
         <v>183</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>457</v>
+        <v>489</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>458</v>
+        <v>490</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>247</v>
@@ -6340,10 +6491,10 @@
         <v>97</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>459</v>
+        <v>491</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>460</v>
+        <v>492</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>231</v>
@@ -6390,10 +6541,10 @@
         <v>185</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>462</v>
+        <v>494</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>250</v>
@@ -6440,10 +6591,10 @@
         <v>187</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>463</v>
+        <v>495</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>421</v>
+        <v>453</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>236</v>
@@ -6493,7 +6644,7 @@
         <v>219</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>464</v>
+        <v>496</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>295</v>
@@ -6540,10 +6691,10 @@
         <v>190</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>465</v>
+        <v>497</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>466</v>
+        <v>498</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>251</v>
@@ -6590,10 +6741,10 @@
         <v>193</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>467</v>
+        <v>499</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>468</v>
+        <v>500</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>252</v>
@@ -6640,10 +6791,10 @@
         <v>151</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>447</v>
+        <v>479</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>469</v>
+        <v>501</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>241</v>
@@ -6690,10 +6841,10 @@
         <v>167</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>470</v>
+        <v>502</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>471</v>
+        <v>503</v>
       </c>
       <c r="D71" s="10" t="s">
         <v>231</v>
@@ -6740,10 +6891,10 @@
         <v>121</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>472</v>
+        <v>504</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>473</v>
+        <v>505</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>236</v>
@@ -6790,10 +6941,10 @@
         <v>197</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>474</v>
+        <v>506</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>475</v>
+        <v>507</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>252</v>
@@ -6840,10 +6991,10 @@
         <v>195</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>476</v>
+        <v>508</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>477</v>
+        <v>509</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>252</v>
@@ -6890,10 +7041,10 @@
         <v>200</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>478</v>
+        <v>510</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>479</v>
+        <v>511</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>231</v>
@@ -6943,7 +7094,7 @@
         <v>152</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>480</v>
+        <v>512</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>296</v>
@@ -6993,7 +7144,7 @@
         <v>305</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>481</v>
+        <v>513</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>296</v>
@@ -7036,10 +7187,10 @@
         <v>281</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>482</v>
+        <v>514</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>483</v>
+        <v>515</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>270</v>
@@ -7085,7 +7236,7 @@
         <v>306</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="D79" s="10" t="s">
         <v>296</v>
@@ -7128,10 +7279,10 @@
         <v>283</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>485</v>
+        <v>517</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>486</v>
+        <v>518</v>
       </c>
       <c r="D80" s="10" t="s">
         <v>276</v>
@@ -7174,10 +7325,10 @@
         <v>307</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>487</v>
+        <v>519</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>488</v>
+        <v>520</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>308</v>
@@ -7220,10 +7371,10 @@
         <v>284</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>489</v>
+        <v>521</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>490</v>
+        <v>522</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>285</v>
@@ -7269,7 +7420,7 @@
         <v>309</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>491</v>
+        <v>523</v>
       </c>
       <c r="D83" s="10" t="s">
         <v>310</v>
@@ -7312,10 +7463,10 @@
         <v>286</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>492</v>
+        <v>524</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
       <c r="D84" s="10" t="s">
         <v>248</v>
@@ -7358,10 +7509,10 @@
         <v>311</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>494</v>
+        <v>526</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>495</v>
+        <v>527</v>
       </c>
       <c r="D85" s="10" t="s">
         <v>300</v>
@@ -7404,10 +7555,10 @@
         <v>287</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>496</v>
+        <v>528</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>497</v>
+        <v>529</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>230</v>
@@ -7450,10 +7601,10 @@
         <v>312</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>498</v>
+        <v>530</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>499</v>
+        <v>531</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>313</v>
@@ -7496,10 +7647,10 @@
         <v>314</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>500</v>
+        <v>532</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>501</v>
+        <v>533</v>
       </c>
       <c r="D88" s="10" t="s">
         <v>240</v>
@@ -7542,10 +7693,10 @@
         <v>315</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>502</v>
+        <v>534</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>503</v>
+        <v>535</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>296</v>
@@ -7588,10 +7739,10 @@
         <v>152</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>504</v>
+        <v>536</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>505</v>
+        <v>537</v>
       </c>
       <c r="D90" s="10" t="s">
         <v>296</v>
@@ -7634,10 +7785,10 @@
         <v>288</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>506</v>
+        <v>538</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>507</v>
+        <v>539</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>276</v>
@@ -7680,10 +7831,10 @@
         <v>316</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>508</v>
+        <v>540</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>509</v>
+        <v>541</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>296</v>
@@ -7726,10 +7877,10 @@
         <v>317</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>510</v>
+        <v>542</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>511</v>
+        <v>543</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>313</v>
@@ -7772,10 +7923,10 @@
         <v>318</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>512</v>
+        <v>544</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>513</v>
+        <v>545</v>
       </c>
       <c r="D94" s="10" t="s">
         <v>319</v>
@@ -7818,10 +7969,10 @@
         <v>320</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>514</v>
+        <v>546</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>515</v>
+        <v>547</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>296</v>
@@ -7864,10 +8015,10 @@
         <v>289</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>516</v>
+        <v>548</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>517</v>
+        <v>549</v>
       </c>
       <c r="D96" s="10" t="s">
         <v>236</v>
@@ -7910,10 +8061,10 @@
         <v>321</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>519</v>
+        <v>551</v>
       </c>
       <c r="D97" s="10" t="s">
         <v>230</v>
@@ -7956,10 +8107,10 @@
         <v>290</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>520</v>
+        <v>552</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>521</v>
+        <v>553</v>
       </c>
       <c r="D98" s="10" t="s">
         <v>252</v>
@@ -8002,10 +8153,10 @@
         <v>291</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>522</v>
+        <v>554</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>523</v>
+        <v>555</v>
       </c>
       <c r="D99" s="10" t="s">
         <v>236</v>
@@ -8048,10 +8199,10 @@
         <v>322</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>524</v>
+        <v>556</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>525</v>
+        <v>557</v>
       </c>
       <c r="D100" s="10" t="s">
         <v>296</v>
@@ -8094,10 +8245,10 @@
         <v>292</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>526</v>
+        <v>558</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>527</v>
+        <v>559</v>
       </c>
       <c r="D101" s="10" t="s">
         <v>231</v>
@@ -8140,10 +8291,10 @@
         <v>293</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>528</v>
+        <v>560</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>529</v>
+        <v>561</v>
       </c>
       <c r="D102" s="10" t="s">
         <v>251</v>
@@ -8186,10 +8337,10 @@
         <v>323</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>530</v>
+        <v>562</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>531</v>
+        <v>563</v>
       </c>
       <c r="D103" s="10" t="s">
         <v>324</v>
@@ -8232,10 +8383,10 @@
         <v>325</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>532</v>
+        <v>564</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>533</v>
+        <v>565</v>
       </c>
       <c r="D104" s="10" t="s">
         <v>308</v>
@@ -8278,10 +8429,10 @@
         <v>326</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>534</v>
+        <v>566</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>535</v>
+        <v>567</v>
       </c>
       <c r="D105" s="10" t="s">
         <v>302</v>
@@ -8324,10 +8475,10 @@
         <v>327</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>536</v>
+        <v>568</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>537</v>
+        <v>569</v>
       </c>
       <c r="D106" s="10" t="s">
         <v>240</v>
@@ -8370,10 +8521,10 @@
         <v>328</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>538</v>
+        <v>570</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>539</v>
+        <v>571</v>
       </c>
       <c r="D107" s="10" t="s">
         <v>329</v>
@@ -8416,10 +8567,10 @@
         <v>330</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>540</v>
+        <v>572</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>541</v>
+        <v>573</v>
       </c>
       <c r="D108" s="10" t="s">
         <v>246</v>
@@ -8473,7 +8624,7 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="29" t="s">
-        <v>542</v>
+        <v>574</v>
       </c>
       <c r="C2" s="29"/>
       <c r="D2" s="29"/>
@@ -8483,208 +8634,208 @@
       <c r="H2" s="29"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="50" t="s">
-        <v>543</v>
-      </c>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
+      <c r="B4" s="61" t="s">
+        <v>575</v>
+      </c>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="51" t="s">
-        <v>544</v>
-      </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
+      <c r="B5" s="62" t="s">
+        <v>576</v>
+      </c>
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="51" t="s">
-        <v>545</v>
-      </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
+      <c r="B6" s="62" t="s">
+        <v>577</v>
+      </c>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="51" t="s">
+      <c r="B7" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="51"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="51" t="s">
-        <v>546</v>
-      </c>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
+      <c r="B8" s="62" t="s">
+        <v>578</v>
+      </c>
+      <c r="C8" s="62"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="62"/>
+      <c r="I8" s="62"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="51" t="s">
-        <v>547</v>
-      </c>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
+      <c r="B9" s="62" t="s">
+        <v>579</v>
+      </c>
+      <c r="C9" s="62"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="62"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="51"/>
-      <c r="F10" s="51"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="62"/>
+      <c r="I10" s="62"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="50" t="s">
-        <v>548</v>
-      </c>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
+      <c r="B11" s="61" t="s">
+        <v>580</v>
+      </c>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="51" t="s">
-        <v>549</v>
-      </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
+      <c r="B12" s="62" t="s">
+        <v>581</v>
+      </c>
+      <c r="C12" s="62"/>
+      <c r="D12" s="62"/>
+      <c r="E12" s="62"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="62"/>
+      <c r="H12" s="62"/>
+      <c r="I12" s="62"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="51" t="s">
-        <v>550</v>
-      </c>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
+      <c r="B13" s="62" t="s">
+        <v>582</v>
+      </c>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
+      <c r="G13" s="62"/>
+      <c r="H13" s="62"/>
+      <c r="I13" s="62"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="51" t="s">
-        <v>551</v>
-      </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
+      <c r="B14" s="62" t="s">
+        <v>583</v>
+      </c>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="51" t="s">
-        <v>552</v>
-      </c>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="51"/>
+      <c r="B15" s="62" t="s">
+        <v>584</v>
+      </c>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="51" t="s">
-        <v>553</v>
-      </c>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
+      <c r="B16" s="62" t="s">
+        <v>585</v>
+      </c>
+      <c r="C16" s="62"/>
+      <c r="D16" s="62"/>
+      <c r="E16" s="62"/>
+      <c r="F16" s="62"/>
+      <c r="G16" s="62"/>
+      <c r="H16" s="62"/>
+      <c r="I16" s="62"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="51" t="s">
-        <v>554</v>
-      </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="51"/>
+      <c r="B17" s="62" t="s">
+        <v>586</v>
+      </c>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="62"/>
+      <c r="H17" s="62"/>
+      <c r="I17" s="62"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="51" t="s">
-        <v>555</v>
-      </c>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
+      <c r="B18" s="62" t="s">
+        <v>587</v>
+      </c>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="62"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="62"/>
+      <c r="I18" s="62"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="51" t="s">
-        <v>556</v>
-      </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51"/>
+      <c r="B19" s="62" t="s">
+        <v>588</v>
+      </c>
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="62"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="51" t="s">
-        <v>557</v>
-      </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51"/>
+      <c r="B20" s="62" t="s">
+        <v>589</v>
+      </c>
+      <c r="C20" s="62"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -18293,13 +18444,18 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I7"/>
+  <dimension ref="B2:I109"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="5" width="14" customWidth="1"/>
+    <col min="6" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="29" t="s">
         <v>332</v>
       </c>
@@ -18309,88 +18465,1902 @@
       <c r="F2" s="29"/>
       <c r="G2" s="29"/>
       <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B3" s="50" t="s">
+        <v>333</v>
+      </c>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="6">
+        <v>75</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6">
+        <v>2</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6">
+        <v>14</v>
+      </c>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6">
+        <v>16</v>
+      </c>
+      <c r="I6" s="6"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="51" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="C13" s="46">
+        <v>4</v>
+      </c>
+      <c r="D13" s="46">
+        <v>0</v>
+      </c>
+      <c r="E13" s="52">
+        <v>4</v>
+      </c>
+      <c r="F13" s="53" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="C14" s="46">
+        <v>3</v>
+      </c>
+      <c r="D14" s="46">
+        <v>3</v>
+      </c>
+      <c r="E14" s="52">
+        <v>6</v>
+      </c>
+      <c r="F14" s="54" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="C15" s="46">
+        <v>9</v>
+      </c>
+      <c r="D15" s="46">
+        <v>3</v>
+      </c>
+      <c r="E15" s="52">
+        <v>12</v>
+      </c>
+      <c r="F15" s="54" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="C16" s="46">
+        <v>8</v>
+      </c>
+      <c r="D16" s="46">
+        <v>8</v>
+      </c>
+      <c r="E16" s="52">
+        <v>16</v>
+      </c>
+      <c r="F16" s="54" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="C17" s="46">
+        <v>3</v>
+      </c>
+      <c r="D17" s="46">
+        <v>5</v>
+      </c>
+      <c r="E17" s="52">
+        <v>8</v>
+      </c>
+      <c r="F17" s="55" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C18" s="46">
+        <v>0</v>
+      </c>
+      <c r="D18" s="46">
+        <v>6</v>
+      </c>
+      <c r="E18" s="52">
+        <v>6</v>
+      </c>
+      <c r="F18" s="55" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="C19" s="46">
+        <v>4</v>
+      </c>
+      <c r="D19" s="46">
+        <v>3</v>
+      </c>
+      <c r="E19" s="52">
+        <v>7</v>
+      </c>
+      <c r="F19" s="54" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C20" s="46">
+        <v>7</v>
+      </c>
+      <c r="D20" s="46">
+        <v>7</v>
+      </c>
+      <c r="E20" s="52">
+        <v>14</v>
+      </c>
+      <c r="F20" s="54" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="C21" s="46">
+        <v>1</v>
+      </c>
+      <c r="D21" s="46">
+        <v>1</v>
+      </c>
+      <c r="E21" s="52">
+        <v>2</v>
+      </c>
+      <c r="F21" s="55" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="56" t="s">
+        <v>361</v>
+      </c>
+      <c r="C22" s="57">
+        <v>39</v>
+      </c>
+      <c r="D22" s="57">
+        <v>36</v>
+      </c>
+      <c r="E22" s="57">
+        <v>75</v>
+      </c>
+      <c r="F22" s="58" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B25" s="59" t="s">
+        <v>362</v>
+      </c>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="59"/>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B27" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C27" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D27" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E27" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F27" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G27" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H27" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I27" s="9" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="10" t="s">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B28" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C28" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="D6" s="49" t="s">
+      <c r="D28" s="49" t="s">
         <v>251</v>
       </c>
-      <c r="E6" s="49" t="s">
+      <c r="E28" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="F6" s="46">
-        <v>1</v>
-      </c>
-      <c r="G6" s="46">
-        <v>1</v>
-      </c>
-      <c r="H6" s="47">
+      <c r="F28" s="46">
+        <v>1</v>
+      </c>
+      <c r="G28" s="46">
+        <v>1</v>
+      </c>
+      <c r="H28" s="47">
         <v>675</v>
       </c>
-      <c r="I6" s="49" t="s">
+      <c r="I28" s="49" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="10" t="s">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B29" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C29" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="D7" s="49" t="s">
+      <c r="D29" s="49" t="s">
         <v>241</v>
       </c>
-      <c r="E7" s="49" t="s">
+      <c r="E29" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="F7" s="46">
-        <v>1</v>
-      </c>
-      <c r="G7" s="46">
-        <v>1</v>
-      </c>
-      <c r="H7" s="47">
-        <v>0</v>
-      </c>
-      <c r="I7" s="49" t="s">
+      <c r="F29" s="46">
+        <v>1</v>
+      </c>
+      <c r="G29" s="46">
+        <v>1</v>
+      </c>
+      <c r="H29" s="47">
+        <v>0</v>
+      </c>
+      <c r="I29" s="49" t="s">
         <v>269</v>
       </c>
     </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B32" s="59" t="s">
+        <v>363</v>
+      </c>
+      <c r="C32" s="59"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="59"/>
+      <c r="H32" s="59"/>
+      <c r="I32" s="59"/>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B35" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="E35" s="46">
+        <v>1</v>
+      </c>
+      <c r="F35" s="46">
+        <v>1</v>
+      </c>
+      <c r="G35" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B36" s="60" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="E36" s="46">
+        <v>1</v>
+      </c>
+      <c r="F36" s="46">
+        <v>1</v>
+      </c>
+      <c r="G36" s="47">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B37" s="60" t="s">
+        <v>205</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="E37" s="46">
+        <v>1</v>
+      </c>
+      <c r="F37" s="46">
+        <v>1</v>
+      </c>
+      <c r="G37" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B38" s="60" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="E38" s="46">
+        <v>1</v>
+      </c>
+      <c r="F38" s="46">
+        <v>1</v>
+      </c>
+      <c r="G38" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="60" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="E39" s="46">
+        <v>1</v>
+      </c>
+      <c r="F39" s="46">
+        <v>1</v>
+      </c>
+      <c r="G39" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="60" t="s">
+        <v>127</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="E40" s="46">
+        <v>1</v>
+      </c>
+      <c r="F40" s="46">
+        <v>1</v>
+      </c>
+      <c r="G40" s="47">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E41" s="46">
+        <v>2</v>
+      </c>
+      <c r="F41" s="46">
+        <v>10</v>
+      </c>
+      <c r="G41" s="47">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="E42" s="46">
+        <v>1</v>
+      </c>
+      <c r="F42" s="46">
+        <v>1</v>
+      </c>
+      <c r="G42" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B43" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E43" s="46">
+        <v>3</v>
+      </c>
+      <c r="F43" s="46">
+        <v>7</v>
+      </c>
+      <c r="G43" s="47">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B44" s="60" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="E44" s="46">
+        <v>2</v>
+      </c>
+      <c r="F44" s="46">
+        <v>2</v>
+      </c>
+      <c r="G44" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B45" s="60" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="E45" s="46">
+        <v>1</v>
+      </c>
+      <c r="F45" s="46">
+        <v>1</v>
+      </c>
+      <c r="G45" s="47">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B46" s="60" t="s">
+        <v>130</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E46" s="46">
+        <v>2</v>
+      </c>
+      <c r="F46" s="46">
+        <v>10</v>
+      </c>
+      <c r="G46" s="47">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B47" s="60" t="s">
+        <v>130</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="E47" s="46">
+        <v>1</v>
+      </c>
+      <c r="F47" s="46">
+        <v>1</v>
+      </c>
+      <c r="G47" s="47">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B48" s="60" t="s">
+        <v>130</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="E48" s="46">
+        <v>1</v>
+      </c>
+      <c r="F48" s="46">
+        <v>2</v>
+      </c>
+      <c r="G48" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B49" s="60" t="s">
+        <v>108</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="E49" s="46">
+        <v>2</v>
+      </c>
+      <c r="F49" s="46">
+        <v>10</v>
+      </c>
+      <c r="G49" s="47">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="60" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="E50" s="46">
+        <v>2</v>
+      </c>
+      <c r="F50" s="46">
+        <v>10</v>
+      </c>
+      <c r="G50" s="47">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="60" t="s">
+        <v>212</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E51" s="46">
+        <v>1</v>
+      </c>
+      <c r="F51" s="46">
+        <v>1</v>
+      </c>
+      <c r="G51" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="E52" s="46">
+        <v>1</v>
+      </c>
+      <c r="F52" s="46">
+        <v>1</v>
+      </c>
+      <c r="G52" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B53" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E53" s="46">
+        <v>2</v>
+      </c>
+      <c r="F53" s="46">
+        <v>10</v>
+      </c>
+      <c r="G53" s="47">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B54" s="60" t="s">
+        <v>156</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="E54" s="46">
+        <v>1</v>
+      </c>
+      <c r="F54" s="46">
+        <v>2</v>
+      </c>
+      <c r="G54" s="47">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B55" s="60" t="s">
+        <v>216</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="E55" s="46">
+        <v>1</v>
+      </c>
+      <c r="F55" s="46">
+        <v>2</v>
+      </c>
+      <c r="G55" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B56" s="60" t="s">
+        <v>140</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E56" s="46">
+        <v>2</v>
+      </c>
+      <c r="F56" s="46">
+        <v>10</v>
+      </c>
+      <c r="G56" s="47">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B57" s="60" t="s">
+        <v>176</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="E57" s="46">
+        <v>1</v>
+      </c>
+      <c r="F57" s="46">
+        <v>1</v>
+      </c>
+      <c r="G57" s="47">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B58" s="60" t="s">
+        <v>304</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="E58" s="46">
+        <v>3</v>
+      </c>
+      <c r="F58" s="46">
+        <v>9</v>
+      </c>
+      <c r="G58" s="47">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B59" s="60" t="s">
+        <v>106</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E59" s="46">
+        <v>3</v>
+      </c>
+      <c r="F59" s="46">
+        <v>11</v>
+      </c>
+      <c r="G59" s="47">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B60" s="60" t="s">
+        <v>106</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="E60" s="46">
+        <v>3</v>
+      </c>
+      <c r="F60" s="46">
+        <v>5</v>
+      </c>
+      <c r="G60" s="47">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B61" s="60" t="s">
+        <v>157</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="E61" s="46">
+        <v>4</v>
+      </c>
+      <c r="F61" s="46">
+        <v>8</v>
+      </c>
+      <c r="G61" s="47">
+        <v>3725</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B62" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="E62" s="46">
+        <v>1</v>
+      </c>
+      <c r="F62" s="46">
+        <v>1</v>
+      </c>
+      <c r="G62" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B63" s="60" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="E63" s="46">
+        <v>4</v>
+      </c>
+      <c r="F63" s="46">
+        <v>4</v>
+      </c>
+      <c r="G63" s="47">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B64" s="60" t="s">
+        <v>95</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="E64" s="46">
+        <v>2</v>
+      </c>
+      <c r="F64" s="46">
+        <v>2</v>
+      </c>
+      <c r="G64" s="47">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B65" s="60" t="s">
+        <v>165</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="E65" s="46">
+        <v>1</v>
+      </c>
+      <c r="F65" s="46">
+        <v>2</v>
+      </c>
+      <c r="G65" s="47">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B66" s="60" t="s">
+        <v>184</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="E66" s="46">
+        <v>1</v>
+      </c>
+      <c r="F66" s="46">
+        <v>1</v>
+      </c>
+      <c r="G66" s="47">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B67" s="60" t="s">
+        <v>98</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E67" s="46">
+        <v>4</v>
+      </c>
+      <c r="F67" s="46">
+        <v>18</v>
+      </c>
+      <c r="G67" s="47">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B68" s="60" t="s">
+        <v>189</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="E68" s="46">
+        <v>5</v>
+      </c>
+      <c r="F68" s="46">
+        <v>13</v>
+      </c>
+      <c r="G68" s="47">
+        <v>6075</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B69" s="60" t="s">
+        <v>189</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="E69" s="46">
+        <v>5</v>
+      </c>
+      <c r="F69" s="46">
+        <v>10</v>
+      </c>
+      <c r="G69" s="47">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B70" s="60" t="s">
+        <v>189</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="E70" s="46">
+        <v>2</v>
+      </c>
+      <c r="F70" s="46">
+        <v>2</v>
+      </c>
+      <c r="G70" s="47">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B71" s="60" t="s">
+        <v>249</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E71" s="46">
+        <v>3</v>
+      </c>
+      <c r="F71" s="46">
+        <v>4</v>
+      </c>
+      <c r="G71" s="47">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B72" s="60" t="s">
+        <v>186</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="E72" s="46">
+        <v>1</v>
+      </c>
+      <c r="F72" s="46">
+        <v>1</v>
+      </c>
+      <c r="G72" s="47">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B73" s="60" t="s">
+        <v>188</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E73" s="46">
+        <v>1</v>
+      </c>
+      <c r="F73" s="46">
+        <v>1</v>
+      </c>
+      <c r="G73" s="47">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B74" s="60" t="s">
+        <v>235</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="E74" s="46">
+        <v>7</v>
+      </c>
+      <c r="F74" s="46">
+        <v>35</v>
+      </c>
+      <c r="G74" s="47">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B75" s="60" t="s">
+        <v>191</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="E75" s="46">
+        <v>2</v>
+      </c>
+      <c r="F75" s="46">
+        <v>2</v>
+      </c>
+      <c r="G75" s="47">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B76" s="60" t="s">
+        <v>191</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="E76" s="46">
+        <v>1</v>
+      </c>
+      <c r="F76" s="46">
+        <v>1</v>
+      </c>
+      <c r="G76" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B77" s="60" t="s">
+        <v>191</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E77" s="46">
+        <v>1</v>
+      </c>
+      <c r="F77" s="46">
+        <v>1</v>
+      </c>
+      <c r="G77" s="47">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B78" s="60" t="s">
+        <v>299</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E78" s="46">
+        <v>11</v>
+      </c>
+      <c r="F78" s="46">
+        <v>25</v>
+      </c>
+      <c r="G78" s="47">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B79" s="60" t="s">
+        <v>237</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E79" s="46">
+        <v>8</v>
+      </c>
+      <c r="F79" s="46">
+        <v>22</v>
+      </c>
+      <c r="G79" s="47">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B80" s="60" t="s">
+        <v>297</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E80" s="46">
+        <v>4</v>
+      </c>
+      <c r="F80" s="46">
+        <v>23</v>
+      </c>
+      <c r="G80" s="47">
+        <v>12600</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B81" s="60" t="s">
+        <v>194</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="E81" s="46">
+        <v>1</v>
+      </c>
+      <c r="F81" s="46">
+        <v>1</v>
+      </c>
+      <c r="G81" s="47">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B82" s="60" t="s">
+        <v>123</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E82" s="46">
+        <v>4</v>
+      </c>
+      <c r="F82" s="46">
+        <v>5</v>
+      </c>
+      <c r="G82" s="47">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B83" s="60" t="s">
+        <v>123</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="E83" s="46">
+        <v>6</v>
+      </c>
+      <c r="F83" s="46">
+        <v>12</v>
+      </c>
+      <c r="G83" s="47">
+        <v>7350</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B84" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="E84" s="46">
+        <v>2</v>
+      </c>
+      <c r="F84" s="46">
+        <v>5</v>
+      </c>
+      <c r="G84" s="47">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B85" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D85" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="E85" s="46">
+        <v>1</v>
+      </c>
+      <c r="F85" s="46">
+        <v>4</v>
+      </c>
+      <c r="G85" s="47">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B86" s="60" t="s">
+        <v>303</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D86" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E86" s="46">
+        <v>6</v>
+      </c>
+      <c r="F86" s="46">
+        <v>14</v>
+      </c>
+      <c r="G86" s="47">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B87" s="60" t="s">
+        <v>138</v>
+      </c>
+      <c r="C87" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E87" s="46">
+        <v>2</v>
+      </c>
+      <c r="F87" s="46">
+        <v>4</v>
+      </c>
+      <c r="G87" s="47">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B88" s="60" t="s">
+        <v>280</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D88" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E88" s="46">
+        <v>2</v>
+      </c>
+      <c r="F88" s="46">
+        <v>2</v>
+      </c>
+      <c r="G88" s="47">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B89" s="60" t="s">
+        <v>202</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="E89" s="46">
+        <v>2</v>
+      </c>
+      <c r="F89" s="46">
+        <v>10</v>
+      </c>
+      <c r="G89" s="47">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B90" s="60" t="s">
+        <v>239</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E90" s="46">
+        <v>3</v>
+      </c>
+      <c r="F90" s="46">
+        <v>18</v>
+      </c>
+      <c r="G90" s="47">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B91" s="60" t="s">
+        <v>238</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E91" s="46">
+        <v>2</v>
+      </c>
+      <c r="F91" s="46">
+        <v>6</v>
+      </c>
+      <c r="G91" s="47">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B92" s="60" t="s">
+        <v>238</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E92" s="46">
+        <v>4</v>
+      </c>
+      <c r="F92" s="46">
+        <v>17</v>
+      </c>
+      <c r="G92" s="47">
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B93" s="60" t="s">
+        <v>122</v>
+      </c>
+      <c r="C93" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="E93" s="46">
+        <v>2</v>
+      </c>
+      <c r="F93" s="46">
+        <v>10</v>
+      </c>
+      <c r="G93" s="47">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B94" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E94" s="46">
+        <v>5</v>
+      </c>
+      <c r="F94" s="46">
+        <v>41</v>
+      </c>
+      <c r="G94" s="47">
+        <v>21900</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B95" s="60" t="s">
+        <v>198</v>
+      </c>
+      <c r="C95" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D95" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="E95" s="46">
+        <v>1</v>
+      </c>
+      <c r="F95" s="46">
+        <v>1</v>
+      </c>
+      <c r="G95" s="47">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B96" s="60" t="s">
+        <v>196</v>
+      </c>
+      <c r="C96" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="E96" s="46">
+        <v>1</v>
+      </c>
+      <c r="F96" s="46">
+        <v>1</v>
+      </c>
+      <c r="G96" s="47">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B97" s="60" t="s">
+        <v>275</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D97" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E97" s="46">
+        <v>3</v>
+      </c>
+      <c r="F97" s="46">
+        <v>12</v>
+      </c>
+      <c r="G97" s="47">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B98" s="60" t="s">
+        <v>274</v>
+      </c>
+      <c r="C98" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E98" s="46">
+        <v>6</v>
+      </c>
+      <c r="F98" s="46">
+        <v>12</v>
+      </c>
+      <c r="G98" s="47">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B99" s="60" t="s">
+        <v>201</v>
+      </c>
+      <c r="C99" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D99" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="E99" s="46">
+        <v>1</v>
+      </c>
+      <c r="F99" s="46">
+        <v>1</v>
+      </c>
+      <c r="G99" s="47">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B100" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="C100" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D100" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E100" s="46">
+        <v>8</v>
+      </c>
+      <c r="F100" s="46">
+        <v>19</v>
+      </c>
+      <c r="G100" s="47">
+        <v>9300</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B101" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="C101" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D101" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E101" s="46">
+        <v>8</v>
+      </c>
+      <c r="F101" s="46">
+        <v>64</v>
+      </c>
+      <c r="G101" s="47">
+        <v>37200</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B102" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="C102" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D102" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="E102" s="46">
+        <v>1</v>
+      </c>
+      <c r="F102" s="46">
+        <v>4</v>
+      </c>
+      <c r="G102" s="47">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B103" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="C103" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D103" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E103" s="46">
+        <v>6</v>
+      </c>
+      <c r="F103" s="46">
+        <v>43</v>
+      </c>
+      <c r="G103" s="47">
+        <v>25050</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B104" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D104" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E104" s="46">
+        <v>6</v>
+      </c>
+      <c r="F104" s="46">
+        <v>24</v>
+      </c>
+      <c r="G104" s="47">
+        <v>12700</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B105" s="60" t="s">
+        <v>298</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D105" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E105" s="46">
+        <v>4</v>
+      </c>
+      <c r="F105" s="46">
+        <v>17</v>
+      </c>
+      <c r="G105" s="47">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B106" s="60" t="s">
+        <v>273</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D106" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="E106" s="46">
+        <v>4</v>
+      </c>
+      <c r="F106" s="46">
+        <v>12</v>
+      </c>
+      <c r="G106" s="47">
+        <v>6655</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B107" s="60" t="s">
+        <v>272</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="E107" s="46">
+        <v>4</v>
+      </c>
+      <c r="F107" s="46">
+        <v>7</v>
+      </c>
+      <c r="G107" s="47">
+        <v>5680</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B108" s="60" t="s">
+        <v>272</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D108" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E108" s="46">
+        <v>16</v>
+      </c>
+      <c r="F108" s="46">
+        <v>45</v>
+      </c>
+      <c r="G108" s="47">
+        <v>22300</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B109" s="60" t="s">
+        <v>234</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D109" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E109" s="46">
+        <v>15</v>
+      </c>
+      <c r="F109" s="46">
+        <v>34</v>
+      </c>
+      <c r="G109" s="47">
+        <v>19200</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:H2"/>
+  <mergeCells count="13">
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="D6:E7"/>
+    <mergeCell ref="F6:G7"/>
+    <mergeCell ref="H6:I7"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B32:I32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -18411,7 +20381,7 @@
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="29" t="s">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="C2" s="29"/>
       <c r="D2" s="29"/>
@@ -18423,7 +20393,7 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -18447,13 +20417,13 @@
         <v>9</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>335</v>
+        <v>367</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>62</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>68</v>
@@ -18869,7 +20839,7 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="29" t="s">
-        <v>337</v>
+        <v>369</v>
       </c>
       <c r="C2" s="29"/>
       <c r="D2" s="29"/>
@@ -18892,7 +20862,7 @@
         <v>267</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>68</v>

--- a/activity/WEEKLY_RECAP_REP.xlsx
+++ b/activity/WEEKLY_RECAP_REP.xlsx
@@ -95,10 +95,10 @@
     <t>monthly reset</t>
   </si>
   <si>
-    <t>−73%</t>
-  </si>
-  <si>
-    <t>+456%</t>
+    <t>−93%</t>
+  </si>
+  <si>
+    <t>−53%</t>
   </si>
   <si>
     <t>—</t>
@@ -107,28 +107,28 @@
     <t>+$3,675 wk/wk</t>
   </si>
   <si>
-    <t>−$1,600 wk/wk</t>
-  </si>
-  <si>
-    <t>+$2,075 wk/wk</t>
-  </si>
-  <si>
-    <t>+$22,200 wk/wk</t>
-  </si>
-  <si>
-    <t>+$9,050 wk/wk</t>
-  </si>
-  <si>
-    <t>+$31,250 wk/wk</t>
-  </si>
-  <si>
-    <t>−20%</t>
+    <t>+$3,725 wk/wk</t>
+  </si>
+  <si>
+    <t>+$7,400 wk/wk</t>
+  </si>
+  <si>
+    <t>+$21,000 wk/wk</t>
+  </si>
+  <si>
+    <t>+$13,850 wk/wk</t>
+  </si>
+  <si>
+    <t>+$34,850 wk/wk</t>
+  </si>
+  <si>
+    <t>−80%</t>
   </si>
   <si>
     <t>MTD Vials</t>
   </si>
   <si>
-    <t>−36%</t>
+    <t>−87%</t>
   </si>
   <si>
     <t xml:space="preserve">  → Paid Vials</t>
@@ -1885,14 +1885,14 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="B0AEA8"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="4E9F3D"/>
       <sz val="9"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="B0AEA8"/>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -2106,13 +2106,13 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2621,19 +2621,19 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
-        <v>5600</v>
+        <v>7400</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4">
-        <v>30050</v>
+        <v>34850</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4">
-        <v>5224</v>
+        <v>7024</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="5">
-        <v>0.9328571428571428</v>
+        <v>0.9491891891891892</v>
       </c>
       <c r="I7" s="5"/>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" s="6"/>
       <c r="H10" s="4">
@@ -2783,13 +2783,13 @@
         <v>3675</v>
       </c>
       <c r="D20" s="11">
-        <v>1925</v>
+        <v>3725</v>
       </c>
       <c r="E20" s="12">
-        <v>5600</v>
+        <v>7400</v>
       </c>
       <c r="F20" s="13">
-        <v>21000</v>
+        <v>109650</v>
       </c>
       <c r="G20" s="13">
         <v>109650</v>
@@ -2823,13 +2823,13 @@
         <v>21000</v>
       </c>
       <c r="D22" s="11">
-        <v>9050</v>
+        <v>13850</v>
       </c>
       <c r="E22" s="12">
-        <v>30050</v>
+        <v>34850</v>
       </c>
       <c r="F22" s="13">
-        <v>5400</v>
+        <v>73500</v>
       </c>
       <c r="G22" s="13">
         <v>73500</v>
@@ -2848,7 +2848,7 @@
       <c r="E23" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="F23" s="19" t="s">
+      <c r="F23" s="17" t="s">
         <v>25</v>
       </c>
       <c r="G23" s="18" t="s">
@@ -2868,10 +2868,10 @@
       <c r="E24" s="12">
         <v>360385</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="F24" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G24" s="20" t="s">
+      <c r="G24" s="19" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2879,10 +2879,10 @@
       <c r="B25" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="20" t="s">
         <v>28</v>
       </c>
       <c r="E25" s="21" t="s">
@@ -2908,10 +2908,10 @@
       <c r="E26" s="12">
         <v>323110</v>
       </c>
-      <c r="F26" s="20" t="s">
+      <c r="F26" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G26" s="20" t="s">
+      <c r="G26" s="19" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2919,10 +2919,10 @@
       <c r="B27" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="20" t="s">
         <v>31</v>
       </c>
       <c r="E27" s="21" t="s">
@@ -2943,13 +2943,13 @@
         <v>8</v>
       </c>
       <c r="D28" s="23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F28" s="25">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="G28" s="25">
         <v>65</v>
@@ -2983,16 +2983,16 @@
         <v>19</v>
       </c>
       <c r="D30" s="23">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E30" s="24">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F30" s="25">
-        <v>45</v>
+        <v>246</v>
       </c>
       <c r="G30" s="25">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="31" ht="14" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -3020,18 +3020,18 @@
         <v>36</v>
       </c>
       <c r="C32" s="23">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D32" s="23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E32" s="24">
+        <v>14</v>
+      </c>
+      <c r="F32" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="F32" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="20" t="s">
+      <c r="G32" s="19" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3060,18 +3060,18 @@
         <v>37</v>
       </c>
       <c r="C34" s="23">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D34" s="23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E34" s="24">
-        <v>3</v>
-      </c>
-      <c r="F34" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G34" s="20" t="s">
+      <c r="G34" s="19" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3108,10 +3108,10 @@
       <c r="E36" s="24">
         <v>2</v>
       </c>
-      <c r="F36" s="20" t="s">
+      <c r="F36" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G36" s="20" t="s">
+      <c r="G36" s="19" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3159,16 +3159,16 @@
       <c r="B39" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="20" t="s">
         <v>40</v>
       </c>
       <c r="E39" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="F39" s="19" t="s">
+      <c r="F39" s="20" t="s">
         <v>42</v>
       </c>
       <c r="G39" s="18" t="s">
@@ -3199,16 +3199,16 @@
       <c r="B41" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="C41" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="19" t="s">
+      <c r="D41" s="20" t="s">
         <v>45</v>
       </c>
       <c r="E41" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="F41" s="19" t="s">
+      <c r="F41" s="20" t="s">
         <v>47</v>
       </c>
       <c r="G41" s="18" t="s">
@@ -3228,10 +3228,10 @@
       <c r="E42" s="24">
         <v>57</v>
       </c>
-      <c r="F42" s="20" t="s">
+      <c r="F42" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G42" s="20" t="s">
+      <c r="G42" s="19" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       <c r="B43" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C43" s="19" t="s">
+      <c r="C43" s="20" t="s">
         <v>49</v>
       </c>
       <c r="D43" s="15" t="s">
@@ -3268,10 +3268,10 @@
       <c r="E44" s="24">
         <v>107</v>
       </c>
-      <c r="F44" s="20" t="s">
+      <c r="F44" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G44" s="20" t="s">
+      <c r="G44" s="19" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
       <c r="B45" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C45" s="19" t="s">
+      <c r="C45" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="D45" s="19" t="s">
+      <c r="D45" s="20" t="s">
         <v>49</v>
       </c>
       <c r="E45" s="21" t="s">
@@ -15881,19 +15881,19 @@
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="4">
-        <v>1925</v>
+        <v>3725</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>9050</v>
+        <v>13850</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4">
-        <v>1757</v>
+        <v>3557</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="5">
-        <v>0.9127272727272727</v>
+        <v>0.9548993288590604</v>
       </c>
       <c r="I6" s="5"/>
     </row>
@@ -15939,11 +15939,11 @@
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" s="6"/>
       <c r="H9" s="6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="4">

--- a/activity/WEEKLY_RECAP_REP.xlsx
+++ b/activity/WEEKLY_RECAP_REP.xlsx
@@ -11,17 +11,19 @@
     <sheet sheetId="5" name="Rep - Megan" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="Top Accounts" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="New Clients" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Outstanding AR" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="At-Risk" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="All Data" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="README" state="visible" r:id="rId14"/>
+    <sheet sheetId="8" name="MoM Trend" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Free Vial Watch" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Outstanding AR" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="At-Risk" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="All Data" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="README" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2583" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2879" uniqueCount="631">
   <si>
     <t>Weekly Rep Recap</t>
   </si>
@@ -1118,6 +1120,117 @@
     <t>First Invoice</t>
   </si>
   <si>
+    <t>Month over Month</t>
+  </si>
+  <si>
+    <t>Invoiced revenue by invoice date · cash collected by payment date · through 2026-09-11</t>
+  </si>
+  <si>
+    <t>YTD Net Invoiced</t>
+  </si>
+  <si>
+    <t>YTD Cash Collected</t>
+  </si>
+  <si>
+    <t>Best Month (Aug)</t>
+  </si>
+  <si>
+    <t>YTD Discount Rate</t>
+  </si>
+  <si>
+    <t>Free</t>
+  </si>
+  <si>
+    <t>Gross list $</t>
+  </si>
+  <si>
+    <t>Discount $</t>
+  </si>
+  <si>
+    <t>Disc %</t>
+  </si>
+  <si>
+    <t>Net invoiced $</t>
+  </si>
+  <si>
+    <t>Cash collected $</t>
+  </si>
+  <si>
+    <t>YTD</t>
+  </si>
+  <si>
+    <t>Cash and revenue move on different clocks: invoiced revenue is when the sale was booked, cash collected is when the money arrived. Amber Free cells = free rate over 25% of that month's total.</t>
+  </si>
+  <si>
+    <t>Free Vial Watch — sampling ROI</t>
+  </si>
+  <si>
+    <t>Every clinic that took a $0 vial (any promo: SAMPLE26, FREE_VIALS, RES-CENTA, EMTNSTUDY, or uncoded). "Converted" = they placed a paid order after their most recent free order.</t>
+  </si>
+  <si>
+    <t>Clinics Sampled</t>
+  </si>
+  <si>
+    <t>Free Vials Given</t>
+  </si>
+  <si>
+    <t>Converted to Paid</t>
+  </si>
+  <si>
+    <t>Conversion Rate</t>
+  </si>
+  <si>
+    <t>List Value Given</t>
+  </si>
+  <si>
+    <t>Revenue from Converted</t>
+  </si>
+  <si>
+    <t>Last Free Order</t>
+  </si>
+  <si>
+    <t>Promo(s)</t>
+  </si>
+  <si>
+    <t>List Value</t>
+  </si>
+  <si>
+    <t>Paid After</t>
+  </si>
+  <si>
+    <t>SAMPLE26, FREE_VIALS, RES-CENTA</t>
+  </si>
+  <si>
+    <t>Still in window</t>
+  </si>
+  <si>
+    <t>SAMPLE26</t>
+  </si>
+  <si>
+    <t>SAMPLE26, RES-CENTA</t>
+  </si>
+  <si>
+    <t>FREE_VIALS</t>
+  </si>
+  <si>
+    <t>FREE_VIALS, SAMPLE26</t>
+  </si>
+  <si>
+    <t>Last call</t>
+  </si>
+  <si>
+    <t>EMTNSTUDY</t>
+  </si>
+  <si>
+    <t>Close out</t>
+  </si>
+  <si>
+    <t>Converted</t>
+  </si>
+  <si>
+    <t>Follow-up windows: 0–29 days = still in window · 30–59 days = last call this month · 60+ days = close out, no follow-up worked. List value = vials × $825 (approx per-vial list price).</t>
+  </si>
+  <si>
     <t>Outstanding Balances (Aging)</t>
   </si>
   <si>
@@ -1128,6 +1241,18 @@
   </si>
   <si>
     <t>Days Since</t>
+  </si>
+  <si>
+    <t>Call Priority</t>
+  </si>
+  <si>
+    <t>Call this week</t>
+  </si>
+  <si>
+    <t>Within terms — monitor</t>
+  </si>
+  <si>
+    <t>Escalate — 90+ days quiet</t>
   </si>
   <si>
     <t>At-Risk / Inactive Accounts</t>
@@ -1802,7 +1927,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0;(&quot;$&quot;#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1972,8 +2097,26 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="964219"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="964219"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="1E7F3E"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1998,6 +2141,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="F8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -2054,7 +2212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -2222,6 +2380,42 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="30" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="28" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3333,6 +3527,1147 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:J20"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="29" t="s">
+        <v>402</v>
+      </c>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="E6" s="47">
+        <v>6000</v>
+      </c>
+      <c r="F6" s="47">
+        <v>25050</v>
+      </c>
+      <c r="G6" s="47">
+        <v>19050</v>
+      </c>
+      <c r="H6" s="46">
+        <v>32</v>
+      </c>
+      <c r="I6" s="49" t="s">
+        <v>75</v>
+      </c>
+      <c r="J6" s="69" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="E7" s="47">
+        <v>4800</v>
+      </c>
+      <c r="F7" s="47">
+        <v>9600</v>
+      </c>
+      <c r="G7" s="47">
+        <v>4800</v>
+      </c>
+      <c r="H7" s="46">
+        <v>2</v>
+      </c>
+      <c r="I7" s="49" t="s">
+        <v>101</v>
+      </c>
+      <c r="J7" s="69" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>245</v>
+      </c>
+      <c r="E8" s="47">
+        <v>4800</v>
+      </c>
+      <c r="F8" s="47">
+        <v>6075</v>
+      </c>
+      <c r="G8" s="47">
+        <v>1313.12</v>
+      </c>
+      <c r="H8" s="46">
+        <v>15</v>
+      </c>
+      <c r="I8" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="J8" s="69" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="49" t="s">
+        <v>250</v>
+      </c>
+      <c r="E9" s="47">
+        <v>4800</v>
+      </c>
+      <c r="F9" s="47">
+        <v>6000</v>
+      </c>
+      <c r="G9" s="47">
+        <v>1200</v>
+      </c>
+      <c r="H9" s="46">
+        <v>22</v>
+      </c>
+      <c r="I9" s="49" t="s">
+        <v>85</v>
+      </c>
+      <c r="J9" s="69" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>296</v>
+      </c>
+      <c r="E10" s="47">
+        <v>3600</v>
+      </c>
+      <c r="F10" s="47">
+        <v>3600</v>
+      </c>
+      <c r="G10" s="47">
+        <v>0</v>
+      </c>
+      <c r="H10" s="46">
+        <v>31</v>
+      </c>
+      <c r="I10" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="J10" s="69" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="E11" s="47">
+        <v>3350</v>
+      </c>
+      <c r="F11" s="47">
+        <v>22300</v>
+      </c>
+      <c r="G11" s="47">
+        <v>19021.76</v>
+      </c>
+      <c r="H11" s="46">
+        <v>10</v>
+      </c>
+      <c r="I11" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="J11" s="69" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="E12" s="47">
+        <v>3000</v>
+      </c>
+      <c r="F12" s="47">
+        <v>19200</v>
+      </c>
+      <c r="G12" s="47">
+        <v>16200</v>
+      </c>
+      <c r="H12" s="46">
+        <v>9</v>
+      </c>
+      <c r="I12" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="J12" s="69" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="49" t="s">
+        <v>296</v>
+      </c>
+      <c r="E13" s="47">
+        <v>3000</v>
+      </c>
+      <c r="F13" s="47">
+        <v>12600</v>
+      </c>
+      <c r="G13" s="47">
+        <v>9600</v>
+      </c>
+      <c r="H13" s="46">
+        <v>21</v>
+      </c>
+      <c r="I13" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="J13" s="69" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>270</v>
+      </c>
+      <c r="E14" s="47">
+        <v>1800</v>
+      </c>
+      <c r="F14" s="47">
+        <v>2400</v>
+      </c>
+      <c r="G14" s="47">
+        <v>600</v>
+      </c>
+      <c r="H14" s="46">
+        <v>3</v>
+      </c>
+      <c r="I14" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="J14" s="68" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="E15" s="47">
+        <v>1200</v>
+      </c>
+      <c r="F15" s="47">
+        <v>5680</v>
+      </c>
+      <c r="G15" s="47">
+        <v>4515.88</v>
+      </c>
+      <c r="H15" s="46">
+        <v>15</v>
+      </c>
+      <c r="I15" s="49" t="s">
+        <v>79</v>
+      </c>
+      <c r="J15" s="68" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="49" t="s">
+        <v>236</v>
+      </c>
+      <c r="E16" s="47">
+        <v>1182.06</v>
+      </c>
+      <c r="F16" s="47">
+        <v>10800</v>
+      </c>
+      <c r="G16" s="47">
+        <v>9689.7</v>
+      </c>
+      <c r="H16" s="46">
+        <v>28</v>
+      </c>
+      <c r="I16" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="J16" s="68" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="D17" s="49" t="s">
+        <v>247</v>
+      </c>
+      <c r="E17" s="47">
+        <v>675</v>
+      </c>
+      <c r="F17" s="47">
+        <v>1275</v>
+      </c>
+      <c r="G17" s="47">
+        <v>600</v>
+      </c>
+      <c r="H17" s="46">
+        <v>24</v>
+      </c>
+      <c r="I17" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="J17" s="68" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="49" t="s">
+        <v>296</v>
+      </c>
+      <c r="E18" s="47">
+        <v>600</v>
+      </c>
+      <c r="F18" s="47">
+        <v>10800</v>
+      </c>
+      <c r="G18" s="47">
+        <v>10200</v>
+      </c>
+      <c r="H18" s="46">
+        <v>23</v>
+      </c>
+      <c r="I18" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="J18" s="68" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="D19" s="49" t="s">
+        <v>300</v>
+      </c>
+      <c r="E19" s="47">
+        <v>600</v>
+      </c>
+      <c r="F19" s="47">
+        <v>600</v>
+      </c>
+      <c r="G19" s="47">
+        <v>0</v>
+      </c>
+      <c r="H19" s="46">
+        <v>25</v>
+      </c>
+      <c r="I19" s="49" t="s">
+        <v>127</v>
+      </c>
+      <c r="J19" s="68" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="D20" s="49" t="s">
+        <v>252</v>
+      </c>
+      <c r="E20" s="47">
+        <v>600</v>
+      </c>
+      <c r="F20" s="47">
+        <v>600</v>
+      </c>
+      <c r="G20" s="47">
+        <v>0</v>
+      </c>
+      <c r="H20" s="46">
+        <v>149</v>
+      </c>
+      <c r="I20" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="J20" s="70" t="s">
+        <v>409</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I27"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="29" t="s">
+        <v>410</v>
+      </c>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B5" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" s="49" t="s">
+        <v>296</v>
+      </c>
+      <c r="E6" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="F6" s="46">
+        <v>199</v>
+      </c>
+      <c r="G6" s="49" t="s">
+        <v>153</v>
+      </c>
+      <c r="H6" s="47">
+        <v>2400</v>
+      </c>
+      <c r="I6" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="D7" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="E7" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="F7" s="46">
+        <v>192</v>
+      </c>
+      <c r="G7" s="49" t="s">
+        <v>201</v>
+      </c>
+      <c r="H7" s="47">
+        <v>350</v>
+      </c>
+      <c r="I7" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>252</v>
+      </c>
+      <c r="E8" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="F8" s="46">
+        <v>184</v>
+      </c>
+      <c r="G8" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="H8" s="47">
+        <v>600</v>
+      </c>
+      <c r="I8" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="D9" s="49" t="s">
+        <v>252</v>
+      </c>
+      <c r="E9" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="F9" s="46">
+        <v>183</v>
+      </c>
+      <c r="G9" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="H9" s="47">
+        <v>350</v>
+      </c>
+      <c r="I9" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>236</v>
+      </c>
+      <c r="E10" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="F10" s="46">
+        <v>178</v>
+      </c>
+      <c r="G10" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="H10" s="47">
+        <v>5500</v>
+      </c>
+      <c r="I10" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>241</v>
+      </c>
+      <c r="E11" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="F11" s="46">
+        <v>156</v>
+      </c>
+      <c r="G11" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="H11" s="47">
+        <v>2400</v>
+      </c>
+      <c r="I11" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B12" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="E12" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="F12" s="46">
+        <v>156</v>
+      </c>
+      <c r="G12" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="H12" s="47">
+        <v>700</v>
+      </c>
+      <c r="I12" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B13" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="D13" s="49" t="s">
+        <v>252</v>
+      </c>
+      <c r="E13" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="F13" s="46">
+        <v>149</v>
+      </c>
+      <c r="G13" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="H13" s="47">
+        <v>600</v>
+      </c>
+      <c r="I13" s="47">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>295</v>
+      </c>
+      <c r="E14" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="F14" s="46">
+        <v>143</v>
+      </c>
+      <c r="G14" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="H14" s="47">
+        <v>0</v>
+      </c>
+      <c r="I14" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="D15" s="49" t="s">
+        <v>251</v>
+      </c>
+      <c r="E15" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="F15" s="46">
+        <v>143</v>
+      </c>
+      <c r="G15" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="H15" s="47">
+        <v>600</v>
+      </c>
+      <c r="I15" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D16" s="49" t="s">
+        <v>236</v>
+      </c>
+      <c r="E16" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="F16" s="46">
+        <v>136</v>
+      </c>
+      <c r="G16" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="H16" s="47">
+        <v>600</v>
+      </c>
+      <c r="I16" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="D17" s="49" t="s">
+        <v>250</v>
+      </c>
+      <c r="E17" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="F17" s="46">
+        <v>135</v>
+      </c>
+      <c r="G17" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="H17" s="47">
+        <v>600</v>
+      </c>
+      <c r="I17" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="E18" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="F18" s="46">
+        <v>120</v>
+      </c>
+      <c r="G18" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="H18" s="47">
+        <v>9800</v>
+      </c>
+      <c r="I18" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="D19" s="49" t="s">
+        <v>247</v>
+      </c>
+      <c r="E19" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="F19" s="46">
+        <v>119</v>
+      </c>
+      <c r="G19" s="49" t="s">
+        <v>184</v>
+      </c>
+      <c r="H19" s="47">
+        <v>600</v>
+      </c>
+      <c r="I19" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="D20" s="49" t="s">
+        <v>248</v>
+      </c>
+      <c r="E20" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="F20" s="46">
+        <v>114</v>
+      </c>
+      <c r="G20" s="49" t="s">
+        <v>165</v>
+      </c>
+      <c r="H20" s="47">
+        <v>1200</v>
+      </c>
+      <c r="I20" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B21" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="49" t="s">
+        <v>230</v>
+      </c>
+      <c r="E21" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="F21" s="46">
+        <v>108</v>
+      </c>
+      <c r="G21" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="H21" s="47">
+        <v>10200</v>
+      </c>
+      <c r="I21" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D22" s="49" t="s">
+        <v>230</v>
+      </c>
+      <c r="E22" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="F22" s="46">
+        <v>98</v>
+      </c>
+      <c r="G22" s="49" t="s">
+        <v>181</v>
+      </c>
+      <c r="H22" s="47">
+        <v>600</v>
+      </c>
+      <c r="I22" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="D23" s="49" t="s">
+        <v>301</v>
+      </c>
+      <c r="E23" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="F23" s="46">
+        <v>92</v>
+      </c>
+      <c r="G23" s="49" t="s">
+        <v>218</v>
+      </c>
+      <c r="H23" s="47">
+        <v>0</v>
+      </c>
+      <c r="I23" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B24" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="49" t="s">
+        <v>241</v>
+      </c>
+      <c r="E24" s="49" t="s">
+        <v>269</v>
+      </c>
+      <c r="F24" s="46">
+        <v>87</v>
+      </c>
+      <c r="G24" s="49" t="s">
+        <v>99</v>
+      </c>
+      <c r="H24" s="47">
+        <v>2400</v>
+      </c>
+      <c r="I24" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B25" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="D25" s="49" t="s">
+        <v>230</v>
+      </c>
+      <c r="E25" s="49" t="s">
+        <v>269</v>
+      </c>
+      <c r="F25" s="46">
+        <v>74</v>
+      </c>
+      <c r="G25" s="49" t="s">
+        <v>179</v>
+      </c>
+      <c r="H25" s="47">
+        <v>600</v>
+      </c>
+      <c r="I25" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B26" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D26" s="49" t="s">
+        <v>241</v>
+      </c>
+      <c r="E26" s="49" t="s">
+        <v>269</v>
+      </c>
+      <c r="F26" s="46">
+        <v>71</v>
+      </c>
+      <c r="G26" s="49" t="s">
+        <v>142</v>
+      </c>
+      <c r="H26" s="47">
+        <v>4800</v>
+      </c>
+      <c r="I26" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B27" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D27" s="49" t="s">
+        <v>231</v>
+      </c>
+      <c r="E27" s="49" t="s">
+        <v>269</v>
+      </c>
+      <c r="F27" s="46">
+        <v>65</v>
+      </c>
+      <c r="G27" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="H27" s="47">
+        <v>600</v>
+      </c>
+      <c r="I27" s="47">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P108"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
@@ -3341,46 +4676,46 @@
         <v>262</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>370</v>
+        <v>411</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>371</v>
+        <v>412</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>224</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>372</v>
+        <v>413</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>373</v>
+        <v>414</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>226</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>374</v>
+        <v>415</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>375</v>
+        <v>416</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>227</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>376</v>
+        <v>417</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="M1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>378</v>
+        <v>419</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>379</v>
+        <v>420</v>
       </c>
       <c r="P1" s="9" t="s">
         <v>229</v>
@@ -3391,10 +4726,10 @@
         <v>203</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>380</v>
+        <v>421</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>381</v>
+        <v>422</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>241</v>
@@ -3441,10 +4776,10 @@
         <v>143</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>382</v>
+        <v>423</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>383</v>
+        <v>424</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>241</v>
@@ -3491,10 +4826,10 @@
         <v>100</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>231</v>
@@ -3544,7 +4879,7 @@
         <v>104</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>240</v>
@@ -3591,10 +4926,10 @@
         <v>146</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>387</v>
+        <v>428</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>388</v>
+        <v>429</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>270</v>
@@ -3641,10 +4976,10 @@
         <v>168</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>389</v>
+        <v>430</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>390</v>
+        <v>431</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>251</v>
@@ -3691,10 +5026,10 @@
         <v>83</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>391</v>
+        <v>432</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>392</v>
+        <v>433</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>231</v>
@@ -3744,7 +5079,7 @@
         <v>77</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>231</v>
@@ -3794,7 +5129,7 @@
         <v>109</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>394</v>
+        <v>435</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>231</v>
@@ -3841,10 +5176,10 @@
         <v>204</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>395</v>
+        <v>436</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>396</v>
+        <v>437</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>231</v>
@@ -3891,10 +5226,10 @@
         <v>206</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>397</v>
+        <v>438</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>398</v>
+        <v>439</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>295</v>
@@ -3941,10 +5276,10 @@
         <v>118</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>399</v>
+        <v>440</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>400</v>
+        <v>441</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>231</v>
@@ -3994,7 +5329,7 @@
         <v>112</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>401</v>
+        <v>442</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>245</v>
@@ -4041,10 +5376,10 @@
         <v>207</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>402</v>
+        <v>443</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>403</v>
+        <v>444</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>270</v>
@@ -4091,10 +5426,10 @@
         <v>169</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>404</v>
+        <v>445</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>241</v>
@@ -4144,7 +5479,7 @@
         <v>89</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>406</v>
+        <v>447</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>296</v>
@@ -4191,10 +5526,10 @@
         <v>145</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>407</v>
+        <v>448</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>408</v>
+        <v>449</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>231</v>
@@ -4244,7 +5579,7 @@
         <v>71</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>409</v>
+        <v>450</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>230</v>
@@ -4291,10 +5626,10 @@
         <v>161</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>410</v>
+        <v>451</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>411</v>
+        <v>452</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>241</v>
@@ -4341,10 +5676,10 @@
         <v>114</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>412</v>
+        <v>453</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>236</v>
@@ -4394,7 +5729,7 @@
         <v>116</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>414</v>
+        <v>455</v>
       </c>
       <c r="D22" s="10" t="s">
         <v>250</v>
@@ -4444,7 +5779,7 @@
         <v>90</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>415</v>
+        <v>456</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>296</v>
@@ -4491,10 +5826,10 @@
         <v>159</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>416</v>
+        <v>457</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>247</v>
@@ -4541,10 +5876,10 @@
         <v>172</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>418</v>
+        <v>459</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>419</v>
+        <v>460</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>300</v>
@@ -4591,10 +5926,10 @@
         <v>126</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>420</v>
+        <v>461</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>421</v>
+        <v>462</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>250</v>
@@ -4641,10 +5976,10 @@
         <v>92</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>422</v>
+        <v>463</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>423</v>
+        <v>464</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>236</v>
@@ -4691,10 +6026,10 @@
         <v>208</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>424</v>
+        <v>465</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>425</v>
+        <v>466</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>250</v>
@@ -4741,10 +6076,10 @@
         <v>86</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>426</v>
+        <v>467</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>427</v>
+        <v>468</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>231</v>
@@ -4791,10 +6126,10 @@
         <v>148</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>428</v>
+        <v>469</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>429</v>
+        <v>470</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>241</v>
@@ -4841,10 +6176,10 @@
         <v>103</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>430</v>
+        <v>471</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>431</v>
+        <v>472</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>231</v>
@@ -4894,7 +6229,7 @@
         <v>80</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>432</v>
+        <v>473</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>231</v>
@@ -4941,10 +6276,10 @@
         <v>144</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>433</v>
+        <v>474</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>434</v>
+        <v>475</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>296</v>
@@ -4991,10 +6326,10 @@
         <v>209</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>435</v>
+        <v>476</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>436</v>
+        <v>477</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>236</v>
@@ -5041,10 +6376,10 @@
         <v>74</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>437</v>
+        <v>478</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>438</v>
+        <v>479</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>231</v>
@@ -5091,10 +6426,10 @@
         <v>120</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>439</v>
+        <v>480</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>440</v>
+        <v>481</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>231</v>
@@ -5144,7 +6479,7 @@
         <v>173</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>441</v>
+        <v>482</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>276</v>
@@ -5191,10 +6526,10 @@
         <v>129</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>442</v>
+        <v>483</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>443</v>
+        <v>484</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>230</v>
@@ -5241,10 +6576,10 @@
         <v>174</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>444</v>
+        <v>485</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>445</v>
+        <v>486</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>231</v>
@@ -5291,10 +6626,10 @@
         <v>210</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>446</v>
+        <v>487</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>447</v>
+        <v>488</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>230</v>
@@ -5341,10 +6676,10 @@
         <v>131</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>448</v>
+        <v>489</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>449</v>
+        <v>490</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>231</v>
@@ -5391,10 +6726,10 @@
         <v>132</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>450</v>
+        <v>491</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>451</v>
+        <v>492</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>231</v>
@@ -5441,10 +6776,10 @@
         <v>107</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>452</v>
+        <v>493</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>453</v>
+        <v>494</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>236</v>
@@ -5491,10 +6826,10 @@
         <v>211</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>454</v>
+        <v>495</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>455</v>
+        <v>496</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>301</v>
@@ -5541,10 +6876,10 @@
         <v>213</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>456</v>
+        <v>497</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>457</v>
+        <v>498</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>230</v>
@@ -5591,10 +6926,10 @@
         <v>124</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>458</v>
+        <v>499</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>459</v>
+        <v>500</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>230</v>
@@ -5641,10 +6976,10 @@
         <v>134</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>460</v>
+        <v>501</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>461</v>
+        <v>502</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>277</v>
@@ -5691,10 +7026,10 @@
         <v>163</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>462</v>
+        <v>503</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>463</v>
+        <v>504</v>
       </c>
       <c r="D48" s="10" t="s">
         <v>252</v>
@@ -5744,7 +7079,7 @@
         <v>155</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>464</v>
+        <v>505</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>231</v>
@@ -5794,7 +7129,7 @@
         <v>158</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>465</v>
+        <v>506</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>296</v>
@@ -5841,10 +7176,10 @@
         <v>136</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>466</v>
+        <v>507</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>467</v>
+        <v>508</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>246</v>
@@ -5891,10 +7226,10 @@
         <v>215</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>468</v>
+        <v>509</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>469</v>
+        <v>510</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>278</v>
@@ -5941,10 +7276,10 @@
         <v>139</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>470</v>
+        <v>511</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>471</v>
+        <v>512</v>
       </c>
       <c r="D53" s="10" t="s">
         <v>302</v>
@@ -5994,7 +7329,7 @@
         <v>110</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>472</v>
+        <v>513</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>241</v>
@@ -6041,10 +7376,10 @@
         <v>175</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>473</v>
+        <v>514</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>474</v>
+        <v>515</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>231</v>
@@ -6091,10 +7426,10 @@
         <v>141</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>475</v>
+        <v>516</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>476</v>
+        <v>517</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>241</v>
@@ -6141,10 +7476,10 @@
         <v>178</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>477</v>
+        <v>518</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>478</v>
+        <v>519</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>230</v>
@@ -6191,10 +7526,10 @@
         <v>149</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>479</v>
+        <v>520</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>480</v>
+        <v>521</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>241</v>
@@ -6241,10 +7576,10 @@
         <v>217</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>481</v>
+        <v>522</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>482</v>
+        <v>523</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>301</v>
@@ -6291,10 +7626,10 @@
         <v>180</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>483</v>
+        <v>524</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>484</v>
+        <v>525</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>230</v>
@@ -6341,10 +7676,10 @@
         <v>94</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>485</v>
+        <v>526</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>486</v>
+        <v>527</v>
       </c>
       <c r="D61" s="10" t="s">
         <v>230</v>
@@ -6391,10 +7726,10 @@
         <v>164</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>487</v>
+        <v>528</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>488</v>
+        <v>529</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>248</v>
@@ -6441,10 +7776,10 @@
         <v>183</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>489</v>
+        <v>530</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>490</v>
+        <v>531</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>247</v>
@@ -6491,10 +7826,10 @@
         <v>97</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>491</v>
+        <v>532</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>492</v>
+        <v>533</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>231</v>
@@ -6541,10 +7876,10 @@
         <v>185</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>493</v>
+        <v>534</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>494</v>
+        <v>535</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>250</v>
@@ -6591,10 +7926,10 @@
         <v>187</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>495</v>
+        <v>536</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>453</v>
+        <v>494</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>236</v>
@@ -6644,7 +7979,7 @@
         <v>219</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>496</v>
+        <v>537</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>295</v>
@@ -6691,10 +8026,10 @@
         <v>190</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>498</v>
+        <v>539</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>251</v>
@@ -6741,10 +8076,10 @@
         <v>193</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>499</v>
+        <v>540</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>500</v>
+        <v>541</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>252</v>
@@ -6791,10 +8126,10 @@
         <v>151</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>479</v>
+        <v>520</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>501</v>
+        <v>542</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>241</v>
@@ -6841,10 +8176,10 @@
         <v>167</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>502</v>
+        <v>543</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>503</v>
+        <v>544</v>
       </c>
       <c r="D71" s="10" t="s">
         <v>231</v>
@@ -6891,10 +8226,10 @@
         <v>121</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>504</v>
+        <v>545</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>505</v>
+        <v>546</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>236</v>
@@ -6941,10 +8276,10 @@
         <v>197</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>506</v>
+        <v>547</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>507</v>
+        <v>548</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>252</v>
@@ -6991,10 +8326,10 @@
         <v>195</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>508</v>
+        <v>549</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>509</v>
+        <v>550</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>252</v>
@@ -7041,10 +8376,10 @@
         <v>200</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>510</v>
+        <v>551</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>511</v>
+        <v>552</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>231</v>
@@ -7094,7 +8429,7 @@
         <v>152</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>512</v>
+        <v>553</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>296</v>
@@ -7144,7 +8479,7 @@
         <v>305</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>513</v>
+        <v>554</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>296</v>
@@ -7187,10 +8522,10 @@
         <v>281</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>514</v>
+        <v>555</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>515</v>
+        <v>556</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>270</v>
@@ -7236,7 +8571,7 @@
         <v>306</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>516</v>
+        <v>557</v>
       </c>
       <c r="D79" s="10" t="s">
         <v>296</v>
@@ -7279,10 +8614,10 @@
         <v>283</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>517</v>
+        <v>558</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>518</v>
+        <v>559</v>
       </c>
       <c r="D80" s="10" t="s">
         <v>276</v>
@@ -7325,10 +8660,10 @@
         <v>307</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>519</v>
+        <v>560</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>520</v>
+        <v>561</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>308</v>
@@ -7371,10 +8706,10 @@
         <v>284</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>521</v>
+        <v>562</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>522</v>
+        <v>563</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>285</v>
@@ -7420,7 +8755,7 @@
         <v>309</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>523</v>
+        <v>564</v>
       </c>
       <c r="D83" s="10" t="s">
         <v>310</v>
@@ -7463,10 +8798,10 @@
         <v>286</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>524</v>
+        <v>565</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>525</v>
+        <v>566</v>
       </c>
       <c r="D84" s="10" t="s">
         <v>248</v>
@@ -7509,10 +8844,10 @@
         <v>311</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>526</v>
+        <v>567</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>527</v>
+        <v>568</v>
       </c>
       <c r="D85" s="10" t="s">
         <v>300</v>
@@ -7555,10 +8890,10 @@
         <v>287</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>528</v>
+        <v>569</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>529</v>
+        <v>570</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>230</v>
@@ -7601,10 +8936,10 @@
         <v>312</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>530</v>
+        <v>571</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>531</v>
+        <v>572</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>313</v>
@@ -7647,10 +8982,10 @@
         <v>314</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>532</v>
+        <v>573</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>533</v>
+        <v>574</v>
       </c>
       <c r="D88" s="10" t="s">
         <v>240</v>
@@ -7693,10 +9028,10 @@
         <v>315</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>534</v>
+        <v>575</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>535</v>
+        <v>576</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>296</v>
@@ -7739,10 +9074,10 @@
         <v>152</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>536</v>
+        <v>577</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>537</v>
+        <v>578</v>
       </c>
       <c r="D90" s="10" t="s">
         <v>296</v>
@@ -7785,10 +9120,10 @@
         <v>288</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>538</v>
+        <v>579</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>539</v>
+        <v>580</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>276</v>
@@ -7831,10 +9166,10 @@
         <v>316</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>540</v>
+        <v>581</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>541</v>
+        <v>582</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>296</v>
@@ -7877,10 +9212,10 @@
         <v>317</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>542</v>
+        <v>583</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>543</v>
+        <v>584</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>313</v>
@@ -7923,10 +9258,10 @@
         <v>318</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>544</v>
+        <v>585</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>545</v>
+        <v>586</v>
       </c>
       <c r="D94" s="10" t="s">
         <v>319</v>
@@ -7969,10 +9304,10 @@
         <v>320</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>546</v>
+        <v>587</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>547</v>
+        <v>588</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>296</v>
@@ -8015,10 +9350,10 @@
         <v>289</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>548</v>
+        <v>589</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>549</v>
+        <v>590</v>
       </c>
       <c r="D96" s="10" t="s">
         <v>236</v>
@@ -8061,10 +9396,10 @@
         <v>321</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>550</v>
+        <v>591</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>551</v>
+        <v>592</v>
       </c>
       <c r="D97" s="10" t="s">
         <v>230</v>
@@ -8107,10 +9442,10 @@
         <v>290</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>552</v>
+        <v>593</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>553</v>
+        <v>594</v>
       </c>
       <c r="D98" s="10" t="s">
         <v>252</v>
@@ -8153,10 +9488,10 @@
         <v>291</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>554</v>
+        <v>595</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>555</v>
+        <v>596</v>
       </c>
       <c r="D99" s="10" t="s">
         <v>236</v>
@@ -8199,10 +9534,10 @@
         <v>322</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>556</v>
+        <v>597</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>557</v>
+        <v>598</v>
       </c>
       <c r="D100" s="10" t="s">
         <v>296</v>
@@ -8245,10 +9580,10 @@
         <v>292</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>558</v>
+        <v>599</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>559</v>
+        <v>600</v>
       </c>
       <c r="D101" s="10" t="s">
         <v>231</v>
@@ -8291,10 +9626,10 @@
         <v>293</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>560</v>
+        <v>601</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>561</v>
+        <v>602</v>
       </c>
       <c r="D102" s="10" t="s">
         <v>251</v>
@@ -8337,10 +9672,10 @@
         <v>323</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>562</v>
+        <v>603</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>563</v>
+        <v>604</v>
       </c>
       <c r="D103" s="10" t="s">
         <v>324</v>
@@ -8383,10 +9718,10 @@
         <v>325</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>564</v>
+        <v>605</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>565</v>
+        <v>606</v>
       </c>
       <c r="D104" s="10" t="s">
         <v>308</v>
@@ -8429,10 +9764,10 @@
         <v>326</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>567</v>
+        <v>608</v>
       </c>
       <c r="D105" s="10" t="s">
         <v>302</v>
@@ -8475,10 +9810,10 @@
         <v>327</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>568</v>
+        <v>609</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>569</v>
+        <v>610</v>
       </c>
       <c r="D106" s="10" t="s">
         <v>240</v>
@@ -8521,10 +9856,10 @@
         <v>328</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>570</v>
+        <v>611</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>571</v>
+        <v>612</v>
       </c>
       <c r="D107" s="10" t="s">
         <v>329</v>
@@ -8567,10 +9902,10 @@
         <v>330</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>572</v>
+        <v>613</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>573</v>
+        <v>614</v>
       </c>
       <c r="D108" s="10" t="s">
         <v>246</v>
@@ -8614,7 +9949,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:I20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
@@ -8624,7 +9959,7 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="29" t="s">
-        <v>574</v>
+        <v>615</v>
       </c>
       <c r="C2" s="29"/>
       <c r="D2" s="29"/>
@@ -8634,208 +9969,208 @@
       <c r="H2" s="29"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="61" t="s">
-        <v>575</v>
-      </c>
-      <c r="C4" s="61"/>
-      <c r="D4" s="61"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="61"/>
-      <c r="G4" s="61"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="61"/>
+      <c r="B4" s="73" t="s">
+        <v>616</v>
+      </c>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="62" t="s">
-        <v>576</v>
-      </c>
-      <c r="C5" s="62"/>
-      <c r="D5" s="62"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
+      <c r="B5" s="74" t="s">
+        <v>617</v>
+      </c>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="62" t="s">
-        <v>577</v>
-      </c>
-      <c r="C6" s="62"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
-      <c r="G6" s="62"/>
-      <c r="H6" s="62"/>
-      <c r="I6" s="62"/>
+      <c r="B6" s="74" t="s">
+        <v>618</v>
+      </c>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="74"/>
+      <c r="I6" s="74"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="62" t="s">
+      <c r="B7" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
-      <c r="H7" s="62"/>
-      <c r="I7" s="62"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="62" t="s">
-        <v>578</v>
-      </c>
-      <c r="C8" s="62"/>
-      <c r="D8" s="62"/>
-      <c r="E8" s="62"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="62"/>
-      <c r="I8" s="62"/>
+      <c r="B8" s="74" t="s">
+        <v>619</v>
+      </c>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="74"/>
+      <c r="H8" s="74"/>
+      <c r="I8" s="74"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="62" t="s">
-        <v>579</v>
-      </c>
-      <c r="C9" s="62"/>
-      <c r="D9" s="62"/>
-      <c r="E9" s="62"/>
-      <c r="F9" s="62"/>
-      <c r="G9" s="62"/>
-      <c r="H9" s="62"/>
-      <c r="I9" s="62"/>
+      <c r="B9" s="74" t="s">
+        <v>620</v>
+      </c>
+      <c r="C9" s="74"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="74"/>
+      <c r="H9" s="74"/>
+      <c r="I9" s="74"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="62" t="s">
+      <c r="B10" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="62"/>
-      <c r="D10" s="62"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="62"/>
-      <c r="I10" s="62"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="74"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="61" t="s">
-        <v>580</v>
-      </c>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
+      <c r="B11" s="73" t="s">
+        <v>621</v>
+      </c>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="62" t="s">
-        <v>581</v>
-      </c>
-      <c r="C12" s="62"/>
-      <c r="D12" s="62"/>
-      <c r="E12" s="62"/>
-      <c r="F12" s="62"/>
-      <c r="G12" s="62"/>
-      <c r="H12" s="62"/>
-      <c r="I12" s="62"/>
+      <c r="B12" s="74" t="s">
+        <v>622</v>
+      </c>
+      <c r="C12" s="74"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="74"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="62" t="s">
-        <v>582</v>
-      </c>
-      <c r="C13" s="62"/>
-      <c r="D13" s="62"/>
-      <c r="E13" s="62"/>
-      <c r="F13" s="62"/>
-      <c r="G13" s="62"/>
-      <c r="H13" s="62"/>
-      <c r="I13" s="62"/>
+      <c r="B13" s="74" t="s">
+        <v>623</v>
+      </c>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="62" t="s">
-        <v>583</v>
-      </c>
-      <c r="C14" s="62"/>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
-      <c r="G14" s="62"/>
-      <c r="H14" s="62"/>
-      <c r="I14" s="62"/>
+      <c r="B14" s="74" t="s">
+        <v>624</v>
+      </c>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="74"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="62" t="s">
-        <v>584</v>
-      </c>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="62"/>
+      <c r="B15" s="74" t="s">
+        <v>625</v>
+      </c>
+      <c r="C15" s="74"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="74"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="62" t="s">
-        <v>585</v>
-      </c>
-      <c r="C16" s="62"/>
-      <c r="D16" s="62"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="62"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="62"/>
+      <c r="B16" s="74" t="s">
+        <v>626</v>
+      </c>
+      <c r="C16" s="74"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="74"/>
+      <c r="I16" s="74"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="62" t="s">
-        <v>586</v>
-      </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="62"/>
-      <c r="E17" s="62"/>
-      <c r="F17" s="62"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="62"/>
-      <c r="I17" s="62"/>
+      <c r="B17" s="74" t="s">
+        <v>627</v>
+      </c>
+      <c r="C17" s="74"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="74"/>
+      <c r="I17" s="74"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="62" t="s">
-        <v>587</v>
-      </c>
-      <c r="C18" s="62"/>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
-      <c r="G18" s="62"/>
-      <c r="H18" s="62"/>
-      <c r="I18" s="62"/>
+      <c r="B18" s="74" t="s">
+        <v>628</v>
+      </c>
+      <c r="C18" s="74"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74"/>
+      <c r="G18" s="74"/>
+      <c r="H18" s="74"/>
+      <c r="I18" s="74"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="62" t="s">
-        <v>588</v>
-      </c>
-      <c r="C19" s="62"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="62"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="62"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="62"/>
+      <c r="B19" s="74" t="s">
+        <v>629</v>
+      </c>
+      <c r="C19" s="74"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="74"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="62" t="s">
-        <v>589</v>
-      </c>
-      <c r="C20" s="62"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="62"/>
-      <c r="F20" s="62"/>
-      <c r="G20" s="62"/>
-      <c r="H20" s="62"/>
-      <c r="I20" s="62"/>
+      <c r="B20" s="74" t="s">
+        <v>630</v>
+      </c>
+      <c r="C20" s="74"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -20369,17 +21704,17 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I20"/>
+  <dimension ref="B2:K22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="9" width="14" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="6" width="8" customWidth="1"/>
+    <col min="7" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="29" t="s">
         <v>365</v>
       </c>
@@ -20390,439 +21725,448 @@
       <c r="G2" s="29"/>
       <c r="H2" s="29"/>
       <c r="I2" s="29"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B3" s="8" t="s">
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B3" s="50" t="s">
         <v>366</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="B5" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="4">
+        <v>360385</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
+        <v>323110</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4">
+        <v>109650</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="5">
+        <v>0.4458514008057324</v>
+      </c>
+      <c r="I6" s="5"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B10" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B11" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="C11" s="46">
+        <v>4</v>
+      </c>
+      <c r="D11" s="46">
+        <v>8</v>
+      </c>
+      <c r="E11" s="46">
+        <v>8</v>
+      </c>
+      <c r="F11" s="46">
+        <v>0</v>
+      </c>
+      <c r="G11" s="47">
+        <v>10540</v>
+      </c>
+      <c r="H11" s="47">
+        <v>680</v>
+      </c>
+      <c r="I11" s="61">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="J11" s="62">
+        <v>9860</v>
+      </c>
+      <c r="K11" s="47">
+        <v>7330</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B12" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="C12" s="46">
+        <v>10</v>
+      </c>
+      <c r="D12" s="46">
+        <v>19</v>
+      </c>
+      <c r="E12" s="46">
+        <v>19</v>
+      </c>
+      <c r="F12" s="46">
+        <v>0</v>
+      </c>
+      <c r="G12" s="47">
+        <v>21425</v>
+      </c>
+      <c r="H12" s="47">
+        <v>9725</v>
+      </c>
+      <c r="I12" s="61">
+        <v>0.4539089848308051</v>
+      </c>
+      <c r="J12" s="62">
+        <v>11700</v>
+      </c>
+      <c r="K12" s="47">
+        <v>7530</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B13" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="C13" s="46">
+        <v>22</v>
+      </c>
+      <c r="D13" s="46">
+        <v>78</v>
+      </c>
+      <c r="E13" s="46">
+        <v>75</v>
+      </c>
+      <c r="F13" s="46">
+        <v>3</v>
+      </c>
+      <c r="G13" s="47">
+        <v>112125</v>
+      </c>
+      <c r="H13" s="47">
+        <v>70125</v>
+      </c>
+      <c r="I13" s="61">
+        <v>0.6254180602006689</v>
+      </c>
+      <c r="J13" s="62">
+        <v>42000</v>
+      </c>
+      <c r="K13" s="47">
+        <v>19150</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B14" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="C14" s="46">
+        <v>35</v>
+      </c>
+      <c r="D14" s="46">
+        <v>112</v>
+      </c>
+      <c r="E14" s="46">
+        <v>103</v>
+      </c>
+      <c r="F14" s="46">
         <v>9</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" s="49" t="s">
-        <v>231</v>
-      </c>
-      <c r="E6" s="47">
-        <v>6000</v>
-      </c>
-      <c r="F6" s="47">
-        <v>25050</v>
-      </c>
-      <c r="G6" s="47">
-        <v>19050</v>
-      </c>
-      <c r="H6" s="46">
+      <c r="G14" s="47">
+        <v>90350</v>
+      </c>
+      <c r="H14" s="47">
+        <v>29050</v>
+      </c>
+      <c r="I14" s="61">
+        <v>0.3215273934698395</v>
+      </c>
+      <c r="J14" s="62">
+        <v>61300</v>
+      </c>
+      <c r="K14" s="47">
+        <v>40200</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B15" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="C15" s="46">
         <v>32</v>
       </c>
-      <c r="I6" s="49" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>231</v>
-      </c>
-      <c r="E7" s="47">
-        <v>4800</v>
-      </c>
-      <c r="F7" s="47">
-        <v>9600</v>
-      </c>
-      <c r="G7" s="47">
-        <v>4800</v>
-      </c>
-      <c r="H7" s="46">
-        <v>2</v>
-      </c>
-      <c r="I7" s="49" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" s="49" t="s">
-        <v>245</v>
-      </c>
-      <c r="E8" s="47">
-        <v>4800</v>
-      </c>
-      <c r="F8" s="47">
-        <v>6075</v>
-      </c>
-      <c r="G8" s="47">
-        <v>1313.12</v>
-      </c>
-      <c r="H8" s="46">
-        <v>15</v>
-      </c>
-      <c r="I8" s="49" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="10" t="s">
+      <c r="D15" s="46">
+        <v>98</v>
+      </c>
+      <c r="E15" s="46">
+        <v>90</v>
+      </c>
+      <c r="F15" s="46">
+        <v>8</v>
+      </c>
+      <c r="G15" s="47">
+        <v>78375</v>
+      </c>
+      <c r="H15" s="47">
+        <v>24625</v>
+      </c>
+      <c r="I15" s="61">
+        <v>0.3141945773524721</v>
+      </c>
+      <c r="J15" s="62">
+        <v>53750</v>
+      </c>
+      <c r="K15" s="47">
+        <v>50750</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C16" s="46">
+        <v>25</v>
+      </c>
+      <c r="D16" s="46">
+        <v>58</v>
+      </c>
+      <c r="E16" s="46">
+        <v>47</v>
+      </c>
+      <c r="F16" s="46">
+        <v>11</v>
+      </c>
+      <c r="G16" s="47">
+        <v>46950</v>
+      </c>
+      <c r="H16" s="47">
+        <v>17700</v>
+      </c>
+      <c r="I16" s="61">
+        <v>0.3769968051118211</v>
+      </c>
+      <c r="J16" s="62">
+        <v>29250</v>
+      </c>
+      <c r="K16" s="47">
+        <v>54400</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="C17" s="46">
+        <v>29</v>
+      </c>
+      <c r="D17" s="46">
+        <v>82</v>
+      </c>
+      <c r="E17" s="46">
+        <v>59</v>
+      </c>
+      <c r="F17" s="63">
+        <v>23</v>
+      </c>
+      <c r="G17" s="47">
+        <v>64400</v>
+      </c>
+      <c r="H17" s="47">
+        <v>28925</v>
+      </c>
+      <c r="I17" s="61">
+        <v>0.44914596273291924</v>
+      </c>
+      <c r="J17" s="62">
+        <v>35475</v>
+      </c>
+      <c r="K17" s="47">
+        <v>35400</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B18" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C18" s="46">
+        <v>65</v>
+      </c>
+      <c r="D18" s="46">
+        <v>246</v>
+      </c>
+      <c r="E18" s="46">
+        <v>181</v>
+      </c>
+      <c r="F18" s="63">
+        <v>65</v>
+      </c>
+      <c r="G18" s="47">
+        <v>201825</v>
+      </c>
+      <c r="H18" s="47">
+        <v>92175</v>
+      </c>
+      <c r="I18" s="61">
+        <v>0.4567075436640654</v>
+      </c>
+      <c r="J18" s="62">
+        <v>109650</v>
+      </c>
+      <c r="K18" s="47">
+        <v>73500</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B19" s="56" t="s">
+        <v>359</v>
+      </c>
+      <c r="C19" s="46">
+        <v>13</v>
+      </c>
+      <c r="D19" s="46">
+        <v>32</v>
+      </c>
+      <c r="E19" s="46">
+        <v>14</v>
+      </c>
+      <c r="F19" s="63">
         <v>18</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" s="49" t="s">
-        <v>250</v>
-      </c>
-      <c r="E9" s="47">
-        <v>4800</v>
-      </c>
-      <c r="F9" s="47">
-        <v>6000</v>
-      </c>
-      <c r="G9" s="47">
-        <v>1200</v>
-      </c>
-      <c r="H9" s="46">
-        <v>22</v>
-      </c>
-      <c r="I9" s="49" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>296</v>
-      </c>
-      <c r="E10" s="47">
-        <v>3600</v>
-      </c>
-      <c r="F10" s="47">
-        <v>3600</v>
-      </c>
-      <c r="G10" s="47">
-        <v>0</v>
-      </c>
-      <c r="H10" s="46">
-        <v>31</v>
-      </c>
-      <c r="I10" s="49" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>231</v>
-      </c>
-      <c r="E11" s="47">
-        <v>3350</v>
-      </c>
-      <c r="F11" s="47">
-        <v>22300</v>
-      </c>
-      <c r="G11" s="47">
-        <v>19021.76</v>
-      </c>
-      <c r="H11" s="46">
-        <v>10</v>
-      </c>
-      <c r="I11" s="49" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>231</v>
-      </c>
-      <c r="E12" s="47">
-        <v>3000</v>
-      </c>
-      <c r="F12" s="47">
-        <v>19200</v>
-      </c>
-      <c r="G12" s="47">
-        <v>16200</v>
-      </c>
-      <c r="H12" s="46">
-        <v>9</v>
-      </c>
-      <c r="I12" s="49" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" s="49" t="s">
-        <v>296</v>
-      </c>
-      <c r="E13" s="47">
-        <v>3000</v>
-      </c>
-      <c r="F13" s="47">
-        <v>12600</v>
-      </c>
-      <c r="G13" s="47">
-        <v>9600</v>
-      </c>
-      <c r="H13" s="46">
-        <v>21</v>
-      </c>
-      <c r="I13" s="49" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D14" s="49" t="s">
-        <v>270</v>
-      </c>
-      <c r="E14" s="47">
-        <v>1800</v>
-      </c>
-      <c r="F14" s="47">
-        <v>2400</v>
-      </c>
-      <c r="G14" s="47">
-        <v>600</v>
-      </c>
-      <c r="H14" s="46">
-        <v>3</v>
-      </c>
-      <c r="I14" s="49" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" s="49" t="s">
-        <v>231</v>
-      </c>
-      <c r="E15" s="47">
-        <v>1200</v>
-      </c>
-      <c r="F15" s="47">
-        <v>5680</v>
-      </c>
-      <c r="G15" s="47">
-        <v>4515.88</v>
-      </c>
-      <c r="H15" s="46">
-        <v>15</v>
-      </c>
-      <c r="I15" s="49" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" s="49" t="s">
-        <v>236</v>
-      </c>
-      <c r="E16" s="47">
-        <v>1182.06</v>
-      </c>
-      <c r="F16" s="47">
-        <v>10800</v>
-      </c>
-      <c r="G16" s="47">
-        <v>9689.7</v>
-      </c>
-      <c r="H16" s="46">
-        <v>28</v>
-      </c>
-      <c r="I16" s="49" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="D17" s="49" t="s">
-        <v>247</v>
-      </c>
-      <c r="E17" s="47">
-        <v>675</v>
-      </c>
-      <c r="F17" s="47">
-        <v>1275</v>
-      </c>
-      <c r="G17" s="47">
-        <v>600</v>
-      </c>
-      <c r="H17" s="46">
-        <v>24</v>
-      </c>
-      <c r="I17" s="49" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" s="49" t="s">
-        <v>296</v>
-      </c>
-      <c r="E18" s="47">
-        <v>600</v>
-      </c>
-      <c r="F18" s="47">
-        <v>10800</v>
-      </c>
-      <c r="G18" s="47">
-        <v>10200</v>
-      </c>
-      <c r="H18" s="46">
-        <v>23</v>
-      </c>
-      <c r="I18" s="49" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="D19" s="49" t="s">
-        <v>300</v>
-      </c>
-      <c r="E19" s="47">
-        <v>600</v>
-      </c>
-      <c r="F19" s="47">
-        <v>600</v>
-      </c>
       <c r="G19" s="47">
-        <v>0</v>
-      </c>
-      <c r="H19" s="46">
-        <v>25</v>
-      </c>
-      <c r="I19" s="49" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="D20" s="49" t="s">
-        <v>252</v>
-      </c>
-      <c r="E20" s="47">
-        <v>600</v>
-      </c>
-      <c r="F20" s="47">
-        <v>600</v>
-      </c>
-      <c r="G20" s="47">
-        <v>0</v>
-      </c>
-      <c r="H20" s="46">
-        <v>149</v>
-      </c>
-      <c r="I20" s="49" t="s">
-        <v>194</v>
-      </c>
+        <v>24350</v>
+      </c>
+      <c r="H19" s="47">
+        <v>16950</v>
+      </c>
+      <c r="I19" s="61">
+        <v>0.6960985626283368</v>
+      </c>
+      <c r="J19" s="62">
+        <v>7400</v>
+      </c>
+      <c r="K19" s="47">
+        <v>34850</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B20" s="56" t="s">
+        <v>377</v>
+      </c>
+      <c r="C20" s="57">
+        <v>235</v>
+      </c>
+      <c r="D20" s="57">
+        <v>733</v>
+      </c>
+      <c r="E20" s="57">
+        <v>596</v>
+      </c>
+      <c r="F20" s="57">
+        <v>137</v>
+      </c>
+      <c r="G20" s="64">
+        <v>650340</v>
+      </c>
+      <c r="H20" s="64">
+        <v>289955</v>
+      </c>
+      <c r="I20" s="65">
+        <v>0.4458514008057324</v>
+      </c>
+      <c r="J20" s="64">
+        <v>360385</v>
+      </c>
+      <c r="K20" s="64">
+        <v>323110</v>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B22" s="66" t="s">
+        <v>378</v>
+      </c>
+      <c r="C22" s="66"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="66"/>
+      <c r="K22" s="66"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
+  <mergeCells count="11">
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="B6:C7"/>
+    <mergeCell ref="D6:E7"/>
+    <mergeCell ref="F6:G7"/>
+    <mergeCell ref="H6:I7"/>
+    <mergeCell ref="B22:K22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -20831,15 +22175,22 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:I27"/>
+  <dimension ref="B2:J65"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="29" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="C2" s="29"/>
       <c r="D2" s="29"/>
@@ -20847,608 +22198,1516 @@
       <c r="F2" s="29"/>
       <c r="G2" s="29"/>
       <c r="H2" s="29"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="66" t="s">
+        <v>380</v>
+      </c>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="6">
+        <v>47</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6">
+        <v>137</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6">
+        <v>4</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="5">
+        <v>0.0851063829787234</v>
+      </c>
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="4">
+        <v>113025</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4">
+        <v>10800</v>
+      </c>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="E5" s="9" t="s">
+      <c r="D15" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="J15" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="I5" s="9" t="s">
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="46">
+        <v>2</v>
+      </c>
+      <c r="F16" s="46">
+        <v>19</v>
+      </c>
+      <c r="G16" s="67" t="s">
+        <v>391</v>
+      </c>
+      <c r="H16" s="47">
+        <v>15675</v>
+      </c>
+      <c r="I16" s="47">
+        <v>0</v>
+      </c>
+      <c r="J16" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="60" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" s="46">
+        <v>2</v>
+      </c>
+      <c r="F17" s="46">
+        <v>1</v>
+      </c>
+      <c r="G17" s="67" t="s">
+        <v>393</v>
+      </c>
+      <c r="H17" s="47">
+        <v>825</v>
+      </c>
+      <c r="I17" s="47">
+        <v>0</v>
+      </c>
+      <c r="J17" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" s="46">
+        <v>3</v>
+      </c>
+      <c r="F18" s="46">
+        <v>5</v>
+      </c>
+      <c r="G18" s="67" t="s">
+        <v>394</v>
+      </c>
+      <c r="H18" s="47">
+        <v>4125</v>
+      </c>
+      <c r="I18" s="47">
+        <v>0</v>
+      </c>
+      <c r="J18" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="60" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="46">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="10" t="s">
+      <c r="F19" s="46">
+        <v>2</v>
+      </c>
+      <c r="G19" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H19" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I19" s="47">
+        <v>0</v>
+      </c>
+      <c r="J19" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="46">
+        <v>10</v>
+      </c>
+      <c r="F20" s="46">
+        <v>7</v>
+      </c>
+      <c r="G20" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H20" s="47">
+        <v>5775</v>
+      </c>
+      <c r="I20" s="47">
+        <v>0</v>
+      </c>
+      <c r="J20" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="60" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="46">
+        <v>10</v>
+      </c>
+      <c r="F21" s="46">
+        <v>7</v>
+      </c>
+      <c r="G21" s="67" t="s">
+        <v>393</v>
+      </c>
+      <c r="H21" s="47">
+        <v>5775</v>
+      </c>
+      <c r="I21" s="47">
+        <v>0</v>
+      </c>
+      <c r="J21" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="60" t="s">
+        <v>205</v>
+      </c>
+      <c r="E22" s="46">
+        <v>11</v>
+      </c>
+      <c r="F22" s="46">
+        <v>1</v>
+      </c>
+      <c r="G22" s="67" t="s">
+        <v>393</v>
+      </c>
+      <c r="H22" s="47">
+        <v>825</v>
+      </c>
+      <c r="I22" s="47">
+        <v>0</v>
+      </c>
+      <c r="J22" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="D6" s="49" t="s">
-        <v>296</v>
-      </c>
-      <c r="E6" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="F6" s="46">
-        <v>199</v>
-      </c>
-      <c r="G6" s="49" t="s">
-        <v>153</v>
-      </c>
-      <c r="H6" s="47">
+      <c r="D23" s="60" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="46">
+        <v>14</v>
+      </c>
+      <c r="F23" s="46">
+        <v>1</v>
+      </c>
+      <c r="G23" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H23" s="47">
+        <v>825</v>
+      </c>
+      <c r="I23" s="47">
+        <v>0</v>
+      </c>
+      <c r="J23" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="60" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" s="46">
+        <v>15</v>
+      </c>
+      <c r="F24" s="46">
+        <v>3</v>
+      </c>
+      <c r="G24" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H24" s="47">
+        <v>2475</v>
+      </c>
+      <c r="I24" s="47">
+        <v>0</v>
+      </c>
+      <c r="J24" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="60" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="46">
+        <v>17</v>
+      </c>
+      <c r="F25" s="46">
+        <v>1</v>
+      </c>
+      <c r="G25" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H25" s="47">
+        <v>825</v>
+      </c>
+      <c r="I25" s="47">
+        <v>0</v>
+      </c>
+      <c r="J25" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="60" t="s">
+        <v>170</v>
+      </c>
+      <c r="E26" s="46">
+        <v>18</v>
+      </c>
+      <c r="F26" s="46">
+        <v>1</v>
+      </c>
+      <c r="G26" s="67" t="s">
+        <v>393</v>
+      </c>
+      <c r="H26" s="47">
+        <v>825</v>
+      </c>
+      <c r="I26" s="47">
+        <v>0</v>
+      </c>
+      <c r="J26" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="60" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" s="46">
+        <v>21</v>
+      </c>
+      <c r="F27" s="46">
+        <v>2</v>
+      </c>
+      <c r="G27" s="67" t="s">
+        <v>393</v>
+      </c>
+      <c r="H27" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I27" s="47">
+        <v>0</v>
+      </c>
+      <c r="J27" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="60" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="46">
+        <v>21</v>
+      </c>
+      <c r="F28" s="46">
+        <v>2</v>
+      </c>
+      <c r="G28" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H28" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I28" s="47">
+        <v>0</v>
+      </c>
+      <c r="J28" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="60" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="46">
+        <v>21</v>
+      </c>
+      <c r="F29" s="46">
+        <v>4</v>
+      </c>
+      <c r="G29" s="67" t="s">
+        <v>393</v>
+      </c>
+      <c r="H29" s="47">
+        <v>3300</v>
+      </c>
+      <c r="I29" s="47">
+        <v>0</v>
+      </c>
+      <c r="J29" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="E30" s="46">
+        <v>22</v>
+      </c>
+      <c r="F30" s="46">
+        <v>8</v>
+      </c>
+      <c r="G30" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H30" s="47">
+        <v>6600</v>
+      </c>
+      <c r="I30" s="47">
+        <v>0</v>
+      </c>
+      <c r="J30" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B31" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="E31" s="46">
+        <v>22</v>
+      </c>
+      <c r="F31" s="46">
+        <v>2</v>
+      </c>
+      <c r="G31" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H31" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I31" s="47">
+        <v>0</v>
+      </c>
+      <c r="J31" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B32" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" s="46">
+        <v>23</v>
+      </c>
+      <c r="F32" s="46">
+        <v>7</v>
+      </c>
+      <c r="G32" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H32" s="47">
+        <v>5775</v>
+      </c>
+      <c r="I32" s="47">
+        <v>0</v>
+      </c>
+      <c r="J32" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B33" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" s="46">
+        <v>28</v>
+      </c>
+      <c r="F33" s="46">
+        <v>4</v>
+      </c>
+      <c r="G33" s="67" t="s">
+        <v>396</v>
+      </c>
+      <c r="H33" s="47">
+        <v>3300</v>
+      </c>
+      <c r="I33" s="47">
+        <v>0</v>
+      </c>
+      <c r="J33" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="E34" s="46">
+        <v>28</v>
+      </c>
+      <c r="F34" s="46">
+        <v>1</v>
+      </c>
+      <c r="G34" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H34" s="47">
+        <v>825</v>
+      </c>
+      <c r="I34" s="47">
+        <v>0</v>
+      </c>
+      <c r="J34" s="68" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="60" t="s">
+        <v>87</v>
+      </c>
+      <c r="E35" s="46">
+        <v>30</v>
+      </c>
+      <c r="F35" s="46">
+        <v>2</v>
+      </c>
+      <c r="G35" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H35" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I35" s="47">
+        <v>0</v>
+      </c>
+      <c r="J35" s="69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B36" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="E36" s="46">
+        <v>31</v>
+      </c>
+      <c r="F36" s="46">
+        <v>6</v>
+      </c>
+      <c r="G36" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H36" s="47">
+        <v>4950</v>
+      </c>
+      <c r="I36" s="47">
+        <v>0</v>
+      </c>
+      <c r="J36" s="69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="E37" s="46">
+        <v>31</v>
+      </c>
+      <c r="F37" s="46">
+        <v>2</v>
+      </c>
+      <c r="G37" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H37" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I37" s="47">
+        <v>0</v>
+      </c>
+      <c r="J37" s="69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B38" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="60" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38" s="46">
+        <v>32</v>
+      </c>
+      <c r="F38" s="46">
+        <v>2</v>
+      </c>
+      <c r="G38" s="67" t="s">
+        <v>393</v>
+      </c>
+      <c r="H38" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I38" s="47">
+        <v>0</v>
+      </c>
+      <c r="J38" s="69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B39" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="60" t="s">
+        <v>75</v>
+      </c>
+      <c r="E39" s="46">
+        <v>32</v>
+      </c>
+      <c r="F39" s="46">
+        <v>2</v>
+      </c>
+      <c r="G39" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H39" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I39" s="47">
+        <v>0</v>
+      </c>
+      <c r="J39" s="69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D40" s="60" t="s">
+        <v>130</v>
+      </c>
+      <c r="E40" s="46">
+        <v>38</v>
+      </c>
+      <c r="F40" s="46">
+        <v>2</v>
+      </c>
+      <c r="G40" s="67" t="s">
+        <v>393</v>
+      </c>
+      <c r="H40" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I40" s="47">
+        <v>0</v>
+      </c>
+      <c r="J40" s="69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41" s="60" t="s">
+        <v>130</v>
+      </c>
+      <c r="E41" s="46">
+        <v>38</v>
+      </c>
+      <c r="F41" s="46">
+        <v>2</v>
+      </c>
+      <c r="G41" s="67" t="s">
+        <v>393</v>
+      </c>
+      <c r="H41" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I41" s="47">
+        <v>0</v>
+      </c>
+      <c r="J41" s="69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" s="60" t="s">
+        <v>108</v>
+      </c>
+      <c r="E42" s="46">
+        <v>39</v>
+      </c>
+      <c r="F42" s="46">
+        <v>2</v>
+      </c>
+      <c r="G42" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H42" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I42" s="47">
+        <v>0</v>
+      </c>
+      <c r="J42" s="69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B43" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="60" t="s">
+        <v>108</v>
+      </c>
+      <c r="E43" s="46">
+        <v>39</v>
+      </c>
+      <c r="F43" s="46">
+        <v>2</v>
+      </c>
+      <c r="G43" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H43" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I43" s="47">
+        <v>0</v>
+      </c>
+      <c r="J43" s="69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B44" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="60" t="s">
+        <v>212</v>
+      </c>
+      <c r="E44" s="46">
+        <v>42</v>
+      </c>
+      <c r="F44" s="46">
+        <v>1</v>
+      </c>
+      <c r="G44" s="67" t="s">
+        <v>393</v>
+      </c>
+      <c r="H44" s="47">
+        <v>825</v>
+      </c>
+      <c r="I44" s="47">
+        <v>0</v>
+      </c>
+      <c r="J44" s="69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B45" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" s="60" t="s">
+        <v>214</v>
+      </c>
+      <c r="E45" s="46">
+        <v>46</v>
+      </c>
+      <c r="F45" s="46">
+        <v>1</v>
+      </c>
+      <c r="G45" s="67" t="s">
+        <v>393</v>
+      </c>
+      <c r="H45" s="47">
+        <v>825</v>
+      </c>
+      <c r="I45" s="47">
+        <v>0</v>
+      </c>
+      <c r="J45" s="69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="E46" s="46">
+        <v>47</v>
+      </c>
+      <c r="F46" s="46">
+        <v>2</v>
+      </c>
+      <c r="G46" s="67" t="s">
+        <v>393</v>
+      </c>
+      <c r="H46" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I46" s="47">
+        <v>0</v>
+      </c>
+      <c r="J46" s="69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B47" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="E47" s="46">
+        <v>50</v>
+      </c>
+      <c r="F47" s="46">
+        <v>2</v>
+      </c>
+      <c r="G47" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H47" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I47" s="47">
+        <v>0</v>
+      </c>
+      <c r="J47" s="69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B48" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" s="60" t="s">
+        <v>156</v>
+      </c>
+      <c r="E48" s="46">
+        <v>51</v>
+      </c>
+      <c r="F48" s="46">
+        <v>7</v>
+      </c>
+      <c r="G48" s="67" t="s">
+        <v>398</v>
+      </c>
+      <c r="H48" s="47">
+        <v>5775</v>
+      </c>
+      <c r="I48" s="47">
+        <v>0</v>
+      </c>
+      <c r="J48" s="69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B49" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="60" t="s">
+        <v>137</v>
+      </c>
+      <c r="E49" s="46">
+        <v>52</v>
+      </c>
+      <c r="F49" s="46">
+        <v>2</v>
+      </c>
+      <c r="G49" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H49" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I49" s="47">
+        <v>0</v>
+      </c>
+      <c r="J49" s="69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B50" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="60" t="s">
+        <v>216</v>
+      </c>
+      <c r="E50" s="46">
+        <v>53</v>
+      </c>
+      <c r="F50" s="46">
+        <v>2</v>
+      </c>
+      <c r="G50" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H50" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I50" s="47">
+        <v>0</v>
+      </c>
+      <c r="J50" s="69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B51" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" s="60" t="s">
+        <v>140</v>
+      </c>
+      <c r="E51" s="46">
+        <v>58</v>
+      </c>
+      <c r="F51" s="46">
+        <v>2</v>
+      </c>
+      <c r="G51" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H51" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I51" s="47">
+        <v>0</v>
+      </c>
+      <c r="J51" s="69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B52" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="60" t="s">
+        <v>111</v>
+      </c>
+      <c r="E52" s="46">
+        <v>59</v>
+      </c>
+      <c r="F52" s="46">
+        <v>3</v>
+      </c>
+      <c r="G52" s="67" t="s">
+        <v>396</v>
+      </c>
+      <c r="H52" s="47">
+        <v>2475</v>
+      </c>
+      <c r="I52" s="47">
+        <v>0</v>
+      </c>
+      <c r="J52" s="69" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B53" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D53" s="60" t="s">
+        <v>142</v>
+      </c>
+      <c r="E53" s="46">
+        <v>71</v>
+      </c>
+      <c r="F53" s="46">
+        <v>1</v>
+      </c>
+      <c r="G53" s="67" t="s">
+        <v>393</v>
+      </c>
+      <c r="H53" s="47">
+        <v>825</v>
+      </c>
+      <c r="I53" s="47">
+        <v>0</v>
+      </c>
+      <c r="J53" s="70" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B54" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54" s="60" t="s">
+        <v>179</v>
+      </c>
+      <c r="E54" s="46">
+        <v>74</v>
+      </c>
+      <c r="F54" s="46">
+        <v>3</v>
+      </c>
+      <c r="G54" s="67" t="s">
+        <v>393</v>
+      </c>
+      <c r="H54" s="47">
+        <v>2475</v>
+      </c>
+      <c r="I54" s="47">
+        <v>0</v>
+      </c>
+      <c r="J54" s="70" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B55" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D55" s="60" t="s">
+        <v>99</v>
+      </c>
+      <c r="E55" s="46">
+        <v>87</v>
+      </c>
+      <c r="F55" s="46">
+        <v>1</v>
+      </c>
+      <c r="G55" s="67" t="s">
+        <v>393</v>
+      </c>
+      <c r="H55" s="47">
+        <v>825</v>
+      </c>
+      <c r="I55" s="47">
+        <v>0</v>
+      </c>
+      <c r="J55" s="70" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B56" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" s="60" t="s">
+        <v>218</v>
+      </c>
+      <c r="E56" s="46">
+        <v>92</v>
+      </c>
+      <c r="F56" s="46">
+        <v>1</v>
+      </c>
+      <c r="G56" s="67" t="s">
+        <v>393</v>
+      </c>
+      <c r="H56" s="47">
+        <v>825</v>
+      </c>
+      <c r="I56" s="47">
+        <v>0</v>
+      </c>
+      <c r="J56" s="70" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B57" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D57" s="60" t="s">
+        <v>181</v>
+      </c>
+      <c r="E57" s="46">
+        <v>98</v>
+      </c>
+      <c r="F57" s="46">
+        <v>1</v>
+      </c>
+      <c r="G57" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H57" s="47">
+        <v>825</v>
+      </c>
+      <c r="I57" s="47">
+        <v>0</v>
+      </c>
+      <c r="J57" s="70" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B58" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D58" s="60" t="s">
+        <v>191</v>
+      </c>
+      <c r="E58" s="46">
+        <v>143</v>
+      </c>
+      <c r="F58" s="46">
+        <v>1</v>
+      </c>
+      <c r="G58" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H58" s="47">
+        <v>825</v>
+      </c>
+      <c r="I58" s="47">
+        <v>0</v>
+      </c>
+      <c r="J58" s="70" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B59" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D59" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="E59" s="46">
+        <v>28</v>
+      </c>
+      <c r="F59" s="46">
+        <v>2</v>
+      </c>
+      <c r="G59" s="67" t="s">
+        <v>393</v>
+      </c>
+      <c r="H59" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I59" s="71">
+        <v>4800</v>
+      </c>
+      <c r="J59" s="72" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B60" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D60" s="60" t="s">
+        <v>81</v>
+      </c>
+      <c r="E60" s="46">
+        <v>31</v>
+      </c>
+      <c r="F60" s="46">
+        <v>1</v>
+      </c>
+      <c r="G60" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H60" s="47">
+        <v>825</v>
+      </c>
+      <c r="I60" s="71">
+        <v>1800</v>
+      </c>
+      <c r="J60" s="72" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B61" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D61" s="60" t="s">
+        <v>106</v>
+      </c>
+      <c r="E61" s="46">
+        <v>79</v>
+      </c>
+      <c r="F61" s="46">
+        <v>1</v>
+      </c>
+      <c r="G61" s="67" t="s">
+        <v>393</v>
+      </c>
+      <c r="H61" s="47">
+        <v>825</v>
+      </c>
+      <c r="I61" s="71">
         <v>2400</v>
       </c>
-      <c r="I6" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="D7" s="49" t="s">
-        <v>231</v>
-      </c>
-      <c r="E7" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="F7" s="46">
-        <v>192</v>
-      </c>
-      <c r="G7" s="49" t="s">
-        <v>201</v>
-      </c>
-      <c r="H7" s="47">
-        <v>350</v>
-      </c>
-      <c r="I7" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="D8" s="49" t="s">
-        <v>252</v>
-      </c>
-      <c r="E8" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="F8" s="46">
-        <v>184</v>
-      </c>
-      <c r="G8" s="49" t="s">
-        <v>196</v>
-      </c>
-      <c r="H8" s="47">
-        <v>600</v>
-      </c>
-      <c r="I8" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="D9" s="49" t="s">
-        <v>252</v>
-      </c>
-      <c r="E9" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="F9" s="46">
-        <v>183</v>
-      </c>
-      <c r="G9" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="H9" s="47">
-        <v>350</v>
-      </c>
-      <c r="I9" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="D10" s="49" t="s">
-        <v>236</v>
-      </c>
-      <c r="E10" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="F10" s="46">
-        <v>178</v>
-      </c>
-      <c r="G10" s="49" t="s">
-        <v>122</v>
-      </c>
-      <c r="H10" s="47">
-        <v>5500</v>
-      </c>
-      <c r="I10" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="10" t="s">
+      <c r="J61" s="72" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B62" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C62" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="D11" s="49" t="s">
-        <v>241</v>
-      </c>
-      <c r="E11" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="F11" s="46">
-        <v>156</v>
-      </c>
-      <c r="G11" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="H11" s="47">
-        <v>2400</v>
-      </c>
-      <c r="I11" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>231</v>
-      </c>
-      <c r="E12" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="F12" s="46">
-        <v>156</v>
-      </c>
-      <c r="G12" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="H12" s="47">
-        <v>700</v>
-      </c>
-      <c r="I12" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="D13" s="49" t="s">
-        <v>252</v>
-      </c>
-      <c r="E13" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="F13" s="46">
-        <v>149</v>
-      </c>
-      <c r="G13" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="H13" s="47">
-        <v>600</v>
-      </c>
-      <c r="I13" s="47">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="D14" s="49" t="s">
-        <v>295</v>
-      </c>
-      <c r="E14" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="F14" s="46">
-        <v>143</v>
-      </c>
-      <c r="G14" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="H14" s="47">
-        <v>0</v>
-      </c>
-      <c r="I14" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="D15" s="49" t="s">
-        <v>251</v>
-      </c>
-      <c r="E15" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="F15" s="46">
-        <v>143</v>
-      </c>
-      <c r="G15" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="H15" s="47">
-        <v>600</v>
-      </c>
-      <c r="I15" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="D16" s="49" t="s">
-        <v>236</v>
-      </c>
-      <c r="E16" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="F16" s="46">
-        <v>136</v>
-      </c>
-      <c r="G16" s="49" t="s">
-        <v>188</v>
-      </c>
-      <c r="H16" s="47">
-        <v>600</v>
-      </c>
-      <c r="I16" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="D17" s="49" t="s">
-        <v>250</v>
-      </c>
-      <c r="E17" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="F17" s="46">
-        <v>135</v>
-      </c>
-      <c r="G17" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="H17" s="47">
-        <v>600</v>
-      </c>
-      <c r="I17" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" s="49" t="s">
-        <v>231</v>
-      </c>
-      <c r="E18" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="F18" s="46">
-        <v>120</v>
-      </c>
-      <c r="G18" s="49" t="s">
-        <v>98</v>
-      </c>
-      <c r="H18" s="47">
-        <v>9800</v>
-      </c>
-      <c r="I18" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="D19" s="49" t="s">
-        <v>247</v>
-      </c>
-      <c r="E19" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="F19" s="46">
-        <v>119</v>
-      </c>
-      <c r="G19" s="49" t="s">
-        <v>184</v>
-      </c>
-      <c r="H19" s="47">
-        <v>600</v>
-      </c>
-      <c r="I19" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="D20" s="49" t="s">
-        <v>248</v>
-      </c>
-      <c r="E20" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="F20" s="46">
-        <v>114</v>
-      </c>
-      <c r="G20" s="49" t="s">
-        <v>165</v>
-      </c>
-      <c r="H20" s="47">
-        <v>1200</v>
-      </c>
-      <c r="I20" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="49" t="s">
-        <v>230</v>
-      </c>
-      <c r="E21" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="F21" s="46">
-        <v>108</v>
-      </c>
-      <c r="G21" s="49" t="s">
-        <v>95</v>
-      </c>
-      <c r="H21" s="47">
-        <v>10200</v>
-      </c>
-      <c r="I21" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="D22" s="49" t="s">
-        <v>230</v>
-      </c>
-      <c r="E22" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="F22" s="46">
-        <v>98</v>
-      </c>
-      <c r="G22" s="49" t="s">
-        <v>181</v>
-      </c>
-      <c r="H22" s="47">
-        <v>600</v>
-      </c>
-      <c r="I22" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="D23" s="49" t="s">
-        <v>301</v>
-      </c>
-      <c r="E23" s="49" t="s">
-        <v>279</v>
-      </c>
-      <c r="F23" s="46">
-        <v>92</v>
-      </c>
-      <c r="G23" s="49" t="s">
-        <v>218</v>
-      </c>
-      <c r="H23" s="47">
-        <v>0</v>
-      </c>
-      <c r="I23" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="D24" s="49" t="s">
-        <v>241</v>
-      </c>
-      <c r="E24" s="49" t="s">
-        <v>269</v>
-      </c>
-      <c r="F24" s="46">
-        <v>87</v>
-      </c>
-      <c r="G24" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="H24" s="47">
-        <v>2400</v>
-      </c>
-      <c r="I24" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B25" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>178</v>
-      </c>
-      <c r="D25" s="49" t="s">
-        <v>230</v>
-      </c>
-      <c r="E25" s="49" t="s">
-        <v>269</v>
-      </c>
-      <c r="F25" s="46">
-        <v>74</v>
-      </c>
-      <c r="G25" s="49" t="s">
-        <v>179</v>
-      </c>
-      <c r="H25" s="47">
-        <v>600</v>
-      </c>
-      <c r="I25" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B26" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="D26" s="49" t="s">
-        <v>241</v>
-      </c>
-      <c r="E26" s="49" t="s">
-        <v>269</v>
-      </c>
-      <c r="F26" s="46">
-        <v>71</v>
-      </c>
-      <c r="G26" s="49" t="s">
-        <v>142</v>
-      </c>
-      <c r="H26" s="47">
-        <v>4800</v>
-      </c>
-      <c r="I26" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="10" t="s">
+      <c r="D62" s="60" t="s">
+        <v>238</v>
+      </c>
+      <c r="E62" s="46">
         <v>175</v>
       </c>
-      <c r="D27" s="49" t="s">
-        <v>231</v>
-      </c>
-      <c r="E27" s="49" t="s">
-        <v>269</v>
-      </c>
-      <c r="F27" s="46">
-        <v>65</v>
-      </c>
-      <c r="G27" s="49" t="s">
-        <v>176</v>
-      </c>
-      <c r="H27" s="47">
-        <v>600</v>
-      </c>
-      <c r="I27" s="47">
-        <v>0</v>
-      </c>
+      <c r="F62" s="46">
+        <v>3</v>
+      </c>
+      <c r="G62" s="67" t="s">
+        <v>395</v>
+      </c>
+      <c r="H62" s="47">
+        <v>2475</v>
+      </c>
+      <c r="I62" s="71">
+        <v>1800</v>
+      </c>
+      <c r="J62" s="72" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B65" s="66" t="s">
+        <v>401</v>
+      </c>
+      <c r="C65" s="66"/>
+      <c r="D65" s="66"/>
+      <c r="E65" s="66"/>
+      <c r="F65" s="66"/>
+      <c r="G65" s="66"/>
+      <c r="H65" s="66"/>
+      <c r="I65" s="66"/>
+      <c r="J65" s="66"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:H2"/>
+  <mergeCells count="15">
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="D7:E8"/>
+    <mergeCell ref="F7:G8"/>
+    <mergeCell ref="H7:I8"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="D11:E12"/>
+    <mergeCell ref="B65:J65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/activity/WEEKLY_RECAP_REP.xlsx
+++ b/activity/WEEKLY_RECAP_REP.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3076" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3475" uniqueCount="725">
   <si>
     <t>Weekly Rep Recap</t>
   </si>
@@ -1165,10 +1165,10 @@
     <t>Cash and revenue move on different clocks: invoiced revenue is when the sale was booked, cash collected is when the money arrived. Amber Free cells = free rate over 25% of that month's total.</t>
   </si>
   <si>
-    <t>Free Vial Watch — sampling ROI</t>
-  </si>
-  <si>
-    <t>Every clinic that took a $0 vial (any promo: SAMPLE26, FREE_VIALS, RES-CENTA, EMTNSTUDY, or uncoded). "Converted" = they placed a paid order after their most recent free order.</t>
+    <t>Free Vial Watch | Customer-acquisition samples</t>
+  </si>
+  <si>
+    <t>SAMPLE26 and FREE_VIALS only. Clinical/research and uncoded giveaways are excluded. "Converted" means a later non-research paid order was booked; this is not proof of a new customer or of sample-caused revenue.</t>
   </si>
   <si>
     <t>Clinics Sampled</t>
@@ -1189,6 +1189,9 @@
     <t>Revenue from Converted</t>
   </si>
   <si>
+    <t>Reported Invoice COGS</t>
+  </si>
+  <si>
     <t>Last Free Order</t>
   </si>
   <si>
@@ -1198,10 +1201,13 @@
     <t>List Value</t>
   </si>
   <si>
+    <t>Invoice COGS</t>
+  </si>
+  <si>
     <t>Paid After</t>
   </si>
   <si>
-    <t>SAMPLE26, FREE_VIALS, RES-CENTA</t>
+    <t>SAMPLE26, FREE_VIALS</t>
   </si>
   <si>
     <t>Still in window</t>
@@ -1210,21 +1216,6 @@
     <t>FREE_VIALS</t>
   </si>
   <si>
-    <t>SAMPLE26, FREE_VIALS</t>
-  </si>
-  <si>
-    <t>MAINTAIN_LAUNCH</t>
-  </si>
-  <si>
-    <t>RES-CENTA</t>
-  </si>
-  <si>
-    <t>SAMPLE26, RES-CENTA</t>
-  </si>
-  <si>
-    <t>FREE_VIALS, SAMPLE26, MAINTAIN_LAUNCH</t>
-  </si>
-  <si>
     <t>FREE_VIALS, SAMPLE26</t>
   </si>
   <si>
@@ -1237,13 +1228,265 @@
     <t>Close out</t>
   </si>
   <si>
-    <t>EMTNSTUDY</t>
-  </si>
-  <si>
     <t>Converted</t>
   </si>
   <si>
-    <t>Follow-up windows: 0–29 days = still in window · 30–59 days = last call this month · 60+ days = close out, no follow-up worked. List value = vials × $825 (approx per-vial list price).</t>
+    <t>TOTALS</t>
+  </si>
+  <si>
+    <t>List value and COGS come from the invoice, not an assumed per-vial price. Reported COGS may include shipping. Shipping below is informational only; it is not added again. No estimated shipping is used. Follow-up windows: 0–29 / 30–59 / 60+ days.</t>
+  </si>
+  <si>
+    <t>Each free-sample order | Invoice-recorded list value and COGS</t>
+  </si>
+  <si>
+    <t>Invoice #</t>
+  </si>
+  <si>
+    <t>Invoice date</t>
+  </si>
+  <si>
+    <t>Promo code</t>
+  </si>
+  <si>
+    <t>List value ($)</t>
+  </si>
+  <si>
+    <t>Invoice COGS ($)</t>
+  </si>
+  <si>
+    <t>Net shipping ($)</t>
+  </si>
+  <si>
+    <t>Source note</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1069</t>
+  </si>
+  <si>
+    <t>Invoice matched</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1198</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1211</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1266</t>
+  </si>
+  <si>
+    <t>Not in promo export</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1065</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1270</t>
+  </si>
+  <si>
+    <t>Not in promo export; $0 COGS reported</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1131</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1269</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1181</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1264</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1258</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1155</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1247</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1245</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1142</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1238</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1177</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1235</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1233</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1076</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1222</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1220</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1219</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1216</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1213</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1209</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1109</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1203</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1208</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1205</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1081</t>
+  </si>
+  <si>
+    <t>2026-05-05</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1200</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1196</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1105</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1190</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1188</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1184</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1179</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1169</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1175</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1173</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1168</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1163</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1162</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1160</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1156</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1154</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1145</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1143</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1133</t>
+  </si>
+  <si>
+    <t>2026-07-03</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1139</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1080</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1128</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1116</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1114</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1111</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1227</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1096</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1165</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1224</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1225</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1113</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1201</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1187</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1151</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1125</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1122</t>
+  </si>
+  <si>
+    <t>CINV-EPL-1016</t>
+  </si>
+  <si>
+    <t>ORDER TOTALS</t>
+  </si>
+  <si>
+    <t>Source reconciliation: this sheet uses the Invoice List. 5 sample order(s) are absent from the Promo Usage export and remain included here. This can differ from Promo Analysis totals. Reported $0 COGS is shown as supplied, not estimated.</t>
   </si>
   <si>
     <t>Outstanding Balances (Aging)</t>
@@ -1961,10 +2204,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0;(&quot;$&quot;#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00;(&quot;$&quot;#,##0.00);&quot;$&quot;0.00"/>
   </numFmts>
   <fonts count="33" x14ac:knownFonts="1">
     <font>
@@ -2251,7 +2496,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -2439,8 +2684,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2456,6 +2707,22 @@
     </xf>
     <xf numFmtId="0" fontId="32" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -3581,7 +3848,7 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="29" t="s">
-        <v>407</v>
+        <v>488</v>
       </c>
       <c r="C2" s="29"/>
       <c r="D2" s="29"/>
@@ -3594,7 +3861,7 @@
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
-        <v>408</v>
+        <v>489</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -3619,19 +3886,19 @@
         <v>9</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>409</v>
+        <v>490</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>51</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>410</v>
+        <v>491</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>57</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>411</v>
+        <v>492</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
@@ -3659,8 +3926,8 @@
       <c r="I6" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="J6" s="69" t="s">
-        <v>412</v>
+      <c r="J6" s="71" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
@@ -3688,8 +3955,8 @@
       <c r="I7" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="J7" s="69" t="s">
-        <v>412</v>
+      <c r="J7" s="71" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.25">
@@ -3717,8 +3984,8 @@
       <c r="I8" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="J8" s="69" t="s">
-        <v>412</v>
+      <c r="J8" s="71" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
@@ -3746,8 +4013,8 @@
       <c r="I9" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="J9" s="69" t="s">
-        <v>412</v>
+      <c r="J9" s="71" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
@@ -3775,8 +4042,8 @@
       <c r="I10" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="J10" s="69" t="s">
-        <v>412</v>
+      <c r="J10" s="71" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
@@ -3804,8 +4071,8 @@
       <c r="I11" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="J11" s="69" t="s">
-        <v>412</v>
+      <c r="J11" s="71" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
@@ -3833,8 +4100,8 @@
       <c r="I12" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="J12" s="69" t="s">
-        <v>412</v>
+      <c r="J12" s="71" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
@@ -3862,8 +4129,8 @@
       <c r="I13" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="J13" s="69" t="s">
-        <v>412</v>
+      <c r="J13" s="71" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
@@ -3891,8 +4158,8 @@
       <c r="I14" s="49" t="s">
         <v>133</v>
       </c>
-      <c r="J14" s="69" t="s">
-        <v>412</v>
+      <c r="J14" s="71" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
@@ -3920,8 +4187,8 @@
       <c r="I15" s="49" t="s">
         <v>115</v>
       </c>
-      <c r="J15" s="69" t="s">
-        <v>412</v>
+      <c r="J15" s="71" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
@@ -3949,8 +4216,8 @@
       <c r="I16" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="J16" s="69" t="s">
-        <v>412</v>
+      <c r="J16" s="71" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
@@ -3978,8 +4245,8 @@
       <c r="I17" s="49" t="s">
         <v>73</v>
       </c>
-      <c r="J17" s="68" t="s">
-        <v>413</v>
+      <c r="J17" s="70" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
@@ -4007,8 +4274,8 @@
       <c r="I18" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="J18" s="68" t="s">
-        <v>413</v>
+      <c r="J18" s="70" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
@@ -4036,8 +4303,8 @@
       <c r="I19" s="49" t="s">
         <v>115</v>
       </c>
-      <c r="J19" s="68" t="s">
-        <v>413</v>
+      <c r="J19" s="70" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
@@ -4065,8 +4332,8 @@
       <c r="I20" s="49" t="s">
         <v>73</v>
       </c>
-      <c r="J20" s="68" t="s">
-        <v>413</v>
+      <c r="J20" s="70" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
@@ -4094,8 +4361,8 @@
       <c r="I21" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="J21" s="68" t="s">
-        <v>413</v>
+      <c r="J21" s="70" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
@@ -4123,8 +4390,8 @@
       <c r="I22" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="J22" s="68" t="s">
-        <v>413</v>
+      <c r="J22" s="70" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
@@ -4152,8 +4419,8 @@
       <c r="I23" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="J23" s="68" t="s">
-        <v>413</v>
+      <c r="J23" s="70" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
@@ -4181,8 +4448,8 @@
       <c r="I24" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="J24" s="68" t="s">
-        <v>413</v>
+      <c r="J24" s="70" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
@@ -4210,8 +4477,8 @@
       <c r="I25" s="49" t="s">
         <v>131</v>
       </c>
-      <c r="J25" s="68" t="s">
-        <v>413</v>
+      <c r="J25" s="70" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
@@ -4239,8 +4506,8 @@
       <c r="I26" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="J26" s="70" t="s">
-        <v>414</v>
+      <c r="J26" s="72" t="s">
+        <v>495</v>
       </c>
     </row>
   </sheetData>
@@ -4263,7 +4530,7 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="29" t="s">
-        <v>415</v>
+        <v>496</v>
       </c>
       <c r="C2" s="29"/>
       <c r="D2" s="29"/>
@@ -4286,7 +4553,7 @@
         <v>264</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>410</v>
+        <v>491</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>57</v>
@@ -5045,46 +5312,46 @@
         <v>259</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>416</v>
+        <v>497</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>417</v>
+        <v>498</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>220</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>418</v>
+        <v>499</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>419</v>
+        <v>500</v>
       </c>
       <c r="G1" s="9" t="s">
         <v>222</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>420</v>
+        <v>501</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>421</v>
+        <v>502</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>223</v>
       </c>
       <c r="K1" s="9" t="s">
-        <v>422</v>
+        <v>503</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>423</v>
+        <v>504</v>
       </c>
       <c r="M1" s="9" t="s">
         <v>9</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>424</v>
+        <v>505</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>425</v>
+        <v>506</v>
       </c>
       <c r="P1" s="9" t="s">
         <v>225</v>
@@ -5098,7 +5365,7 @@
         <v>63</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>426</v>
+        <v>507</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>227</v>
@@ -5148,7 +5415,7 @@
         <v>69</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>427</v>
+        <v>508</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>227</v>
@@ -5198,7 +5465,7 @@
         <v>83</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>428</v>
+        <v>509</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>232</v>
@@ -5245,10 +5512,10 @@
         <v>132</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>429</v>
+        <v>510</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>430</v>
+        <v>511</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>242</v>
@@ -5295,10 +5562,10 @@
         <v>126</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>431</v>
+        <v>512</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>432</v>
+        <v>513</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>242</v>
@@ -5345,10 +5612,10 @@
         <v>110</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>433</v>
+        <v>514</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>434</v>
+        <v>515</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>242</v>
@@ -5395,10 +5662,10 @@
         <v>102</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>435</v>
+        <v>516</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>436</v>
+        <v>517</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>233</v>
@@ -5448,7 +5715,7 @@
         <v>111</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>437</v>
+        <v>518</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>238</v>
@@ -5495,10 +5762,10 @@
         <v>160</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>438</v>
+        <v>519</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>439</v>
+        <v>520</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>226</v>
@@ -5545,10 +5812,10 @@
         <v>202</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>440</v>
+        <v>521</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>441</v>
+        <v>522</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>232</v>
@@ -5595,10 +5862,10 @@
         <v>161</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>442</v>
+        <v>523</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>443</v>
+        <v>524</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>238</v>
@@ -5645,10 +5912,10 @@
         <v>72</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>444</v>
+        <v>525</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>445</v>
+        <v>526</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>227</v>
@@ -5695,10 +5962,10 @@
         <v>84</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>446</v>
+        <v>527</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>447</v>
+        <v>528</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>248</v>
@@ -5745,10 +6012,10 @@
         <v>76</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>448</v>
+        <v>529</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>449</v>
+        <v>530</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>293</v>
@@ -5795,10 +6062,10 @@
         <v>97</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>450</v>
+        <v>531</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>451</v>
+        <v>532</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>294</v>
@@ -5845,10 +6112,10 @@
         <v>114</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>452</v>
+        <v>533</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>453</v>
+        <v>534</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>270</v>
@@ -5895,10 +6162,10 @@
         <v>142</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>454</v>
+        <v>535</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>455</v>
+        <v>536</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>293</v>
@@ -5945,10 +6212,10 @@
         <v>203</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>456</v>
+        <v>537</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>457</v>
+        <v>538</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>238</v>
@@ -5995,10 +6262,10 @@
         <v>107</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>458</v>
+        <v>539</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>459</v>
+        <v>540</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>238</v>
@@ -6045,10 +6312,10 @@
         <v>75</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>460</v>
+        <v>541</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>461</v>
+        <v>542</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>227</v>
@@ -6095,10 +6362,10 @@
         <v>144</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>462</v>
+        <v>543</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>463</v>
+        <v>544</v>
       </c>
       <c r="D22" s="10" t="s">
         <v>271</v>
@@ -6145,10 +6412,10 @@
         <v>168</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>464</v>
+        <v>545</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>465</v>
+        <v>546</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>249</v>
@@ -6198,7 +6465,7 @@
         <v>108</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>466</v>
+        <v>547</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>227</v>
@@ -6245,10 +6512,10 @@
         <v>204</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>467</v>
+        <v>548</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>468</v>
+        <v>549</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>227</v>
@@ -6295,10 +6562,10 @@
         <v>206</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>469</v>
+        <v>550</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>470</v>
+        <v>551</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>296</v>
@@ -6345,10 +6612,10 @@
         <v>120</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>471</v>
+        <v>552</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>472</v>
+        <v>553</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>227</v>
@@ -6398,7 +6665,7 @@
         <v>117</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>473</v>
+        <v>554</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>241</v>
@@ -6445,10 +6712,10 @@
         <v>207</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>474</v>
+        <v>555</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>475</v>
+        <v>556</v>
       </c>
       <c r="D29" s="10" t="s">
         <v>271</v>
@@ -6495,10 +6762,10 @@
         <v>169</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>476</v>
+        <v>557</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>477</v>
+        <v>558</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>238</v>
@@ -6548,7 +6815,7 @@
         <v>81</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>478</v>
+        <v>559</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>293</v>
@@ -6595,10 +6862,10 @@
         <v>143</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>479</v>
+        <v>560</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>480</v>
+        <v>561</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>227</v>
@@ -6648,7 +6915,7 @@
         <v>60</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>481</v>
+        <v>562</v>
       </c>
       <c r="D33" s="10" t="s">
         <v>226</v>
@@ -6698,7 +6965,7 @@
         <v>118</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>482</v>
+        <v>563</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>248</v>
@@ -6748,7 +7015,7 @@
         <v>86</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>483</v>
+        <v>564</v>
       </c>
       <c r="D35" s="10" t="s">
         <v>293</v>
@@ -6795,10 +7062,10 @@
         <v>157</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>484</v>
+        <v>565</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>485</v>
+        <v>566</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>245</v>
@@ -6845,10 +7112,10 @@
         <v>172</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>486</v>
+        <v>567</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>487</v>
+        <v>568</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>300</v>
@@ -6895,10 +7162,10 @@
         <v>88</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>488</v>
+        <v>569</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>489</v>
+        <v>570</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>233</v>
@@ -6945,10 +7212,10 @@
         <v>208</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>490</v>
+        <v>571</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>491</v>
+        <v>572</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>248</v>
@@ -6995,10 +7262,10 @@
         <v>78</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>492</v>
+        <v>573</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>493</v>
+        <v>574</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>227</v>
@@ -7045,10 +7312,10 @@
         <v>146</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>494</v>
+        <v>575</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>495</v>
+        <v>576</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>238</v>
@@ -7095,10 +7362,10 @@
         <v>100</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>496</v>
+        <v>577</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>497</v>
+        <v>578</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>227</v>
@@ -7145,10 +7412,10 @@
         <v>209</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>498</v>
+        <v>579</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>499</v>
+        <v>580</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>233</v>
@@ -7195,10 +7462,10 @@
         <v>66</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>500</v>
+        <v>581</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>501</v>
+        <v>582</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>227</v>
@@ -7245,10 +7512,10 @@
         <v>122</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>502</v>
+        <v>583</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>503</v>
+        <v>584</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>227</v>
@@ -7298,7 +7565,7 @@
         <v>173</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>504</v>
+        <v>585</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>274</v>
@@ -7345,10 +7612,10 @@
         <v>134</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>505</v>
+        <v>586</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>506</v>
+        <v>587</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>226</v>
@@ -7395,10 +7662,10 @@
         <v>174</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>507</v>
+        <v>588</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>508</v>
+        <v>589</v>
       </c>
       <c r="D48" s="10" t="s">
         <v>227</v>
@@ -7445,10 +7712,10 @@
         <v>210</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>509</v>
+        <v>590</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>510</v>
+        <v>591</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>226</v>
@@ -7495,10 +7762,10 @@
         <v>136</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>511</v>
+        <v>592</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>512</v>
+        <v>593</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>227</v>
@@ -7545,10 +7812,10 @@
         <v>138</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>513</v>
+        <v>594</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>514</v>
+        <v>595</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>227</v>
@@ -7595,10 +7862,10 @@
         <v>105</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>515</v>
+        <v>596</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>516</v>
+        <v>597</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>233</v>
@@ -7645,10 +7912,10 @@
         <v>211</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>517</v>
+        <v>598</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>518</v>
+        <v>599</v>
       </c>
       <c r="D53" s="10" t="s">
         <v>302</v>
@@ -7695,10 +7962,10 @@
         <v>128</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>519</v>
+        <v>600</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>520</v>
+        <v>601</v>
       </c>
       <c r="D54" s="10" t="s">
         <v>226</v>
@@ -7745,10 +8012,10 @@
         <v>163</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>521</v>
+        <v>602</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>522</v>
+        <v>603</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>242</v>
@@ -7798,7 +8065,7 @@
         <v>153</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>523</v>
+        <v>604</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>227</v>
@@ -7848,7 +8115,7 @@
         <v>156</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>524</v>
+        <v>605</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>293</v>
@@ -7895,10 +8162,10 @@
         <v>139</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>525</v>
+        <v>606</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>526</v>
+        <v>607</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>244</v>
@@ -7945,10 +8212,10 @@
         <v>213</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>527</v>
+        <v>608</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>528</v>
+        <v>609</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>275</v>
@@ -7995,10 +8262,10 @@
         <v>175</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>529</v>
+        <v>610</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>530</v>
+        <v>611</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>227</v>
@@ -8045,10 +8312,10 @@
         <v>130</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>531</v>
+        <v>612</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>532</v>
+        <v>613</v>
       </c>
       <c r="D61" s="10" t="s">
         <v>238</v>
@@ -8095,10 +8362,10 @@
         <v>178</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>533</v>
+        <v>614</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>534</v>
+        <v>615</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>226</v>
@@ -8145,10 +8412,10 @@
         <v>147</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>535</v>
+        <v>616</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>536</v>
+        <v>617</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>238</v>
@@ -8195,10 +8462,10 @@
         <v>215</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>537</v>
+        <v>618</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>538</v>
+        <v>619</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>302</v>
@@ -8245,10 +8512,10 @@
         <v>180</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>539</v>
+        <v>620</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>540</v>
+        <v>621</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>226</v>
@@ -8295,10 +8562,10 @@
         <v>91</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>541</v>
+        <v>622</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>542</v>
+        <v>623</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>226</v>
@@ -8345,10 +8612,10 @@
         <v>164</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>543</v>
+        <v>624</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>544</v>
+        <v>625</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>246</v>
@@ -8395,10 +8662,10 @@
         <v>183</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>545</v>
+        <v>626</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>546</v>
+        <v>627</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>245</v>
@@ -8445,10 +8712,10 @@
         <v>94</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>547</v>
+        <v>628</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>548</v>
+        <v>629</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>227</v>
@@ -8495,10 +8762,10 @@
         <v>185</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>549</v>
+        <v>630</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>550</v>
+        <v>631</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>248</v>
@@ -8545,10 +8812,10 @@
         <v>187</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>551</v>
+        <v>632</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>516</v>
+        <v>597</v>
       </c>
       <c r="D71" s="10" t="s">
         <v>233</v>
@@ -8598,7 +8865,7 @@
         <v>200</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>552</v>
+        <v>633</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>296</v>
@@ -8645,10 +8912,10 @@
         <v>190</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>553</v>
+        <v>634</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>554</v>
+        <v>635</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>249</v>
@@ -8695,10 +8962,10 @@
         <v>193</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>555</v>
+        <v>636</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>556</v>
+        <v>637</v>
       </c>
       <c r="D74" s="10" t="s">
         <v>242</v>
@@ -8745,10 +9012,10 @@
         <v>149</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>535</v>
+        <v>616</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>557</v>
+        <v>638</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>238</v>
@@ -8795,10 +9062,10 @@
         <v>167</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>558</v>
+        <v>639</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>559</v>
+        <v>640</v>
       </c>
       <c r="D76" s="10" t="s">
         <v>227</v>
@@ -8845,10 +9112,10 @@
         <v>123</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>560</v>
+        <v>641</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>561</v>
+        <v>642</v>
       </c>
       <c r="D77" s="10" t="s">
         <v>233</v>
@@ -8895,10 +9162,10 @@
         <v>194</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>562</v>
+        <v>643</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>563</v>
+        <v>644</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>242</v>
@@ -8945,10 +9212,10 @@
         <v>197</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>564</v>
+        <v>645</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>565</v>
+        <v>646</v>
       </c>
       <c r="D79" s="10" t="s">
         <v>227</v>
@@ -8998,7 +9265,7 @@
         <v>150</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>566</v>
+        <v>647</v>
       </c>
       <c r="D80" s="10" t="s">
         <v>293</v>
@@ -9048,7 +9315,7 @@
         <v>305</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>567</v>
+        <v>648</v>
       </c>
       <c r="D81" s="10" t="s">
         <v>306</v>
@@ -9094,7 +9361,7 @@
         <v>307</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>568</v>
+        <v>649</v>
       </c>
       <c r="D82" s="10" t="s">
         <v>293</v>
@@ -9137,10 +9404,10 @@
         <v>278</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>569</v>
+        <v>650</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>570</v>
+        <v>651</v>
       </c>
       <c r="D83" s="10" t="s">
         <v>274</v>
@@ -9186,7 +9453,7 @@
         <v>308</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>571</v>
+        <v>652</v>
       </c>
       <c r="D84" s="10" t="s">
         <v>293</v>
@@ -9229,10 +9496,10 @@
         <v>280</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>572</v>
+        <v>653</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>573</v>
+        <v>654</v>
       </c>
       <c r="D85" s="10" t="s">
         <v>271</v>
@@ -9275,10 +9542,10 @@
         <v>309</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>574</v>
+        <v>655</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>575</v>
+        <v>656</v>
       </c>
       <c r="D86" s="10" t="s">
         <v>310</v>
@@ -9321,10 +9588,10 @@
         <v>281</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>576</v>
+        <v>657</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>577</v>
+        <v>658</v>
       </c>
       <c r="D87" s="10" t="s">
         <v>282</v>
@@ -9367,10 +9634,10 @@
         <v>311</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>578</v>
+        <v>659</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>579</v>
+        <v>660</v>
       </c>
       <c r="D88" s="10" t="s">
         <v>300</v>
@@ -9413,10 +9680,10 @@
         <v>283</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>580</v>
+        <v>661</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>581</v>
+        <v>662</v>
       </c>
       <c r="D89" s="10" t="s">
         <v>226</v>
@@ -9459,10 +9726,10 @@
         <v>284</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>582</v>
+        <v>663</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>583</v>
+        <v>664</v>
       </c>
       <c r="D90" s="10" t="s">
         <v>246</v>
@@ -9505,10 +9772,10 @@
         <v>312</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>584</v>
+        <v>665</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>585</v>
+        <v>666</v>
       </c>
       <c r="D91" s="10" t="s">
         <v>293</v>
@@ -9551,10 +9818,10 @@
         <v>313</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>586</v>
+        <v>667</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>587</v>
+        <v>668</v>
       </c>
       <c r="D92" s="10" t="s">
         <v>314</v>
@@ -9597,10 +9864,10 @@
         <v>315</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>588</v>
+        <v>669</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>589</v>
+        <v>670</v>
       </c>
       <c r="D93" s="10" t="s">
         <v>232</v>
@@ -9643,10 +9910,10 @@
         <v>316</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>590</v>
+        <v>671</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>591</v>
+        <v>672</v>
       </c>
       <c r="D94" s="10" t="s">
         <v>293</v>
@@ -9689,10 +9956,10 @@
         <v>285</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>592</v>
+        <v>673</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>593</v>
+        <v>674</v>
       </c>
       <c r="D95" s="10" t="s">
         <v>227</v>
@@ -9735,10 +10002,10 @@
         <v>286</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>594</v>
+        <v>675</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>595</v>
+        <v>676</v>
       </c>
       <c r="D96" s="10" t="s">
         <v>249</v>
@@ -9781,10 +10048,10 @@
         <v>317</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>596</v>
+        <v>677</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>597</v>
+        <v>678</v>
       </c>
       <c r="D97" s="10" t="s">
         <v>318</v>
@@ -9827,10 +10094,10 @@
         <v>319</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>598</v>
+        <v>679</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>599</v>
+        <v>680</v>
       </c>
       <c r="D98" s="10" t="s">
         <v>310</v>
@@ -9873,10 +10140,10 @@
         <v>320</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>600</v>
+        <v>681</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>601</v>
+        <v>682</v>
       </c>
       <c r="D99" s="10" t="s">
         <v>294</v>
@@ -9919,10 +10186,10 @@
         <v>321</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>602</v>
+        <v>683</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>603</v>
+        <v>684</v>
       </c>
       <c r="D100" s="10" t="s">
         <v>232</v>
@@ -9965,10 +10232,10 @@
         <v>150</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>604</v>
+        <v>685</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>605</v>
+        <v>686</v>
       </c>
       <c r="D101" s="10" t="s">
         <v>293</v>
@@ -10011,10 +10278,10 @@
         <v>287</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>606</v>
+        <v>687</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>607</v>
+        <v>688</v>
       </c>
       <c r="D102" s="10" t="s">
         <v>274</v>
@@ -10057,10 +10324,10 @@
         <v>288</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>608</v>
+        <v>689</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>609</v>
+        <v>690</v>
       </c>
       <c r="D103" s="10" t="s">
         <v>233</v>
@@ -10103,10 +10370,10 @@
         <v>322</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>610</v>
+        <v>691</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>611</v>
+        <v>692</v>
       </c>
       <c r="D104" s="10" t="s">
         <v>226</v>
@@ -10149,10 +10416,10 @@
         <v>323</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>612</v>
+        <v>693</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>613</v>
+        <v>694</v>
       </c>
       <c r="D105" s="10" t="s">
         <v>314</v>
@@ -10195,10 +10462,10 @@
         <v>324</v>
       </c>
       <c r="B106" s="10" t="s">
-        <v>614</v>
+        <v>695</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>615</v>
+        <v>696</v>
       </c>
       <c r="D106" s="10" t="s">
         <v>293</v>
@@ -10241,10 +10508,10 @@
         <v>325</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>616</v>
+        <v>697</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>617</v>
+        <v>698</v>
       </c>
       <c r="D107" s="10" t="s">
         <v>293</v>
@@ -10287,10 +10554,10 @@
         <v>326</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>618</v>
+        <v>699</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>619</v>
+        <v>700</v>
       </c>
       <c r="D108" s="10" t="s">
         <v>327</v>
@@ -10333,10 +10600,10 @@
         <v>289</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>620</v>
+        <v>701</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>621</v>
+        <v>702</v>
       </c>
       <c r="D109" s="10" t="s">
         <v>233</v>
@@ -10379,10 +10646,10 @@
         <v>328</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>622</v>
+        <v>703</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>623</v>
+        <v>704</v>
       </c>
       <c r="D110" s="10" t="s">
         <v>329</v>
@@ -10425,10 +10692,10 @@
         <v>330</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>624</v>
+        <v>705</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>625</v>
+        <v>706</v>
       </c>
       <c r="D111" s="10" t="s">
         <v>331</v>
@@ -10471,10 +10738,10 @@
         <v>332</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>626</v>
+        <v>707</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>627</v>
+        <v>708</v>
       </c>
       <c r="D112" s="10" t="s">
         <v>244</v>
@@ -10528,7 +10795,7 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="29" t="s">
-        <v>628</v>
+        <v>709</v>
       </c>
       <c r="C2" s="29"/>
       <c r="D2" s="29"/>
@@ -10538,208 +10805,208 @@
       <c r="H2" s="29"/>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="73" t="s">
-        <v>629</v>
-      </c>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
+      <c r="B4" s="83" t="s">
+        <v>710</v>
+      </c>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="74" t="s">
-        <v>630</v>
-      </c>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
+      <c r="B5" s="84" t="s">
+        <v>711</v>
+      </c>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="74" t="s">
-        <v>631</v>
-      </c>
-      <c r="C6" s="74"/>
-      <c r="D6" s="74"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
-      <c r="I6" s="74"/>
+      <c r="B6" s="84" t="s">
+        <v>712</v>
+      </c>
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="84"/>
+      <c r="I6" s="84"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="74" t="s">
+      <c r="B7" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="74"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="74"/>
-      <c r="G7" s="74"/>
-      <c r="H7" s="74"/>
-      <c r="I7" s="74"/>
+      <c r="C7" s="84"/>
+      <c r="D7" s="84"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="84"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="74" t="s">
-        <v>632</v>
-      </c>
-      <c r="C8" s="74"/>
-      <c r="D8" s="74"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="74"/>
-      <c r="G8" s="74"/>
-      <c r="H8" s="74"/>
-      <c r="I8" s="74"/>
+      <c r="B8" s="84" t="s">
+        <v>713</v>
+      </c>
+      <c r="C8" s="84"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
+      <c r="F8" s="84"/>
+      <c r="G8" s="84"/>
+      <c r="H8" s="84"/>
+      <c r="I8" s="84"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="74" t="s">
-        <v>633</v>
-      </c>
-      <c r="C9" s="74"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
+      <c r="B9" s="84" t="s">
+        <v>714</v>
+      </c>
+      <c r="C9" s="84"/>
+      <c r="D9" s="84"/>
+      <c r="E9" s="84"/>
+      <c r="F9" s="84"/>
+      <c r="G9" s="84"/>
+      <c r="H9" s="84"/>
+      <c r="I9" s="84"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="74" t="s">
+      <c r="B10" s="84" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="74"/>
+      <c r="C10" s="84"/>
+      <c r="D10" s="84"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="84"/>
+      <c r="G10" s="84"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="84"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="73" t="s">
-        <v>634</v>
-      </c>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="73"/>
-      <c r="I11" s="73"/>
+      <c r="B11" s="83" t="s">
+        <v>715</v>
+      </c>
+      <c r="C11" s="83"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="74" t="s">
-        <v>635</v>
-      </c>
-      <c r="C12" s="74"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
+      <c r="B12" s="84" t="s">
+        <v>716</v>
+      </c>
+      <c r="C12" s="84"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="74" t="s">
-        <v>636</v>
-      </c>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
+      <c r="B13" s="84" t="s">
+        <v>717</v>
+      </c>
+      <c r="C13" s="84"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="84"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="74" t="s">
-        <v>637</v>
-      </c>
-      <c r="C14" s="74"/>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="74"/>
-      <c r="I14" s="74"/>
+      <c r="B14" s="84" t="s">
+        <v>718</v>
+      </c>
+      <c r="C14" s="84"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="84"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="84"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B15" s="74" t="s">
-        <v>638</v>
-      </c>
-      <c r="C15" s="74"/>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="74"/>
-      <c r="H15" s="74"/>
-      <c r="I15" s="74"/>
+      <c r="B15" s="84" t="s">
+        <v>719</v>
+      </c>
+      <c r="C15" s="84"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="84"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B16" s="74" t="s">
-        <v>639</v>
-      </c>
-      <c r="C16" s="74"/>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="74"/>
-      <c r="I16" s="74"/>
+      <c r="B16" s="84" t="s">
+        <v>720</v>
+      </c>
+      <c r="C16" s="84"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="84"/>
+      <c r="F16" s="84"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="84"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B17" s="74" t="s">
-        <v>640</v>
-      </c>
-      <c r="C17" s="74"/>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="74"/>
-      <c r="I17" s="74"/>
+      <c r="B17" s="84" t="s">
+        <v>721</v>
+      </c>
+      <c r="C17" s="84"/>
+      <c r="D17" s="84"/>
+      <c r="E17" s="84"/>
+      <c r="F17" s="84"/>
+      <c r="G17" s="84"/>
+      <c r="H17" s="84"/>
+      <c r="I17" s="84"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B18" s="74" t="s">
-        <v>641</v>
-      </c>
-      <c r="C18" s="74"/>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="74"/>
-      <c r="H18" s="74"/>
-      <c r="I18" s="74"/>
+      <c r="B18" s="84" t="s">
+        <v>722</v>
+      </c>
+      <c r="C18" s="84"/>
+      <c r="D18" s="84"/>
+      <c r="E18" s="84"/>
+      <c r="F18" s="84"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="84"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="74" t="s">
-        <v>642</v>
-      </c>
-      <c r="C19" s="74"/>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="74"/>
+      <c r="B19" s="84" t="s">
+        <v>723</v>
+      </c>
+      <c r="C19" s="84"/>
+      <c r="D19" s="84"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20" s="74" t="s">
-        <v>643</v>
-      </c>
-      <c r="C20" s="74"/>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="74"/>
+      <c r="B20" s="84" t="s">
+        <v>724</v>
+      </c>
+      <c r="C20" s="84"/>
+      <c r="D20" s="84"/>
+      <c r="E20" s="84"/>
+      <c r="F20" s="84"/>
+      <c r="G20" s="84"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -23280,20 +23547,23 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:J71"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:K141"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="11" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="29" t="s">
         <v>380</v>
       </c>
@@ -23305,8 +23575,9 @@
       <c r="H2" s="29"/>
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="29"/>
+    </row>
+    <row r="3" ht="42" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="66" t="s">
         <v>381</v>
       </c>
@@ -23318,6 +23589,7 @@
       <c r="H3" s="66"/>
       <c r="I3" s="66"/>
       <c r="J3" s="66"/>
+      <c r="K3" s="66"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
@@ -23339,19 +23611,19 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="6">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6">
-        <v>208</v>
+        <v>131</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="5">
-        <v>0.11320754716981132</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="I7" s="5"/>
     </row>
@@ -23365,7 +23637,7 @@
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>386</v>
       </c>
@@ -23374,24 +23646,34 @@
         <v>387</v>
       </c>
       <c r="E10" s="3"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
-        <v>171600</v>
+        <v>105600</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4">
-        <v>19875</v>
+        <v>25275</v>
       </c>
       <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="F11" s="67">
+        <v>3047.919999999999</v>
+      </c>
+      <c r="G11" s="67"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
         <v>219</v>
       </c>
@@ -23399,7 +23681,7 @@
         <v>46</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>263</v>
@@ -23408,19 +23690,22 @@
         <v>261</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J15" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="K15" s="9" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
         <v>75</v>
       </c>
@@ -23434,22 +23719,25 @@
         <v>0</v>
       </c>
       <c r="F16" s="46">
-        <v>23</v>
-      </c>
-      <c r="G16" s="67" t="s">
-        <v>392</v>
+        <v>10</v>
+      </c>
+      <c r="G16" s="68" t="s">
+        <v>394</v>
       </c>
       <c r="H16" s="47">
-        <v>18975</v>
-      </c>
-      <c r="I16" s="47">
-        <v>0</v>
-      </c>
-      <c r="J16" s="68" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+        <v>8250</v>
+      </c>
+      <c r="I16" s="69">
+        <v>84.86</v>
+      </c>
+      <c r="J16" s="47">
+        <v>0</v>
+      </c>
+      <c r="K16" s="70" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
         <v>200</v>
       </c>
@@ -23465,20 +23753,23 @@
       <c r="F17" s="46">
         <v>3</v>
       </c>
-      <c r="G17" s="67" t="s">
-        <v>394</v>
+      <c r="G17" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H17" s="47">
         <v>2475</v>
       </c>
-      <c r="I17" s="47">
-        <v>0</v>
-      </c>
-      <c r="J17" s="68" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I17" s="69">
+        <v>79.54</v>
+      </c>
+      <c r="J17" s="47">
+        <v>0</v>
+      </c>
+      <c r="K17" s="70" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
         <v>130</v>
       </c>
@@ -23494,1486 +23785,3746 @@
       <c r="F18" s="46">
         <v>3</v>
       </c>
-      <c r="G18" s="67" t="s">
-        <v>395</v>
+      <c r="G18" s="68" t="s">
+        <v>394</v>
       </c>
       <c r="H18" s="47">
         <v>2475</v>
       </c>
-      <c r="I18" s="47">
-        <v>0</v>
-      </c>
-      <c r="J18" s="68" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I18" s="69">
+        <v>15.649999999999999</v>
+      </c>
+      <c r="J18" s="47">
+        <v>0</v>
+      </c>
+      <c r="K18" s="70" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D19" s="60" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E19" s="46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="46">
-        <v>3</v>
-      </c>
-      <c r="G19" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="68" t="s">
         <v>396</v>
       </c>
       <c r="H19" s="47">
-        <v>2475</v>
-      </c>
-      <c r="I19" s="47">
-        <v>0</v>
-      </c>
-      <c r="J19" s="68" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+        <v>9900</v>
+      </c>
+      <c r="I19" s="69">
+        <v>46.98</v>
+      </c>
+      <c r="J19" s="47">
+        <v>0</v>
+      </c>
+      <c r="K19" s="70" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D20" s="60" t="s">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="E20" s="46">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F20" s="46">
-        <v>6</v>
-      </c>
-      <c r="G20" s="67" t="s">
-        <v>397</v>
+        <v>3</v>
+      </c>
+      <c r="G20" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H20" s="47">
-        <v>4950</v>
-      </c>
-      <c r="I20" s="47">
-        <v>0</v>
-      </c>
-      <c r="J20" s="68" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+        <v>2475</v>
+      </c>
+      <c r="I20" s="69">
+        <v>9.69</v>
+      </c>
+      <c r="J20" s="47">
+        <v>0</v>
+      </c>
+      <c r="K20" s="70" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>63</v>
+        <v>160</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D21" s="60" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E21" s="46">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F21" s="46">
-        <v>12</v>
-      </c>
-      <c r="G21" s="67" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="68" t="s">
         <v>394</v>
       </c>
       <c r="H21" s="47">
-        <v>9900</v>
-      </c>
-      <c r="I21" s="47">
-        <v>0</v>
-      </c>
-      <c r="J21" s="68" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+        <v>1650</v>
+      </c>
+      <c r="I21" s="69">
+        <v>142.1</v>
+      </c>
+      <c r="J21" s="47">
+        <v>0</v>
+      </c>
+      <c r="K21" s="70" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>69</v>
+        <v>202</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D22" s="60" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E22" s="46">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F22" s="46">
-        <v>13</v>
-      </c>
-      <c r="G22" s="67" t="s">
-        <v>398</v>
+        <v>1</v>
+      </c>
+      <c r="G22" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H22" s="47">
-        <v>10725</v>
-      </c>
-      <c r="I22" s="47">
-        <v>0</v>
-      </c>
-      <c r="J22" s="68" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+        <v>825</v>
+      </c>
+      <c r="I22" s="69">
+        <v>71.47</v>
+      </c>
+      <c r="J22" s="47">
+        <v>0</v>
+      </c>
+      <c r="K22" s="70" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="10" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="60" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="E23" s="46">
+        <v>15</v>
+      </c>
+      <c r="F23" s="46">
+        <v>4</v>
+      </c>
+      <c r="G23" s="68" t="s">
+        <v>397</v>
+      </c>
+      <c r="H23" s="47">
+        <v>3300</v>
+      </c>
+      <c r="I23" s="69">
+        <v>21.74</v>
+      </c>
+      <c r="J23" s="47">
+        <v>0</v>
+      </c>
+      <c r="K23" s="70" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B24" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="60" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24" s="46">
+        <v>19</v>
+      </c>
+      <c r="F24" s="46">
         <v>2</v>
       </c>
-      <c r="F23" s="46">
-        <v>13</v>
-      </c>
-      <c r="G23" s="67" t="s">
+      <c r="G24" s="68" t="s">
+        <v>397</v>
+      </c>
+      <c r="H24" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I24" s="69">
+        <v>83.83999999999999</v>
+      </c>
+      <c r="J24" s="47">
+        <v>0</v>
+      </c>
+      <c r="K24" s="70" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B25" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="60" t="s">
+        <v>137</v>
+      </c>
+      <c r="E25" s="46">
+        <v>21</v>
+      </c>
+      <c r="F25" s="46">
+        <v>1</v>
+      </c>
+      <c r="G25" s="68" t="s">
         <v>398</v>
       </c>
-      <c r="H23" s="47">
-        <v>10725</v>
-      </c>
-      <c r="I23" s="47">
-        <v>0</v>
-      </c>
-      <c r="J23" s="68" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="60" t="s">
-        <v>133</v>
-      </c>
-      <c r="E24" s="46">
-        <v>5</v>
-      </c>
-      <c r="F24" s="46">
-        <v>3</v>
-      </c>
-      <c r="G24" s="67" t="s">
-        <v>394</v>
-      </c>
-      <c r="H24" s="47">
-        <v>2475</v>
-      </c>
-      <c r="I24" s="47">
-        <v>0</v>
-      </c>
-      <c r="J24" s="68" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="60" t="s">
-        <v>103</v>
-      </c>
-      <c r="E25" s="46">
-        <v>6</v>
-      </c>
-      <c r="F25" s="46">
-        <v>6</v>
-      </c>
-      <c r="G25" s="67" t="s">
-        <v>397</v>
-      </c>
       <c r="H25" s="47">
-        <v>4950</v>
-      </c>
-      <c r="I25" s="47">
-        <v>0</v>
-      </c>
-      <c r="J25" s="68" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+        <v>825</v>
+      </c>
+      <c r="I25" s="69">
+        <v>4.6</v>
+      </c>
+      <c r="J25" s="47">
+        <v>0</v>
+      </c>
+      <c r="K25" s="70" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D26" s="60" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E26" s="46">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="F26" s="46">
-        <v>8</v>
-      </c>
-      <c r="G26" s="67" t="s">
-        <v>397</v>
+        <v>7</v>
+      </c>
+      <c r="G26" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H26" s="47">
-        <v>6600</v>
-      </c>
-      <c r="I26" s="47">
-        <v>0</v>
-      </c>
-      <c r="J26" s="68" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+        <v>5775</v>
+      </c>
+      <c r="I26" s="69">
+        <v>95.83</v>
+      </c>
+      <c r="J26" s="47">
+        <v>0</v>
+      </c>
+      <c r="K26" s="70" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="10" t="s">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D27" s="60" t="s">
-        <v>112</v>
+        <v>205</v>
       </c>
       <c r="E27" s="46">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="F27" s="46">
-        <v>9</v>
-      </c>
-      <c r="G27" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="G27" s="68" t="s">
+        <v>398</v>
+      </c>
+      <c r="H27" s="47">
+        <v>825</v>
+      </c>
+      <c r="I27" s="69">
+        <v>46.8</v>
+      </c>
+      <c r="J27" s="47">
+        <v>0</v>
+      </c>
+      <c r="K27" s="71" t="s">
         <v>399</v>
       </c>
-      <c r="H27" s="47">
-        <v>7425</v>
-      </c>
-      <c r="I27" s="47">
-        <v>0</v>
-      </c>
-      <c r="J27" s="68" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="10" t="s">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D28" s="60" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E28" s="46">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F28" s="46">
-        <v>8</v>
-      </c>
-      <c r="G28" s="67" t="s">
-        <v>398</v>
+        <v>1</v>
+      </c>
+      <c r="G28" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H28" s="47">
-        <v>6600</v>
-      </c>
-      <c r="I28" s="47">
-        <v>0</v>
-      </c>
-      <c r="J28" s="68" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+        <v>825</v>
+      </c>
+      <c r="I28" s="69">
+        <v>63.36</v>
+      </c>
+      <c r="J28" s="47">
+        <v>0</v>
+      </c>
+      <c r="K28" s="71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="10" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D29" s="60" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E29" s="46">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="F29" s="46">
-        <v>2</v>
-      </c>
-      <c r="G29" s="67" t="s">
-        <v>395</v>
+        <v>3</v>
+      </c>
+      <c r="G29" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H29" s="47">
-        <v>1650</v>
-      </c>
-      <c r="I29" s="47">
-        <v>0</v>
-      </c>
-      <c r="J29" s="68" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+        <v>2475</v>
+      </c>
+      <c r="I29" s="69">
+        <v>9.69</v>
+      </c>
+      <c r="J29" s="47">
+        <v>0</v>
+      </c>
+      <c r="K29" s="71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="10" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D30" s="60" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E30" s="46">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F30" s="46">
         <v>1</v>
       </c>
-      <c r="G30" s="67" t="s">
-        <v>394</v>
+      <c r="G30" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H30" s="47">
         <v>825</v>
       </c>
-      <c r="I30" s="47">
-        <v>0</v>
-      </c>
-      <c r="J30" s="68" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I30" s="69">
+        <v>67.51</v>
+      </c>
+      <c r="J30" s="47">
+        <v>0</v>
+      </c>
+      <c r="K30" s="71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="10" t="s">
-        <v>97</v>
+        <v>169</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D31" s="60" t="s">
-        <v>98</v>
+        <v>170</v>
       </c>
       <c r="E31" s="46">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F31" s="46">
-        <v>4</v>
-      </c>
-      <c r="G31" s="67" t="s">
-        <v>400</v>
+        <v>1</v>
+      </c>
+      <c r="G31" s="68" t="s">
+        <v>398</v>
       </c>
       <c r="H31" s="47">
-        <v>3300</v>
-      </c>
-      <c r="I31" s="47">
-        <v>0</v>
-      </c>
-      <c r="J31" s="68" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+        <v>825</v>
+      </c>
+      <c r="I31" s="69">
+        <v>78.62</v>
+      </c>
+      <c r="J31" s="47">
+        <v>0</v>
+      </c>
+      <c r="K31" s="71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" s="10" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D32" s="60" t="s">
-        <v>115</v>
+        <v>61</v>
       </c>
       <c r="E32" s="46">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="F32" s="46">
         <v>2</v>
       </c>
-      <c r="G32" s="67" t="s">
-        <v>400</v>
+      <c r="G32" s="68" t="s">
+        <v>398</v>
       </c>
       <c r="H32" s="47">
         <v>1650</v>
       </c>
-      <c r="I32" s="47">
-        <v>0</v>
-      </c>
-      <c r="J32" s="68" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I32" s="69">
+        <v>9.68</v>
+      </c>
+      <c r="J32" s="47">
+        <v>0</v>
+      </c>
+      <c r="K32" s="71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="10" t="s">
-        <v>203</v>
+        <v>81</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D33" s="60" t="s">
-        <v>137</v>
+        <v>61</v>
       </c>
       <c r="E33" s="46">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F33" s="46">
-        <v>1</v>
-      </c>
-      <c r="G33" s="67" t="s">
-        <v>401</v>
+        <v>2</v>
+      </c>
+      <c r="G33" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H33" s="47">
-        <v>825</v>
-      </c>
-      <c r="I33" s="47">
-        <v>0</v>
-      </c>
-      <c r="J33" s="68" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+        <v>1650</v>
+      </c>
+      <c r="I33" s="69">
+        <v>82.83</v>
+      </c>
+      <c r="J33" s="47">
+        <v>0</v>
+      </c>
+      <c r="K33" s="71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="10" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="C34" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D34" s="60" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="E34" s="46">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="F34" s="46">
-        <v>7</v>
-      </c>
-      <c r="G34" s="67" t="s">
-        <v>394</v>
+        <v>4</v>
+      </c>
+      <c r="G34" s="68" t="s">
+        <v>398</v>
       </c>
       <c r="H34" s="47">
-        <v>5775</v>
-      </c>
-      <c r="I34" s="47">
-        <v>0</v>
-      </c>
-      <c r="J34" s="68" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+        <v>3300</v>
+      </c>
+      <c r="I34" s="69">
+        <v>15.66</v>
+      </c>
+      <c r="J34" s="47">
+        <v>0</v>
+      </c>
+      <c r="K34" s="71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="10" t="s">
-        <v>204</v>
+        <v>118</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D35" s="60" t="s">
-        <v>205</v>
+        <v>90</v>
       </c>
       <c r="E35" s="46">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F35" s="46">
-        <v>1</v>
-      </c>
-      <c r="G35" s="67" t="s">
-        <v>401</v>
+        <v>8</v>
+      </c>
+      <c r="G35" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H35" s="47">
-        <v>825</v>
-      </c>
-      <c r="I35" s="47">
-        <v>0</v>
-      </c>
-      <c r="J35" s="69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+        <v>6600</v>
+      </c>
+      <c r="I35" s="69">
+        <v>136.98000000000002</v>
+      </c>
+      <c r="J35" s="47">
+        <v>0</v>
+      </c>
+      <c r="K35" s="71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="10" t="s">
-        <v>206</v>
+        <v>86</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D36" s="60" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="E36" s="46">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F36" s="46">
-        <v>1</v>
-      </c>
-      <c r="G36" s="67" t="s">
-        <v>394</v>
+        <v>3</v>
+      </c>
+      <c r="G36" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H36" s="47">
-        <v>825</v>
-      </c>
-      <c r="I36" s="47">
-        <v>0</v>
-      </c>
-      <c r="J36" s="69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+        <v>2475</v>
+      </c>
+      <c r="I36" s="69">
+        <v>9.69</v>
+      </c>
+      <c r="J36" s="47">
+        <v>0</v>
+      </c>
+      <c r="K36" s="71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="10" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="C37" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D37" s="60" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="E37" s="46">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F37" s="46">
-        <v>3</v>
-      </c>
-      <c r="G37" s="67" t="s">
-        <v>394</v>
+        <v>4</v>
+      </c>
+      <c r="G37" s="68" t="s">
+        <v>397</v>
       </c>
       <c r="H37" s="47">
-        <v>2475</v>
-      </c>
-      <c r="I37" s="47">
-        <v>0</v>
-      </c>
-      <c r="J37" s="69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+        <v>3300</v>
+      </c>
+      <c r="I37" s="69">
+        <v>20.73</v>
+      </c>
+      <c r="J37" s="47">
+        <v>0</v>
+      </c>
+      <c r="K37" s="71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D38" s="60" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="E38" s="46">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F38" s="46">
         <v>1</v>
       </c>
-      <c r="G38" s="67" t="s">
-        <v>394</v>
+      <c r="G38" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H38" s="47">
         <v>825</v>
       </c>
-      <c r="I38" s="47">
-        <v>0</v>
-      </c>
-      <c r="J38" s="69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I38" s="69">
+        <v>3.23</v>
+      </c>
+      <c r="J38" s="47">
+        <v>0</v>
+      </c>
+      <c r="K38" s="71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" s="10" t="s">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D39" s="60" t="s">
-        <v>170</v>
+        <v>79</v>
       </c>
       <c r="E39" s="46">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F39" s="46">
-        <v>1</v>
-      </c>
-      <c r="G39" s="67" t="s">
-        <v>401</v>
+        <v>2</v>
+      </c>
+      <c r="G39" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H39" s="47">
-        <v>825</v>
-      </c>
-      <c r="I39" s="47">
-        <v>0</v>
-      </c>
-      <c r="J39" s="69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+        <v>1650</v>
+      </c>
+      <c r="I39" s="69">
+        <v>7.83</v>
+      </c>
+      <c r="J39" s="47">
+        <v>0</v>
+      </c>
+      <c r="K39" s="71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" s="10" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D40" s="60" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="E40" s="46">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F40" s="46">
         <v>2</v>
       </c>
-      <c r="G40" s="67" t="s">
-        <v>394</v>
+      <c r="G40" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H40" s="47">
         <v>1650</v>
       </c>
-      <c r="I40" s="47">
-        <v>0</v>
-      </c>
-      <c r="J40" s="69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I40" s="69">
+        <v>7.83</v>
+      </c>
+      <c r="J40" s="47">
+        <v>0</v>
+      </c>
+      <c r="K40" s="71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="10" t="s">
-        <v>60</v>
+        <v>209</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D41" s="60" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E41" s="46">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="F41" s="46">
-        <v>4</v>
-      </c>
-      <c r="G41" s="67" t="s">
-        <v>401</v>
+        <v>2</v>
+      </c>
+      <c r="G41" s="68" t="s">
+        <v>398</v>
       </c>
       <c r="H41" s="47">
-        <v>3300</v>
-      </c>
-      <c r="I41" s="47">
-        <v>0</v>
-      </c>
-      <c r="J41" s="69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+        <v>1650</v>
+      </c>
+      <c r="I41" s="69">
+        <v>173.74</v>
+      </c>
+      <c r="J41" s="47">
+        <v>0</v>
+      </c>
+      <c r="K41" s="71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="10" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D42" s="60" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E42" s="46">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F42" s="46">
-        <v>8</v>
-      </c>
-      <c r="G42" s="67" t="s">
-        <v>394</v>
+        <v>2</v>
+      </c>
+      <c r="G42" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H42" s="47">
-        <v>6600</v>
-      </c>
-      <c r="I42" s="47">
-        <v>0</v>
-      </c>
-      <c r="J42" s="69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+        <v>1650</v>
+      </c>
+      <c r="I42" s="69">
+        <v>82.83</v>
+      </c>
+      <c r="J42" s="47">
+        <v>0</v>
+      </c>
+      <c r="K42" s="71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" s="10" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="C43" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D43" s="60" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="E43" s="46">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="F43" s="46">
-        <v>7</v>
-      </c>
-      <c r="G43" s="67" t="s">
-        <v>394</v>
+        <v>2</v>
+      </c>
+      <c r="G43" s="68" t="s">
+        <v>398</v>
       </c>
       <c r="H43" s="47">
-        <v>5775</v>
-      </c>
-      <c r="I43" s="47">
-        <v>0</v>
-      </c>
-      <c r="J43" s="69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+        <v>1650</v>
+      </c>
+      <c r="I43" s="69">
+        <v>7.83</v>
+      </c>
+      <c r="J43" s="47">
+        <v>0</v>
+      </c>
+      <c r="K43" s="71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="10" t="s">
-        <v>88</v>
+        <v>210</v>
       </c>
       <c r="C44" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="60" t="s">
+        <v>135</v>
+      </c>
+      <c r="E44" s="46">
+        <v>57</v>
+      </c>
+      <c r="F44" s="46">
+        <v>2</v>
+      </c>
+      <c r="G44" s="68" t="s">
+        <v>398</v>
+      </c>
+      <c r="H44" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I44" s="69">
+        <v>86.47</v>
+      </c>
+      <c r="J44" s="47">
+        <v>0</v>
+      </c>
+      <c r="K44" s="71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B45" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C45" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D44" s="60" t="s">
-        <v>89</v>
-      </c>
-      <c r="E44" s="46">
-        <v>47</v>
-      </c>
-      <c r="F44" s="46">
-        <v>4</v>
-      </c>
-      <c r="G44" s="67" t="s">
-        <v>400</v>
-      </c>
-      <c r="H44" s="47">
-        <v>3300</v>
-      </c>
-      <c r="I44" s="47">
-        <v>0</v>
-      </c>
-      <c r="J44" s="69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B45" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>18</v>
-      </c>
       <c r="D45" s="60" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="E45" s="46">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="F45" s="46">
-        <v>1</v>
-      </c>
-      <c r="G45" s="67" t="s">
-        <v>394</v>
+        <v>2</v>
+      </c>
+      <c r="G45" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H45" s="47">
-        <v>825</v>
-      </c>
-      <c r="I45" s="47">
-        <v>0</v>
-      </c>
-      <c r="J45" s="69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+        <v>1650</v>
+      </c>
+      <c r="I45" s="69">
+        <v>82.83</v>
+      </c>
+      <c r="J45" s="47">
+        <v>0</v>
+      </c>
+      <c r="K45" s="71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="10" t="s">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D46" s="60" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="E46" s="46">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F46" s="46">
         <v>2</v>
       </c>
-      <c r="G46" s="67" t="s">
-        <v>394</v>
+      <c r="G46" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H46" s="47">
         <v>1650</v>
       </c>
-      <c r="I46" s="47">
-        <v>0</v>
-      </c>
-      <c r="J46" s="69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I46" s="69">
+        <v>82.83</v>
+      </c>
+      <c r="J46" s="47">
+        <v>0</v>
+      </c>
+      <c r="K46" s="71" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" s="10" t="s">
-        <v>100</v>
+        <v>211</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D47" s="60" t="s">
-        <v>101</v>
+        <v>212</v>
       </c>
       <c r="E47" s="46">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="F47" s="46">
-        <v>2</v>
-      </c>
-      <c r="G47" s="67" t="s">
-        <v>394</v>
+        <v>1</v>
+      </c>
+      <c r="G47" s="68" t="s">
+        <v>398</v>
       </c>
       <c r="H47" s="47">
-        <v>1650</v>
-      </c>
-      <c r="I47" s="47">
-        <v>0</v>
-      </c>
-      <c r="J47" s="69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+        <v>825</v>
+      </c>
+      <c r="I47" s="69">
+        <v>74.24</v>
+      </c>
+      <c r="J47" s="47">
+        <v>0</v>
+      </c>
+      <c r="K47" s="72" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" s="10" t="s">
-        <v>209</v>
+        <v>128</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D48" s="60" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="E48" s="46">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F48" s="46">
         <v>2</v>
       </c>
-      <c r="G48" s="67" t="s">
-        <v>401</v>
+      <c r="G48" s="68" t="s">
+        <v>398</v>
       </c>
       <c r="H48" s="47">
         <v>1650</v>
       </c>
-      <c r="I48" s="47">
-        <v>0</v>
-      </c>
-      <c r="J48" s="69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I48" s="69">
+        <v>86.47</v>
+      </c>
+      <c r="J48" s="47">
+        <v>0</v>
+      </c>
+      <c r="K48" s="72" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" s="10" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D49" s="60" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="E49" s="46">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="F49" s="46">
         <v>2</v>
       </c>
-      <c r="G49" s="67" t="s">
-        <v>394</v>
+      <c r="G49" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H49" s="47">
         <v>1650</v>
       </c>
-      <c r="I49" s="47">
-        <v>0</v>
-      </c>
-      <c r="J49" s="69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I49" s="69">
+        <v>100.26</v>
+      </c>
+      <c r="J49" s="47">
+        <v>0</v>
+      </c>
+      <c r="K49" s="72" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" s="10" t="s">
-        <v>134</v>
+        <v>213</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D50" s="60" t="s">
-        <v>135</v>
+        <v>214</v>
       </c>
       <c r="E50" s="46">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="F50" s="46">
         <v>2</v>
       </c>
-      <c r="G50" s="67" t="s">
-        <v>401</v>
+      <c r="G50" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H50" s="47">
         <v>1650</v>
       </c>
-      <c r="I50" s="47">
-        <v>0</v>
-      </c>
-      <c r="J50" s="69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I50" s="69">
+        <v>103.21</v>
+      </c>
+      <c r="J50" s="47">
+        <v>0</v>
+      </c>
+      <c r="K50" s="72" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" s="10" t="s">
-        <v>210</v>
+        <v>111</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D51" s="60" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="E51" s="46">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="F51" s="46">
-        <v>2</v>
-      </c>
-      <c r="G51" s="67" t="s">
-        <v>401</v>
+        <v>3</v>
+      </c>
+      <c r="G51" s="68" t="s">
+        <v>397</v>
       </c>
       <c r="H51" s="47">
-        <v>1650</v>
-      </c>
-      <c r="I51" s="47">
-        <v>0</v>
-      </c>
-      <c r="J51" s="69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+        <v>2475</v>
+      </c>
+      <c r="I51" s="69">
+        <v>19.35</v>
+      </c>
+      <c r="J51" s="47">
+        <v>0</v>
+      </c>
+      <c r="K51" s="72" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" s="10" t="s">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D52" s="60" t="s">
+        <v>179</v>
+      </c>
+      <c r="E52" s="46">
+        <v>93</v>
+      </c>
+      <c r="F52" s="46">
+        <v>3</v>
+      </c>
+      <c r="G52" s="68" t="s">
+        <v>398</v>
+      </c>
+      <c r="H52" s="47">
+        <v>2475</v>
+      </c>
+      <c r="I52" s="69">
+        <v>88.99000000000001</v>
+      </c>
+      <c r="J52" s="47">
+        <v>0</v>
+      </c>
+      <c r="K52" s="72" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B53" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D53" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="E53" s="46">
         <v>106</v>
       </c>
-      <c r="E52" s="46">
-        <v>58</v>
-      </c>
-      <c r="F52" s="46">
-        <v>2</v>
-      </c>
-      <c r="G52" s="67" t="s">
-        <v>394</v>
-      </c>
-      <c r="H52" s="47">
-        <v>1650</v>
-      </c>
-      <c r="I52" s="47">
-        <v>0</v>
-      </c>
-      <c r="J52" s="69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B53" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D53" s="60" t="s">
-        <v>106</v>
-      </c>
-      <c r="E53" s="46">
-        <v>58</v>
-      </c>
       <c r="F53" s="46">
-        <v>2</v>
-      </c>
-      <c r="G53" s="67" t="s">
-        <v>394</v>
+        <v>1</v>
+      </c>
+      <c r="G53" s="68" t="s">
+        <v>398</v>
       </c>
       <c r="H53" s="47">
-        <v>1650</v>
-      </c>
-      <c r="I53" s="47">
-        <v>0</v>
-      </c>
-      <c r="J53" s="69" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+        <v>825</v>
+      </c>
+      <c r="I53" s="69">
+        <v>89.24</v>
+      </c>
+      <c r="J53" s="47">
+        <v>0</v>
+      </c>
+      <c r="K53" s="72" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D54" s="60" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E54" s="46">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="F54" s="46">
         <v>1</v>
       </c>
-      <c r="G54" s="67" t="s">
-        <v>401</v>
+      <c r="G54" s="68" t="s">
+        <v>398</v>
       </c>
       <c r="H54" s="47">
         <v>825</v>
       </c>
-      <c r="I54" s="47">
-        <v>0</v>
-      </c>
-      <c r="J54" s="70" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I54" s="69">
+        <v>96.84</v>
+      </c>
+      <c r="J54" s="47">
+        <v>0</v>
+      </c>
+      <c r="K54" s="72" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" s="10" t="s">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D55" s="60" t="s">
-        <v>129</v>
+        <v>181</v>
       </c>
       <c r="E55" s="46">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="F55" s="46">
-        <v>2</v>
-      </c>
-      <c r="G55" s="67" t="s">
-        <v>401</v>
+        <v>1</v>
+      </c>
+      <c r="G55" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H55" s="47">
-        <v>1650</v>
-      </c>
-      <c r="I55" s="47">
-        <v>0</v>
-      </c>
-      <c r="J55" s="70" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+        <v>825</v>
+      </c>
+      <c r="I55" s="69">
+        <v>80.38</v>
+      </c>
+      <c r="J55" s="47">
+        <v>0</v>
+      </c>
+      <c r="K55" s="72" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B56" s="10" t="s">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D56" s="60" t="s">
-        <v>154</v>
+        <v>82</v>
       </c>
       <c r="E56" s="46">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="F56" s="46">
+        <v>2</v>
+      </c>
+      <c r="G56" s="68" t="s">
+        <v>396</v>
+      </c>
+      <c r="H56" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I56" s="69">
+        <v>9.2</v>
+      </c>
+      <c r="J56" s="73">
+        <v>1800</v>
+      </c>
+      <c r="K56" s="74" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B57" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" s="60" t="s">
+        <v>109</v>
+      </c>
+      <c r="E57" s="46">
+        <v>29</v>
+      </c>
+      <c r="F57" s="46">
         <v>7</v>
       </c>
-      <c r="G56" s="67" t="s">
-        <v>404</v>
-      </c>
-      <c r="H56" s="47">
+      <c r="G57" s="68" t="s">
+        <v>398</v>
+      </c>
+      <c r="H57" s="47">
         <v>5775</v>
       </c>
-      <c r="I56" s="47">
-        <v>0</v>
-      </c>
-      <c r="J56" s="70" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D57" s="60" t="s">
-        <v>140</v>
-      </c>
-      <c r="E57" s="46">
-        <v>71</v>
-      </c>
-      <c r="F57" s="46">
-        <v>2</v>
-      </c>
-      <c r="G57" s="67" t="s">
-        <v>394</v>
-      </c>
-      <c r="H57" s="47">
-        <v>1650</v>
-      </c>
-      <c r="I57" s="47">
-        <v>0</v>
-      </c>
-      <c r="J57" s="70" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I57" s="69">
+        <v>70.5</v>
+      </c>
+      <c r="J57" s="73">
+        <v>3600</v>
+      </c>
+      <c r="K57" s="74" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" s="10" t="s">
-        <v>213</v>
+        <v>102</v>
       </c>
       <c r="C58" s="10" t="s">
         <v>17</v>
       </c>
       <c r="D58" s="60" t="s">
-        <v>214</v>
+        <v>90</v>
       </c>
       <c r="E58" s="46">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="F58" s="46">
         <v>2</v>
       </c>
-      <c r="G58" s="67" t="s">
-        <v>394</v>
+      <c r="G58" s="68" t="s">
+        <v>396</v>
       </c>
       <c r="H58" s="47">
         <v>1650</v>
       </c>
-      <c r="I58" s="47">
-        <v>0</v>
-      </c>
-      <c r="J58" s="70" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I58" s="69">
+        <v>208.23000000000002</v>
+      </c>
+      <c r="J58" s="73">
+        <v>1800</v>
+      </c>
+      <c r="K58" s="74" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" s="10" t="s">
-        <v>178</v>
+        <v>84</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D59" s="60" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="E59" s="46">
+        <v>47</v>
+      </c>
+      <c r="F59" s="46">
+        <v>2</v>
+      </c>
+      <c r="G59" s="68" t="s">
+        <v>398</v>
+      </c>
+      <c r="H59" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I59" s="69">
+        <v>80.56</v>
+      </c>
+      <c r="J59" s="73">
+        <v>10800</v>
+      </c>
+      <c r="K59" s="74" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B60" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D60" s="60" t="s">
         <v>93</v>
       </c>
-      <c r="F59" s="46">
-        <v>3</v>
-      </c>
-      <c r="G59" s="67" t="s">
+      <c r="E60" s="46">
+        <v>69</v>
+      </c>
+      <c r="F60" s="46">
+        <v>2</v>
+      </c>
+      <c r="G60" s="68" t="s">
+        <v>396</v>
+      </c>
+      <c r="H60" s="47">
+        <v>1650</v>
+      </c>
+      <c r="I60" s="69">
+        <v>84.2</v>
+      </c>
+      <c r="J60" s="73">
+        <v>1275</v>
+      </c>
+      <c r="K60" s="74" t="s">
         <v>401</v>
       </c>
-      <c r="H59" s="47">
-        <v>2475</v>
-      </c>
-      <c r="I59" s="47">
-        <v>0</v>
-      </c>
-      <c r="J59" s="70" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B60" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D60" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="E60" s="46">
-        <v>106</v>
-      </c>
-      <c r="F60" s="46">
-        <v>1</v>
-      </c>
-      <c r="G60" s="67" t="s">
-        <v>401</v>
-      </c>
-      <c r="H60" s="47">
-        <v>825</v>
-      </c>
-      <c r="I60" s="47">
-        <v>0</v>
-      </c>
-      <c r="J60" s="70" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" s="10" t="s">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="C61" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D61" s="60" t="s">
-        <v>216</v>
+        <v>301</v>
       </c>
       <c r="E61" s="46">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="F61" s="46">
         <v>1</v>
       </c>
-      <c r="G61" s="67" t="s">
-        <v>401</v>
+      <c r="G61" s="68" t="s">
+        <v>398</v>
       </c>
       <c r="H61" s="47">
         <v>825</v>
       </c>
-      <c r="I61" s="47">
-        <v>0</v>
-      </c>
-      <c r="J61" s="70" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I61" s="69">
+        <v>83.83</v>
+      </c>
+      <c r="J61" s="73">
+        <v>1800</v>
+      </c>
+      <c r="K61" s="74" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" s="10" t="s">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>18</v>
       </c>
       <c r="D62" s="60" t="s">
-        <v>181</v>
+        <v>301</v>
       </c>
       <c r="E62" s="46">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="F62" s="46">
         <v>1</v>
       </c>
-      <c r="G62" s="67" t="s">
-        <v>394</v>
+      <c r="G62" s="68" t="s">
+        <v>398</v>
       </c>
       <c r="H62" s="47">
         <v>825</v>
       </c>
-      <c r="I62" s="47">
-        <v>0</v>
-      </c>
-      <c r="J62" s="70" t="s">
+      <c r="I62" s="69">
+        <v>6.45</v>
+      </c>
+      <c r="J62" s="73">
+        <v>2400</v>
+      </c>
+      <c r="K62" s="74" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B63" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D63" s="60" t="s">
+        <v>235</v>
+      </c>
+      <c r="E63" s="46">
+        <v>194</v>
+      </c>
+      <c r="F63" s="46">
+        <v>3</v>
+      </c>
+      <c r="G63" s="68" t="s">
+        <v>396</v>
+      </c>
+      <c r="H63" s="47">
+        <v>0</v>
+      </c>
+      <c r="I63" s="69">
+        <v>32.7</v>
+      </c>
+      <c r="J63" s="73">
+        <v>1800</v>
+      </c>
+      <c r="K63" s="74" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B64" s="75" t="s">
+        <v>402</v>
+      </c>
+      <c r="H64" s="76">
+        <f>SUM(H16:H63)</f>
+        <v>105600</v>
+      </c>
+      <c r="I64" s="76">
+        <f>SUM(I16:I63)</f>
+        <v>3047.919999999999</v>
+      </c>
+    </row>
+    <row r="66" ht="36" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B66" s="66" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B63" s="10" t="s">
+      <c r="C66" s="66"/>
+      <c r="D66" s="66"/>
+      <c r="E66" s="66"/>
+      <c r="F66" s="66"/>
+      <c r="G66" s="66"/>
+      <c r="H66" s="66"/>
+      <c r="I66" s="66"/>
+      <c r="J66" s="66"/>
+      <c r="K66" s="66"/>
+    </row>
+    <row r="69" ht="28" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B69" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="7"/>
+      <c r="J69" s="7"/>
+      <c r="K69" s="7"/>
+    </row>
+    <row r="70" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B70" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="E70" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="J70" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="K70" s="9" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="71" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B71" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="C71" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71" s="77" t="s">
+        <v>412</v>
+      </c>
+      <c r="E71" s="77" t="s">
+        <v>230</v>
+      </c>
+      <c r="F71" s="78">
+        <v>2</v>
+      </c>
+      <c r="G71" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H71" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I71" s="79">
+        <v>17.66</v>
+      </c>
+      <c r="J71" s="79">
+        <v>0</v>
+      </c>
+      <c r="K71" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="72" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B72" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="C72" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" s="77" t="s">
+        <v>414</v>
+      </c>
+      <c r="E72" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="F72" s="78">
+        <v>2</v>
+      </c>
+      <c r="G72" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H72" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I72" s="79">
+        <v>7.83</v>
+      </c>
+      <c r="J72" s="79">
+        <v>0</v>
+      </c>
+      <c r="K72" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="73" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B73" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="C73" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" s="77" t="s">
+        <v>415</v>
+      </c>
+      <c r="E73" s="77" t="s">
+        <v>170</v>
+      </c>
+      <c r="F73" s="78">
+        <v>2</v>
+      </c>
+      <c r="G73" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H73" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I73" s="79">
+        <v>7.83</v>
+      </c>
+      <c r="J73" s="79">
+        <v>0</v>
+      </c>
+      <c r="K73" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="74" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B74" s="77" t="s">
+        <v>75</v>
+      </c>
+      <c r="C74" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" s="77" t="s">
+        <v>416</v>
+      </c>
+      <c r="E74" s="77" t="s">
+        <v>67</v>
+      </c>
+      <c r="F74" s="78">
+        <v>4</v>
+      </c>
+      <c r="G74" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H74" s="79">
+        <v>3300</v>
+      </c>
+      <c r="I74" s="79">
+        <v>51.54</v>
+      </c>
+      <c r="J74" s="79">
+        <v>-38.62</v>
+      </c>
+      <c r="K74" s="77" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="75" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B75" s="77" t="s">
+        <v>200</v>
+      </c>
+      <c r="C75" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D75" s="77" t="s">
+        <v>418</v>
+      </c>
+      <c r="E75" s="77" t="s">
+        <v>191</v>
+      </c>
+      <c r="F75" s="78">
+        <v>1</v>
+      </c>
+      <c r="G75" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H75" s="79">
+        <v>825</v>
+      </c>
+      <c r="I75" s="79">
+        <v>79.54</v>
+      </c>
+      <c r="J75" s="79">
+        <v>-73.09</v>
+      </c>
+      <c r="K75" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="76" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B76" s="77" t="s">
+        <v>200</v>
+      </c>
+      <c r="C76" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D76" s="77" t="s">
+        <v>419</v>
+      </c>
+      <c r="E76" s="77" t="s">
+        <v>67</v>
+      </c>
+      <c r="F76" s="78">
+        <v>2</v>
+      </c>
+      <c r="G76" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H76" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I76" s="79">
+        <v>0</v>
+      </c>
+      <c r="J76" s="79">
+        <v>0</v>
+      </c>
+      <c r="K76" s="77" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="77" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B77" s="77" t="s">
+        <v>130</v>
+      </c>
+      <c r="C77" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D77" s="77" t="s">
+        <v>421</v>
+      </c>
+      <c r="E77" s="77" t="s">
+        <v>303</v>
+      </c>
+      <c r="F77" s="78">
+        <v>1</v>
+      </c>
+      <c r="G77" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H77" s="79">
+        <v>825</v>
+      </c>
+      <c r="I77" s="79">
+        <v>6.45</v>
+      </c>
+      <c r="J77" s="79">
+        <v>0</v>
+      </c>
+      <c r="K77" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="78" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B78" s="77" t="s">
+        <v>130</v>
+      </c>
+      <c r="C78" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D78" s="77" t="s">
+        <v>422</v>
+      </c>
+      <c r="E78" s="77" t="s">
+        <v>67</v>
+      </c>
+      <c r="F78" s="78">
+        <v>2</v>
+      </c>
+      <c r="G78" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H78" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I78" s="79">
+        <v>9.2</v>
+      </c>
+      <c r="J78" s="79">
+        <v>0</v>
+      </c>
+      <c r="K78" s="77" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="79" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B79" s="77" t="s">
+        <v>63</v>
+      </c>
+      <c r="C79" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D79" s="77" t="s">
+        <v>423</v>
+      </c>
+      <c r="E79" s="77" t="s">
+        <v>101</v>
+      </c>
+      <c r="F79" s="78">
+        <v>6</v>
+      </c>
+      <c r="G79" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H79" s="79">
+        <v>4950</v>
+      </c>
+      <c r="I79" s="79">
+        <v>23.49</v>
+      </c>
+      <c r="J79" s="79">
+        <v>0</v>
+      </c>
+      <c r="K79" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="80" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B80" s="77" t="s">
+        <v>63</v>
+      </c>
+      <c r="C80" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D80" s="77" t="s">
+        <v>424</v>
+      </c>
+      <c r="E80" s="77" t="s">
+        <v>64</v>
+      </c>
+      <c r="F80" s="78">
+        <v>6</v>
+      </c>
+      <c r="G80" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H80" s="79">
+        <v>4950</v>
+      </c>
+      <c r="I80" s="79">
+        <v>23.49</v>
+      </c>
+      <c r="J80" s="79">
+        <v>0</v>
+      </c>
+      <c r="K80" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="81" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B81" s="77" t="s">
+        <v>132</v>
+      </c>
+      <c r="C81" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D81" s="77" t="s">
+        <v>425</v>
+      </c>
+      <c r="E81" s="77" t="s">
+        <v>133</v>
+      </c>
+      <c r="F81" s="78">
+        <v>3</v>
+      </c>
+      <c r="G81" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H81" s="79">
+        <v>2475</v>
+      </c>
+      <c r="I81" s="79">
+        <v>9.69</v>
+      </c>
+      <c r="J81" s="79">
+        <v>0</v>
+      </c>
+      <c r="K81" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="82" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B82" s="77" t="s">
+        <v>160</v>
+      </c>
+      <c r="C82" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D82" s="77" t="s">
+        <v>426</v>
+      </c>
+      <c r="E82" s="77" t="s">
+        <v>292</v>
+      </c>
+      <c r="F82" s="78">
+        <v>1</v>
+      </c>
+      <c r="G82" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H82" s="79">
+        <v>825</v>
+      </c>
+      <c r="I82" s="79">
+        <v>74.24</v>
+      </c>
+      <c r="J82" s="79">
+        <v>-69.64</v>
+      </c>
+      <c r="K82" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="83" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B83" s="77" t="s">
+        <v>160</v>
+      </c>
+      <c r="C83" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D83" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="E83" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="F83" s="78">
+        <v>1</v>
+      </c>
+      <c r="G83" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H83" s="79">
+        <v>825</v>
+      </c>
+      <c r="I83" s="79">
+        <v>67.86</v>
+      </c>
+      <c r="J83" s="79">
+        <v>-64.63</v>
+      </c>
+      <c r="K83" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="84" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B84" s="77" t="s">
+        <v>202</v>
+      </c>
+      <c r="C84" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D84" s="77" t="s">
+        <v>428</v>
+      </c>
+      <c r="E84" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="F84" s="78">
+        <v>1</v>
+      </c>
+      <c r="G84" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H84" s="79">
+        <v>825</v>
+      </c>
+      <c r="I84" s="79">
+        <v>71.47</v>
+      </c>
+      <c r="J84" s="79">
+        <v>-68.24</v>
+      </c>
+      <c r="K84" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="85" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B85" s="77" t="s">
+        <v>97</v>
+      </c>
+      <c r="C85" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D85" s="77" t="s">
+        <v>429</v>
+      </c>
+      <c r="E85" s="77" t="s">
+        <v>295</v>
+      </c>
+      <c r="F85" s="78">
+        <v>2</v>
+      </c>
+      <c r="G85" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H85" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I85" s="79">
+        <v>15.28</v>
+      </c>
+      <c r="J85" s="79">
+        <v>0</v>
+      </c>
+      <c r="K85" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="86" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B86" s="77" t="s">
+        <v>97</v>
+      </c>
+      <c r="C86" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D86" s="77" t="s">
+        <v>430</v>
+      </c>
+      <c r="E86" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="F86" s="78">
+        <v>2</v>
+      </c>
+      <c r="G86" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H86" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I86" s="79">
+        <v>6.46</v>
+      </c>
+      <c r="J86" s="79">
+        <v>0</v>
+      </c>
+      <c r="K86" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="87" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B87" s="77" t="s">
+        <v>142</v>
+      </c>
+      <c r="C87" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D87" s="77" t="s">
+        <v>431</v>
+      </c>
+      <c r="E87" s="77" t="s">
+        <v>101</v>
+      </c>
+      <c r="F87" s="78">
+        <v>1</v>
+      </c>
+      <c r="G87" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H87" s="79">
+        <v>825</v>
+      </c>
+      <c r="I87" s="79">
+        <v>79.24</v>
+      </c>
+      <c r="J87" s="79">
+        <v>-74.64</v>
+      </c>
+      <c r="K87" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="88" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B88" s="77" t="s">
+        <v>142</v>
+      </c>
+      <c r="C88" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D88" s="77" t="s">
+        <v>432</v>
+      </c>
+      <c r="E88" s="77" t="s">
+        <v>115</v>
+      </c>
+      <c r="F88" s="78">
+        <v>1</v>
+      </c>
+      <c r="G88" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H88" s="79">
+        <v>825</v>
+      </c>
+      <c r="I88" s="79">
+        <v>4.6</v>
+      </c>
+      <c r="J88" s="79">
+        <v>0</v>
+      </c>
+      <c r="K88" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="89" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B89" s="77" t="s">
+        <v>203</v>
+      </c>
+      <c r="C89" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D89" s="77" t="s">
+        <v>433</v>
+      </c>
+      <c r="E89" s="77" t="s">
+        <v>137</v>
+      </c>
+      <c r="F89" s="78">
+        <v>1</v>
+      </c>
+      <c r="G89" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H89" s="79">
+        <v>825</v>
+      </c>
+      <c r="I89" s="79">
+        <v>4.6</v>
+      </c>
+      <c r="J89" s="79">
+        <v>0</v>
+      </c>
+      <c r="K89" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="90" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B90" s="77" t="s">
+        <v>108</v>
+      </c>
+      <c r="C90" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D90" s="77" t="s">
+        <v>434</v>
+      </c>
+      <c r="E90" s="77" t="s">
+        <v>186</v>
+      </c>
+      <c r="F90" s="78">
+        <v>6</v>
+      </c>
+      <c r="G90" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H90" s="79">
+        <v>4950</v>
+      </c>
+      <c r="I90" s="79">
+        <v>91.23</v>
+      </c>
+      <c r="J90" s="79">
+        <v>-45.39</v>
+      </c>
+      <c r="K90" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="91" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B91" s="77" t="s">
+        <v>108</v>
+      </c>
+      <c r="C91" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D91" s="77" t="s">
+        <v>435</v>
+      </c>
+      <c r="E91" s="77" t="s">
+        <v>109</v>
+      </c>
+      <c r="F91" s="78">
+        <v>1</v>
+      </c>
+      <c r="G91" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H91" s="79">
+        <v>825</v>
+      </c>
+      <c r="I91" s="79">
+        <v>4.6</v>
+      </c>
+      <c r="J91" s="79">
+        <v>0</v>
+      </c>
+      <c r="K91" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="92" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B92" s="77" t="s">
+        <v>204</v>
+      </c>
+      <c r="C92" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D92" s="77" t="s">
+        <v>436</v>
+      </c>
+      <c r="E92" s="77" t="s">
+        <v>205</v>
+      </c>
+      <c r="F92" s="78">
+        <v>1</v>
+      </c>
+      <c r="G92" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H92" s="79">
+        <v>825</v>
+      </c>
+      <c r="I92" s="79">
+        <v>46.8</v>
+      </c>
+      <c r="J92" s="79">
+        <v>-43.57</v>
+      </c>
+      <c r="K92" s="77" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="93" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B93" s="77" t="s">
+        <v>206</v>
+      </c>
+      <c r="C93" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D93" s="77" t="s">
+        <v>437</v>
+      </c>
+      <c r="E93" s="77" t="s">
+        <v>65</v>
+      </c>
+      <c r="F93" s="78">
+        <v>1</v>
+      </c>
+      <c r="G93" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H93" s="79">
+        <v>825</v>
+      </c>
+      <c r="I93" s="79">
+        <v>63.36</v>
+      </c>
+      <c r="J93" s="79">
+        <v>-58.76</v>
+      </c>
+      <c r="K93" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="94" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B94" s="77" t="s">
+        <v>117</v>
+      </c>
+      <c r="C94" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D94" s="77" t="s">
+        <v>438</v>
+      </c>
+      <c r="E94" s="77" t="s">
+        <v>71</v>
+      </c>
+      <c r="F94" s="78">
+        <v>3</v>
+      </c>
+      <c r="G94" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H94" s="79">
+        <v>2475</v>
+      </c>
+      <c r="I94" s="79">
+        <v>9.69</v>
+      </c>
+      <c r="J94" s="79">
+        <v>0</v>
+      </c>
+      <c r="K94" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="95" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B95" s="77" t="s">
+        <v>207</v>
+      </c>
+      <c r="C95" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D95" s="77" t="s">
+        <v>439</v>
+      </c>
+      <c r="E95" s="77" t="s">
+        <v>80</v>
+      </c>
+      <c r="F95" s="78">
+        <v>1</v>
+      </c>
+      <c r="G95" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H95" s="79">
+        <v>825</v>
+      </c>
+      <c r="I95" s="79">
+        <v>67.51</v>
+      </c>
+      <c r="J95" s="79">
+        <v>-64.28</v>
+      </c>
+      <c r="K95" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="96" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B96" s="77" t="s">
+        <v>169</v>
+      </c>
+      <c r="C96" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D96" s="77" t="s">
+        <v>440</v>
+      </c>
+      <c r="E96" s="77" t="s">
+        <v>170</v>
+      </c>
+      <c r="F96" s="78">
+        <v>1</v>
+      </c>
+      <c r="G96" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H96" s="79">
+        <v>825</v>
+      </c>
+      <c r="I96" s="79">
+        <v>78.62</v>
+      </c>
+      <c r="J96" s="79">
+        <v>-74.02</v>
+      </c>
+      <c r="K96" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="97" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B97" s="77" t="s">
+        <v>161</v>
+      </c>
+      <c r="C97" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D97" s="77" t="s">
+        <v>441</v>
+      </c>
+      <c r="E97" s="77" t="s">
+        <v>121</v>
+      </c>
+      <c r="F97" s="78">
+        <v>1</v>
+      </c>
+      <c r="G97" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H97" s="79">
+        <v>825</v>
+      </c>
+      <c r="I97" s="79">
+        <v>6.45</v>
+      </c>
+      <c r="J97" s="79">
+        <v>0</v>
+      </c>
+      <c r="K97" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="98" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B98" s="77" t="s">
+        <v>161</v>
+      </c>
+      <c r="C98" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D98" s="77" t="s">
+        <v>442</v>
+      </c>
+      <c r="E98" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="F98" s="78">
+        <v>1</v>
+      </c>
+      <c r="G98" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H98" s="79">
+        <v>825</v>
+      </c>
+      <c r="I98" s="79">
+        <v>3.23</v>
+      </c>
+      <c r="J98" s="79">
+        <v>0</v>
+      </c>
+      <c r="K98" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="99" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B99" s="77" t="s">
+        <v>81</v>
+      </c>
+      <c r="C99" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D99" s="77" t="s">
+        <v>443</v>
+      </c>
+      <c r="E99" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="F99" s="78">
+        <v>2</v>
+      </c>
+      <c r="G99" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H99" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I99" s="79">
+        <v>82.83</v>
+      </c>
+      <c r="J99" s="79">
+        <v>-75</v>
+      </c>
+      <c r="K99" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="100" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B100" s="77" t="s">
+        <v>60</v>
+      </c>
+      <c r="C100" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D100" s="77" t="s">
+        <v>444</v>
+      </c>
+      <c r="E100" s="77" t="s">
+        <v>61</v>
+      </c>
+      <c r="F100" s="78">
+        <v>4</v>
+      </c>
+      <c r="G100" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H100" s="79">
+        <v>3300</v>
+      </c>
+      <c r="I100" s="79">
+        <v>15.66</v>
+      </c>
+      <c r="J100" s="79">
+        <v>0</v>
+      </c>
+      <c r="K100" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="101" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B101" s="77" t="s">
+        <v>118</v>
+      </c>
+      <c r="C101" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D101" s="77" t="s">
+        <v>445</v>
+      </c>
+      <c r="E101" s="77" t="s">
+        <v>446</v>
+      </c>
+      <c r="F101" s="78">
+        <v>6</v>
+      </c>
+      <c r="G101" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H101" s="79">
+        <v>4950</v>
+      </c>
+      <c r="I101" s="79">
+        <v>129.15</v>
+      </c>
+      <c r="J101" s="79">
+        <v>-83.31</v>
+      </c>
+      <c r="K101" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="102" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B102" s="77" t="s">
+        <v>118</v>
+      </c>
+      <c r="C102" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D102" s="77" t="s">
+        <v>447</v>
+      </c>
+      <c r="E102" s="77" t="s">
+        <v>90</v>
+      </c>
+      <c r="F102" s="78">
+        <v>2</v>
+      </c>
+      <c r="G102" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H102" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I102" s="79">
+        <v>7.83</v>
+      </c>
+      <c r="J102" s="79">
+        <v>0</v>
+      </c>
+      <c r="K102" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="103" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B103" s="77" t="s">
+        <v>86</v>
+      </c>
+      <c r="C103" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D103" s="77" t="s">
+        <v>448</v>
+      </c>
+      <c r="E103" s="77" t="s">
+        <v>87</v>
+      </c>
+      <c r="F103" s="78">
+        <v>3</v>
+      </c>
+      <c r="G103" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H103" s="79">
+        <v>2475</v>
+      </c>
+      <c r="I103" s="79">
+        <v>9.69</v>
+      </c>
+      <c r="J103" s="79">
+        <v>0</v>
+      </c>
+      <c r="K103" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="104" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B104" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="C104" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D104" s="77" t="s">
+        <v>449</v>
+      </c>
+      <c r="E104" s="77" t="s">
+        <v>152</v>
+      </c>
+      <c r="F104" s="78">
+        <v>2</v>
+      </c>
+      <c r="G104" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H104" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I104" s="79">
+        <v>12.9</v>
+      </c>
+      <c r="J104" s="79">
+        <v>0</v>
+      </c>
+      <c r="K104" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="105" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B105" s="77" t="s">
+        <v>88</v>
+      </c>
+      <c r="C105" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D105" s="77" t="s">
+        <v>450</v>
+      </c>
+      <c r="E105" s="77" t="s">
+        <v>89</v>
+      </c>
+      <c r="F105" s="78">
+        <v>2</v>
+      </c>
+      <c r="G105" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H105" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I105" s="79">
+        <v>7.83</v>
+      </c>
+      <c r="J105" s="79">
+        <v>0</v>
+      </c>
+      <c r="K105" s="77" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="106" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B106" s="77" t="s">
+        <v>208</v>
+      </c>
+      <c r="C106" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D106" s="77" t="s">
+        <v>451</v>
+      </c>
+      <c r="E106" s="77" t="s">
+        <v>89</v>
+      </c>
+      <c r="F106" s="78">
+        <v>1</v>
+      </c>
+      <c r="G106" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H106" s="79">
+        <v>825</v>
+      </c>
+      <c r="I106" s="79">
+        <v>3.23</v>
+      </c>
+      <c r="J106" s="79">
+        <v>0</v>
+      </c>
+      <c r="K106" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="107" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B107" s="77" t="s">
+        <v>78</v>
+      </c>
+      <c r="C107" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107" s="77" t="s">
+        <v>452</v>
+      </c>
+      <c r="E107" s="77" t="s">
+        <v>79</v>
+      </c>
+      <c r="F107" s="78">
+        <v>2</v>
+      </c>
+      <c r="G107" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H107" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I107" s="79">
+        <v>7.83</v>
+      </c>
+      <c r="J107" s="79">
+        <v>0</v>
+      </c>
+      <c r="K107" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="108" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B108" s="77" t="s">
+        <v>100</v>
+      </c>
+      <c r="C108" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D108" s="77" t="s">
+        <v>453</v>
+      </c>
+      <c r="E108" s="77" t="s">
+        <v>101</v>
+      </c>
+      <c r="F108" s="78">
+        <v>2</v>
+      </c>
+      <c r="G108" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H108" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I108" s="79">
+        <v>7.83</v>
+      </c>
+      <c r="J108" s="79">
+        <v>0</v>
+      </c>
+      <c r="K108" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="109" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B109" s="77" t="s">
+        <v>209</v>
+      </c>
+      <c r="C109" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D109" s="77" t="s">
+        <v>454</v>
+      </c>
+      <c r="E109" s="77" t="s">
+        <v>116</v>
+      </c>
+      <c r="F109" s="78">
+        <v>1</v>
+      </c>
+      <c r="G109" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H109" s="79">
+        <v>825</v>
+      </c>
+      <c r="I109" s="79">
+        <v>86.87</v>
+      </c>
+      <c r="J109" s="79">
+        <v>-82.27</v>
+      </c>
+      <c r="K109" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="110" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B110" s="77" t="s">
+        <v>209</v>
+      </c>
+      <c r="C110" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D110" s="77" t="s">
+        <v>455</v>
+      </c>
+      <c r="E110" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="F110" s="78">
+        <v>1</v>
+      </c>
+      <c r="G110" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H110" s="79">
+        <v>825</v>
+      </c>
+      <c r="I110" s="79">
+        <v>86.87</v>
+      </c>
+      <c r="J110" s="79">
+        <v>-82.27</v>
+      </c>
+      <c r="K110" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="111" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B111" s="77" t="s">
+        <v>122</v>
+      </c>
+      <c r="C111" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D111" s="77" t="s">
+        <v>456</v>
+      </c>
+      <c r="E111" s="77" t="s">
+        <v>99</v>
+      </c>
+      <c r="F111" s="78">
+        <v>2</v>
+      </c>
+      <c r="G111" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H111" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I111" s="79">
+        <v>82.83</v>
+      </c>
+      <c r="J111" s="79">
+        <v>-75</v>
+      </c>
+      <c r="K111" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="112" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B112" s="77" t="s">
+        <v>134</v>
+      </c>
+      <c r="C112" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D112" s="77" t="s">
+        <v>457</v>
+      </c>
+      <c r="E112" s="77" t="s">
+        <v>135</v>
+      </c>
+      <c r="F112" s="78">
+        <v>2</v>
+      </c>
+      <c r="G112" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H112" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I112" s="79">
+        <v>7.83</v>
+      </c>
+      <c r="J112" s="79">
+        <v>0</v>
+      </c>
+      <c r="K112" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="113" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B113" s="77" t="s">
+        <v>210</v>
+      </c>
+      <c r="C113" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D113" s="77" t="s">
+        <v>458</v>
+      </c>
+      <c r="E113" s="77" t="s">
+        <v>135</v>
+      </c>
+      <c r="F113" s="78">
+        <v>2</v>
+      </c>
+      <c r="G113" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H113" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I113" s="79">
+        <v>86.47</v>
+      </c>
+      <c r="J113" s="79">
+        <v>-77.27</v>
+      </c>
+      <c r="K113" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="114" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B114" s="77" t="s">
+        <v>138</v>
+      </c>
+      <c r="C114" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D114" s="77" t="s">
+        <v>459</v>
+      </c>
+      <c r="E114" s="77" t="s">
+        <v>106</v>
+      </c>
+      <c r="F114" s="78">
+        <v>2</v>
+      </c>
+      <c r="G114" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H114" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I114" s="79">
+        <v>82.83</v>
+      </c>
+      <c r="J114" s="79">
+        <v>-75</v>
+      </c>
+      <c r="K114" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="115" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B115" s="77" t="s">
+        <v>136</v>
+      </c>
+      <c r="C115" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D115" s="77" t="s">
+        <v>460</v>
+      </c>
+      <c r="E115" s="77" t="s">
+        <v>106</v>
+      </c>
+      <c r="F115" s="78">
+        <v>2</v>
+      </c>
+      <c r="G115" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H115" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I115" s="79">
+        <v>82.83</v>
+      </c>
+      <c r="J115" s="79">
+        <v>-75</v>
+      </c>
+      <c r="K115" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="116" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B116" s="77" t="s">
+        <v>211</v>
+      </c>
+      <c r="C116" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D116" s="77" t="s">
+        <v>461</v>
+      </c>
+      <c r="E116" s="77" t="s">
+        <v>212</v>
+      </c>
+      <c r="F116" s="78">
+        <v>1</v>
+      </c>
+      <c r="G116" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H116" s="79">
+        <v>825</v>
+      </c>
+      <c r="I116" s="79">
+        <v>74.24</v>
+      </c>
+      <c r="J116" s="79">
+        <v>-69.64</v>
+      </c>
+      <c r="K116" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="117" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B117" s="77" t="s">
+        <v>128</v>
+      </c>
+      <c r="C117" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D117" s="77" t="s">
+        <v>462</v>
+      </c>
+      <c r="E117" s="77" t="s">
+        <v>129</v>
+      </c>
+      <c r="F117" s="78">
+        <v>2</v>
+      </c>
+      <c r="G117" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H117" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I117" s="79">
+        <v>86.47</v>
+      </c>
+      <c r="J117" s="79">
+        <v>-77.27</v>
+      </c>
+      <c r="K117" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="118" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B118" s="77" t="s">
+        <v>139</v>
+      </c>
+      <c r="C118" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D118" s="77" t="s">
+        <v>463</v>
+      </c>
+      <c r="E118" s="77" t="s">
+        <v>140</v>
+      </c>
+      <c r="F118" s="78">
+        <v>2</v>
+      </c>
+      <c r="G118" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H118" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I118" s="79">
+        <v>100.26</v>
+      </c>
+      <c r="J118" s="79">
+        <v>-87.36</v>
+      </c>
+      <c r="K118" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="119" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B119" s="77" t="s">
+        <v>213</v>
+      </c>
+      <c r="C119" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D119" s="77" t="s">
+        <v>464</v>
+      </c>
+      <c r="E119" s="77" t="s">
+        <v>214</v>
+      </c>
+      <c r="F119" s="78">
+        <v>2</v>
+      </c>
+      <c r="G119" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H119" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I119" s="79">
+        <v>103.21</v>
+      </c>
+      <c r="J119" s="79">
+        <v>-90.31</v>
+      </c>
+      <c r="K119" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="120" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B120" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="C120" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D120" s="77" t="s">
+        <v>465</v>
+      </c>
+      <c r="E120" s="77" t="s">
+        <v>466</v>
+      </c>
+      <c r="F120" s="78">
+        <v>1</v>
+      </c>
+      <c r="G120" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H120" s="79">
+        <v>825</v>
+      </c>
+      <c r="I120" s="79">
+        <v>6.45</v>
+      </c>
+      <c r="J120" s="79">
+        <v>0</v>
+      </c>
+      <c r="K120" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="121" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B121" s="77" t="s">
+        <v>111</v>
+      </c>
+      <c r="C121" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D121" s="77" t="s">
+        <v>467</v>
+      </c>
+      <c r="E121" s="77" t="s">
+        <v>113</v>
+      </c>
+      <c r="F121" s="78">
+        <v>2</v>
+      </c>
+      <c r="G121" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H121" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I121" s="79">
+        <v>12.9</v>
+      </c>
+      <c r="J121" s="79">
+        <v>0</v>
+      </c>
+      <c r="K121" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="122" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B122" s="77" t="s">
+        <v>178</v>
+      </c>
+      <c r="C122" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D122" s="77" t="s">
+        <v>468</v>
+      </c>
+      <c r="E122" s="77" t="s">
+        <v>247</v>
+      </c>
+      <c r="F122" s="78">
+        <v>1</v>
+      </c>
+      <c r="G122" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H122" s="79">
+        <v>825</v>
+      </c>
+      <c r="I122" s="79">
+        <v>6.45</v>
+      </c>
+      <c r="J122" s="79">
+        <v>0</v>
+      </c>
+      <c r="K122" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="123" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B123" s="77" t="s">
+        <v>178</v>
+      </c>
+      <c r="C123" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D123" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="E123" s="77" t="s">
+        <v>179</v>
+      </c>
+      <c r="F123" s="78">
+        <v>2</v>
+      </c>
+      <c r="G123" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H123" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I123" s="79">
+        <v>82.54</v>
+      </c>
+      <c r="J123" s="79">
+        <v>-69.64</v>
+      </c>
+      <c r="K123" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="124" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B124" s="77" t="s">
+        <v>147</v>
+      </c>
+      <c r="C124" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D124" s="77" t="s">
+        <v>470</v>
+      </c>
+      <c r="E124" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="F124" s="78">
+        <v>1</v>
+      </c>
+      <c r="G124" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H124" s="79">
+        <v>825</v>
+      </c>
+      <c r="I124" s="79">
+        <v>89.24</v>
+      </c>
+      <c r="J124" s="79">
+        <v>-82.79</v>
+      </c>
+      <c r="K124" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="125" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B125" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="C125" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D125" s="77" t="s">
+        <v>471</v>
+      </c>
+      <c r="E125" s="77" t="s">
+        <v>216</v>
+      </c>
+      <c r="F125" s="78">
+        <v>1</v>
+      </c>
+      <c r="G125" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H125" s="79">
+        <v>825</v>
+      </c>
+      <c r="I125" s="79">
+        <v>96.84</v>
+      </c>
+      <c r="J125" s="79">
+        <v>-90.39</v>
+      </c>
+      <c r="K125" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="126" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B126" s="77" t="s">
+        <v>180</v>
+      </c>
+      <c r="C126" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D126" s="77" t="s">
+        <v>472</v>
+      </c>
+      <c r="E126" s="77" t="s">
+        <v>181</v>
+      </c>
+      <c r="F126" s="78">
+        <v>1</v>
+      </c>
+      <c r="G126" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H126" s="79">
+        <v>825</v>
+      </c>
+      <c r="I126" s="79">
+        <v>80.38</v>
+      </c>
+      <c r="J126" s="79">
+        <v>-73.93</v>
+      </c>
+      <c r="K126" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="127" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B127" s="77" t="s">
         <v>72</v>
       </c>
-      <c r="C63" s="10" t="s">
+      <c r="C127" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="D63" s="60" t="s">
+      <c r="D127" s="77" t="s">
+        <v>473</v>
+      </c>
+      <c r="E127" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="E63" s="46">
-        <v>28</v>
-      </c>
-      <c r="F63" s="46">
+      <c r="F127" s="78">
         <v>2</v>
       </c>
-      <c r="G63" s="67" t="s">
-        <v>394</v>
-      </c>
-      <c r="H63" s="47">
+      <c r="G127" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H127" s="79">
         <v>1650</v>
       </c>
-      <c r="I63" s="71">
-        <v>1800</v>
-      </c>
-      <c r="J63" s="72" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B64" s="10" t="s">
+      <c r="I127" s="79">
+        <v>9.2</v>
+      </c>
+      <c r="J127" s="79">
+        <v>0</v>
+      </c>
+      <c r="K127" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="128" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B128" s="77" t="s">
+        <v>69</v>
+      </c>
+      <c r="C128" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D128" s="77" t="s">
+        <v>474</v>
+      </c>
+      <c r="E128" s="77" t="s">
+        <v>165</v>
+      </c>
+      <c r="F128" s="78">
+        <v>1</v>
+      </c>
+      <c r="G128" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H128" s="79">
+        <v>825</v>
+      </c>
+      <c r="I128" s="79">
+        <v>5.75</v>
+      </c>
+      <c r="J128" s="79">
+        <v>0</v>
+      </c>
+      <c r="K128" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="129" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B129" s="77" t="s">
+        <v>69</v>
+      </c>
+      <c r="C129" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D129" s="77" t="s">
+        <v>475</v>
+      </c>
+      <c r="E129" s="77" t="s">
+        <v>135</v>
+      </c>
+      <c r="F129" s="78">
+        <v>1</v>
+      </c>
+      <c r="G129" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H129" s="79">
+        <v>825</v>
+      </c>
+      <c r="I129" s="79">
+        <v>5.75</v>
+      </c>
+      <c r="J129" s="79">
+        <v>0</v>
+      </c>
+      <c r="K129" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="130" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B130" s="77" t="s">
+        <v>69</v>
+      </c>
+      <c r="C130" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D130" s="77" t="s">
+        <v>476</v>
+      </c>
+      <c r="E130" s="77" t="s">
+        <v>109</v>
+      </c>
+      <c r="F130" s="78">
+        <v>4</v>
+      </c>
+      <c r="G130" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H130" s="79">
+        <v>3300</v>
+      </c>
+      <c r="I130" s="79">
+        <v>54.4</v>
+      </c>
+      <c r="J130" s="79">
+        <v>-41.48</v>
+      </c>
+      <c r="K130" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="131" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B131" s="77" t="s">
+        <v>69</v>
+      </c>
+      <c r="C131" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D131" s="77" t="s">
+        <v>477</v>
+      </c>
+      <c r="E131" s="77" t="s">
+        <v>109</v>
+      </c>
+      <c r="F131" s="78">
+        <v>1</v>
+      </c>
+      <c r="G131" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H131" s="79">
+        <v>825</v>
+      </c>
+      <c r="I131" s="79">
+        <v>4.6</v>
+      </c>
+      <c r="J131" s="79">
+        <v>0</v>
+      </c>
+      <c r="K131" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="132" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B132" s="77" t="s">
         <v>102</v>
       </c>
-      <c r="C64" s="10" t="s">
+      <c r="C132" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="D64" s="60" t="s">
+      <c r="D132" s="77" t="s">
+        <v>478</v>
+      </c>
+      <c r="E132" s="77" t="s">
+        <v>479</v>
+      </c>
+      <c r="F132" s="78">
+        <v>1</v>
+      </c>
+      <c r="G132" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H132" s="79">
+        <v>825</v>
+      </c>
+      <c r="I132" s="79">
+        <v>126.08</v>
+      </c>
+      <c r="J132" s="79">
+        <v>-119.63</v>
+      </c>
+      <c r="K132" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="133" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B133" s="77" t="s">
+        <v>102</v>
+      </c>
+      <c r="C133" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D133" s="77" t="s">
+        <v>480</v>
+      </c>
+      <c r="E133" s="77" t="s">
         <v>90</v>
       </c>
-      <c r="E64" s="46">
-        <v>41</v>
-      </c>
-      <c r="F64" s="46">
+      <c r="F133" s="78">
+        <v>1</v>
+      </c>
+      <c r="G133" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H133" s="79">
+        <v>825</v>
+      </c>
+      <c r="I133" s="79">
+        <v>82.15</v>
+      </c>
+      <c r="J133" s="79">
+        <v>-77.55</v>
+      </c>
+      <c r="K133" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="134" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B134" s="77" t="s">
+        <v>84</v>
+      </c>
+      <c r="C134" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="D134" s="77" t="s">
+        <v>481</v>
+      </c>
+      <c r="E134" s="77" t="s">
+        <v>89</v>
+      </c>
+      <c r="F134" s="78">
         <v>2</v>
       </c>
-      <c r="G64" s="67" t="s">
-        <v>394</v>
-      </c>
-      <c r="H64" s="47">
+      <c r="G134" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H134" s="79">
         <v>1650</v>
       </c>
-      <c r="I64" s="71">
-        <v>1800</v>
-      </c>
-      <c r="J64" s="72" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B65" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C65" s="10" t="s">
+      <c r="I134" s="79">
+        <v>80.56</v>
+      </c>
+      <c r="J134" s="79">
+        <v>-74.1</v>
+      </c>
+      <c r="K134" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="135" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B135" s="77" t="s">
+        <v>114</v>
+      </c>
+      <c r="C135" s="77" t="s">
+        <v>17</v>
+      </c>
+      <c r="D135" s="77" t="s">
+        <v>482</v>
+      </c>
+      <c r="E135" s="77" t="s">
+        <v>93</v>
+      </c>
+      <c r="F135" s="78">
+        <v>2</v>
+      </c>
+      <c r="G135" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H135" s="79">
+        <v>1650</v>
+      </c>
+      <c r="I135" s="79">
+        <v>84.2</v>
+      </c>
+      <c r="J135" s="79">
+        <v>-75</v>
+      </c>
+      <c r="K135" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="136" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B136" s="77" t="s">
+        <v>83</v>
+      </c>
+      <c r="C136" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="D65" s="60" t="s">
-        <v>89</v>
-      </c>
-      <c r="E65" s="46">
-        <v>47</v>
-      </c>
-      <c r="F65" s="46">
-        <v>2</v>
-      </c>
-      <c r="G65" s="67" t="s">
-        <v>401</v>
-      </c>
-      <c r="H65" s="47">
-        <v>1650</v>
-      </c>
-      <c r="I65" s="71">
-        <v>10800</v>
-      </c>
-      <c r="J65" s="72" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B66" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C66" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D66" s="60" t="s">
-        <v>93</v>
-      </c>
-      <c r="E66" s="46">
-        <v>69</v>
-      </c>
-      <c r="F66" s="46">
-        <v>2</v>
-      </c>
-      <c r="G66" s="67" t="s">
-        <v>394</v>
-      </c>
-      <c r="H66" s="47">
-        <v>1650</v>
-      </c>
-      <c r="I66" s="71">
-        <v>1275</v>
-      </c>
-      <c r="J66" s="72" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B67" s="10" t="s">
+      <c r="D136" s="77" t="s">
+        <v>483</v>
+      </c>
+      <c r="E136" s="77" t="s">
+        <v>301</v>
+      </c>
+      <c r="F136" s="78">
+        <v>1</v>
+      </c>
+      <c r="G136" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H136" s="79">
+        <v>825</v>
+      </c>
+      <c r="I136" s="79">
+        <v>83.83</v>
+      </c>
+      <c r="J136" s="79">
+        <v>-75</v>
+      </c>
+      <c r="K136" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="137" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B137" s="77" t="s">
         <v>146</v>
       </c>
-      <c r="C67" s="10" t="s">
+      <c r="C137" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="D67" s="60" t="s">
+      <c r="D137" s="77" t="s">
+        <v>484</v>
+      </c>
+      <c r="E137" s="77" t="s">
         <v>301</v>
       </c>
-      <c r="E67" s="46">
-        <v>98</v>
-      </c>
-      <c r="F67" s="46">
-        <v>1</v>
-      </c>
-      <c r="G67" s="67" t="s">
-        <v>401</v>
-      </c>
-      <c r="H67" s="47">
+      <c r="F137" s="78">
+        <v>1</v>
+      </c>
+      <c r="G137" s="78" t="s">
+        <v>398</v>
+      </c>
+      <c r="H137" s="79">
         <v>825</v>
       </c>
-      <c r="I67" s="71">
-        <v>2400</v>
-      </c>
-      <c r="J67" s="72" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B68" s="10" t="s">
+      <c r="I137" s="79">
+        <v>6.45</v>
+      </c>
+      <c r="J137" s="79">
+        <v>0</v>
+      </c>
+      <c r="K137" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="138" ht="32" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B138" s="77" t="s">
         <v>156</v>
       </c>
-      <c r="C68" s="10" t="s">
+      <c r="C138" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="D68" s="60" t="s">
+      <c r="D138" s="77" t="s">
+        <v>485</v>
+      </c>
+      <c r="E138" s="77" t="s">
         <v>235</v>
       </c>
-      <c r="E68" s="46">
-        <v>194</v>
-      </c>
-      <c r="F68" s="46">
+      <c r="F138" s="78">
         <v>3</v>
       </c>
-      <c r="G68" s="67" t="s">
-        <v>394</v>
-      </c>
-      <c r="H68" s="47">
-        <v>2475</v>
-      </c>
-      <c r="I68" s="71">
-        <v>1800</v>
-      </c>
-      <c r="J68" s="72" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="71" ht="24" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B71" s="66" t="s">
-        <v>406</v>
-      </c>
-      <c r="C71" s="66"/>
-      <c r="D71" s="66"/>
-      <c r="E71" s="66"/>
-      <c r="F71" s="66"/>
-      <c r="G71" s="66"/>
-      <c r="H71" s="66"/>
-      <c r="I71" s="66"/>
-      <c r="J71" s="66"/>
+      <c r="G138" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="H138" s="79">
+        <v>0</v>
+      </c>
+      <c r="I138" s="79">
+        <v>32.7</v>
+      </c>
+      <c r="J138" s="79">
+        <v>0</v>
+      </c>
+      <c r="K138" s="77" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="139" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B139" t="s">
+        <v>486</v>
+      </c>
+      <c r="F139" s="80">
+        <f>SUM(F71:F138)</f>
+        <v>131</v>
+      </c>
+      <c r="H139" s="81">
+        <f>SUM(H71:H138)</f>
+        <v>105600</v>
+      </c>
+      <c r="I139" s="81">
+        <f>SUM(I71:I138)</f>
+        <v>3047.9199999999987</v>
+      </c>
+    </row>
+    <row r="141" ht="36" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B141" s="82" t="s">
+        <v>487</v>
+      </c>
+      <c r="C141" s="82"/>
+      <c r="D141" s="82"/>
+      <c r="E141" s="82"/>
+      <c r="F141" s="82"/>
+      <c r="G141" s="82"/>
+      <c r="H141" s="82"/>
+      <c r="I141" s="82"/>
+      <c r="J141" s="82"/>
+      <c r="K141" s="82"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B3:J3"/>
+  <mergeCells count="19">
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B3:K3"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="F6:G6"/>
@@ -24984,11 +27535,14 @@
     <mergeCell ref="H7:I8"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B11:C12"/>
     <mergeCell ref="D11:E12"/>
-    <mergeCell ref="B71:J71"/>
+    <mergeCell ref="F11:G12"/>
+    <mergeCell ref="B66:K66"/>
+    <mergeCell ref="B69:K69"/>
+    <mergeCell ref="B141:K141"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="8" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>